--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Apr-Aug (USD 30K)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Apr-Aug (USD)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Plan Sep+12M" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +51,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F0E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,20 +76,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -461,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -471,7 +462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>book.immo — Business Model v2 (Sep 2026)</t>
+          <t>book.immo — Business Model v2</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -511,7 +502,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Локальные агентства подключают свои CRM к book.immo. Размещение БЕСПЛАТНО (агрегаторы берут деньги). Взамен — сплит комиссии при сделке.</t>
+          <t>Локальные агентства подключают свои CRM к book.immo. Размещение БЕСПЛАТНО. Взамен — сплит комиссии при сделке.</t>
         </is>
       </c>
     </row>
@@ -523,7 +514,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Объекты попадают к нам из CRM ДО публикации на агрегаторах (агентства платят агрегаторам за размещение и делают это с задержкой). Эксклюзивы — в топе выдачи по гео.</t>
+          <t>Объекты попадают к нам из CRM ДО публикации на агрегаторах. Эксклюзивы — в топе выдачи по гео.</t>
         </is>
       </c>
     </row>
@@ -547,7 +538,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Арендаторы/покупатели получают умный подбор + ИИ-автоматизацию: ИИ сам пишет письма, рассылает заявки, отслеживает новые объекты.</t>
+          <t>Арендаторы/покупатели получают умный подбор + ИИ-автоматизацию: заявки, мониторинг, документы.</t>
         </is>
       </c>
     </row>
@@ -559,7 +550,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Сделка закрывается агентством → комиссия делится между book.immo и маклером. Плюс pay-per-result ИИ-сервисы.</t>
+          <t>Сделку закрывает агентство → комиссия делится между book.immo и маклером. Плюс pay-per-result ИИ-сервисы.</t>
         </is>
       </c>
     </row>
@@ -571,7 +562,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Zolak.tech (virtual staging), ИИ-экспозе, квалифицированные лиды из нашей B2C-базы.</t>
+          <t>Zolak.tech (virtual staging), ИИ-экспозе, квалифицированные лиды из B2C-базы.</t>
         </is>
       </c>
     </row>
@@ -581,7 +572,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <f>== REVENUE STREAMS ===</f>
+        <f>== LEGAL ===</f>
         <v/>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -589,166 +580,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R1. Сплит аренда</t>
+          <t>Wohnungsvermittlungsgesetz</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Маклер получает ~2 Kaltmieten (~EUR 2,000-2,400) с собственника (Bestellerprinzip). Доля book.immo 25-30% = ~EUR 600/сделка.</t>
+          <t>Нельзя брать с арендатора комиссию за посредничество аренды. B2C fee — плата за софт, не за посредничество.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R2. Сплит продажа</t>
+          <t>Bestellerprinzip</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tippgeberprovision 20% от комиссии маклера (~EUR 12,000 при цене EUR 400K x 3%) = ~EUR 2,400/сделка.</t>
+          <t>Комиссию платит собственник маклеру. Сплит book.immo — из B2B-агентского договора. Легально.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R3. B2C AI-сервисы</t>
+          <t>GDPR</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Success fee EUR 149 за подписанный договор через ИИ-автоплатформу (заявки, мониторинг, документы). Оформлено как ТЕХНОЛОГИЧЕСКИЙ сервис, не посредничество.</t>
+          <t>DPA-договоры с агентствами; consent B2C-клиентов на передачу заявки.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R4. Agency upsells (позже)</t>
+          <t>Парсинг</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Zolak staging, ИИ-экспозе, premium-размещение лидов — аффилиат/маржа. С M6+.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <f>== LEGAL (критично) ===</f>
-        <v/>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Wohnungsvermittlungsgesetz</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>НЕЛЬЗЯ брать с арендатора комиссию за посредничество аренды. B2C-монетизация = плата за софт/автоматизацию (SaaS/success fee за сервис), договор без слова "Vermittlung".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Bestellerprinzip</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Комиссию за аренду платит заказчик (собственник) маклеру. Наш сплит — из комиссии маклера по агентскому договору B2B. Легально.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>GDPR</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Данные из CRM агентств — DPA-договоры с каждым агентством, данные B2C-клиентов — consent на передачу агентству.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Парсинг</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Публичные витрины; соблюдать robots/ToS-риски, не публиковать чужие фото без обработки. Риск-менеджмент: эксклюзивы снижают зависимость от парсинга.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3">
-        <f>== MOAT / отличие от агрегаторов ===</f>
-        <v/>
-      </c>
-      <c r="B25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Время</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Pre-market инвентарь: доступ к объектам до агрегаторов = главный магнит для B2C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Цена для агентств</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>0 EUR размещение против EUR 100-500+/мес у агрегаторов. Платят только при результате.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ИИ-автоматизация</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Агрегаторы — витрины. Мы — агент-автопилот для клиента (заявки/мониторинг/документы).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Выравнивание интересов</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Мы зарабатываем ТОЛЬКО на закрытых сделках — стимул доводить клиента до подписания, а не продавать клики.</t>
+          <t>Публичные витрины; соблюдать ToS-риски. Эксклюзивы снижают зависимость от парсинга.</t>
         </is>
       </c>
     </row>
@@ -766,7 +639,7 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -783,44 +656,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Инвестиция: $50K. Потрачено на запуск: $30K. Резерв на запуск/маркетинг: $20K.</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Инвестиция: $50,000. Потрачено на запуск: $30,000. Резерв: $20,000.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -829,7 +702,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Development (контракторы: фронт/бэк/парсер)</t>
+          <t>Разработка (фронт / бэк / парсер)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -855,7 +728,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/LLM APIs (Claude/OpenAI: автоматизация, письма)</t>
+          <t>AI / LLM API (автоматизация, письма)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -881,7 +754,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Design / UX (Framer, ассеты, брендинг)</t>
+          <t>Дизайн / UX (Framer, ассеты, брендинг)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -907,7 +780,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure (Vercel, серверы, CMS, Mapbox, Resend)</t>
+          <t>Инфраструктура (Vercel, серверы, CMS, Mapbox, Resend)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -959,7 +832,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tools &amp; Software (GitHub, Figma, Workspace, прочее)</t>
+          <t>Tools &amp; Software</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -985,7 +858,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Legal &amp; Company (юрлицо, договоры, DPA-шаблоны)</t>
+          <t>Legal и юрлицо (договоры, DPA-шаблоны)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1011,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Domain &amp; Trademark (book.immo, TM)</t>
+          <t>Домен и товарный знак (book.immo, TM)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1037,7 +910,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pre-launch marketing (лендинг-тесты, SEO-контент)</t>
+          <t>Pre-launch маркетинг (лендинг-тесты, SEO)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1063,7 +936,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Misc / buffer</t>
+          <t>Прочее / буфер</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1087,40 +960,40 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <f>SUM(B5:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <f>SUM(C5:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <f>SUM(D5:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <f>SUM(E5:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <f>SUM(F5:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="6">
         <f>SUM(G5:G14)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Что построено за $30K:</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Что построено:</t>
         </is>
       </c>
     </row>
@@ -1198,75 +1071,75 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Модель: комиссионный сплит с агентствами + B2C pay-per-result. Деньги только при закрытых сделках.</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Модель: комиссионный сплит с агентствами + B2C pay-per-result.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
@@ -1516,7 +1389,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rental: agent fee EUR 2,200 x 27.5% share</t>
+          <t>Rental: agent fee x 27.5% share</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1526,7 +1399,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sale: agent fee EUR 12,000 x 20% share</t>
+          <t>Sale: agent fee x 20% share</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1759,60 +1632,60 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <f>SUM(B18:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <f>SUM(C18:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <f>SUM(D18:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <f>SUM(E18:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="6">
         <f>SUM(F18:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <f>SUM(G18:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="6">
         <f>SUM(H18:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="6">
         <f>SUM(I18:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <f>SUM(J18:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <f>SUM(K18:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="6">
         <f>SUM(L18:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="6">
         <f>SUM(M18:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="8">
+      <c r="N22" s="6">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
@@ -1827,7 +1700,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marketing B2C (perf + content + SEO)</t>
+          <t>Маркетинг B2C (performance + контент + SEO)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1870,7 +1743,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Agency sales / partnerships (part-time BD)</t>
+          <t>Продажи агентствам / партнёрства (part-time BD)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1913,7 +1786,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Team: dev/support (контракторы)</t>
+          <t>Команда: dev/support (контракторы)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1956,7 +1829,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Infrastructure + AI APIs</t>
+          <t>Инфраструктура + AI API</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1999,7 +1872,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tools, legal, misc</t>
+          <t>Tools, legal, прочее</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2040,66 +1913,66 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>TOTAL COSTS</t>
         </is>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <f>SUM(B25:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
         <f>SUM(C25:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <f>SUM(D25:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="6">
         <f>SUM(E25:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <f>SUM(F25:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <f>SUM(G25:G29)</f>
         <v/>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="6">
         <f>SUM(H25:H29)</f>
         <v/>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="6">
         <f>SUM(I25:I29)</f>
         <v/>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="6">
         <f>SUM(J25:J29)</f>
         <v/>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="6">
         <f>SUM(K25:K29)</f>
         <v/>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="6">
         <f>SUM(L25:L29)</f>
         <v/>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="6">
         <f>SUM(M25:M29)</f>
         <v/>
       </c>
-      <c r="N30" s="8">
+      <c r="N30" s="6">
         <f>SUM(B30:M30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -2160,7 +2033,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CUMULATIVE (incl. $20K reserve)</t>
+          <t>CUMULATIVE (incl. €18,000 reserve)</t>
         </is>
       </c>
       <c r="B33">
@@ -2213,9 +2086,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Note: R3 оформлен как оплата ИИ-сервиса (не Vermittlung) — см. лист Business Model / Legal.</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Note: R3 оформлен как оплата ИИ-сервиса (не Vermittlung) — см. лист Business Model.</t>
         </is>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1751,168 +1751,119 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Продажник: % от выручки агентских сделок</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I39" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="J38" s="8" t="n">
+      <c r="J39" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="K38" s="8" t="n">
+      <c r="K39" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="L39" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="N38">
-        <f>SUM(B38:M38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="N39">
+        <f>SUM(B39:M39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F41">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I41">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J41">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K41">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L41">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M41">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N41">
-        <f>SUM(B41:M41)</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Регистрации: комьюнити</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B42">
-        <f>B9</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C42">
-        <f>C9</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D42">
-        <f>D9</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E42">
-        <f>E9</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F42">
-        <f>F9</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G42">
-        <f>G9</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H42">
-        <f>H9</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I42">
-        <f>I9</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J42">
-        <f>J9</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K42">
-        <f>K9</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L42">
-        <f>L9</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M42">
-        <f>M9</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N42">
@@ -1923,55 +1874,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B43">
-        <f>B12*$B$13</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C43">
-        <f>C12*$B$13</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D43">
-        <f>D12*$B$13</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E43">
-        <f>E12*$B$13</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F43">
-        <f>F12*$B$13</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G43">
-        <f>G12*$B$13</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H43">
-        <f>H12*$B$13</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I43">
-        <f>I12*$B$13</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J43">
-        <f>J12*$B$13</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K43">
-        <f>K12*$B$13</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L43">
-        <f>L12*$B$13</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M43">
-        <f>M12*$B$13</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N43">
@@ -1982,55 +1933,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: SEO</t>
         </is>
       </c>
       <c r="B44">
-        <f>B14*$B$15*$B$16</f>
+        <f>B12*$B$13</f>
         <v/>
       </c>
       <c r="C44">
-        <f>C14*$B$15*$B$16</f>
+        <f>C12*$B$13</f>
         <v/>
       </c>
       <c r="D44">
-        <f>D14*$B$15*$B$16</f>
+        <f>D12*$B$13</f>
         <v/>
       </c>
       <c r="E44">
-        <f>E14*$B$15*$B$16</f>
+        <f>E12*$B$13</f>
         <v/>
       </c>
       <c r="F44">
-        <f>F14*$B$15*$B$16</f>
+        <f>F12*$B$13</f>
         <v/>
       </c>
       <c r="G44">
-        <f>G14*$B$15*$B$16</f>
+        <f>G12*$B$13</f>
         <v/>
       </c>
       <c r="H44">
-        <f>H14*$B$15*$B$16</f>
+        <f>H12*$B$13</f>
         <v/>
       </c>
       <c r="I44">
-        <f>I14*$B$15*$B$16</f>
+        <f>I12*$B$13</f>
         <v/>
       </c>
       <c r="J44">
-        <f>J14*$B$15*$B$16</f>
+        <f>J12*$B$13</f>
         <v/>
       </c>
       <c r="K44">
-        <f>K14*$B$15*$B$16</f>
+        <f>K12*$B$13</f>
         <v/>
       </c>
       <c r="L44">
-        <f>L14*$B$15*$B$16</f>
+        <f>L12*$B$13</f>
         <v/>
       </c>
       <c r="M44">
-        <f>M14*$B$15*$B$16</f>
+        <f>M12*$B$13</f>
         <v/>
       </c>
       <c r="N44">
@@ -2041,55 +1992,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: агентства</t>
         </is>
       </c>
       <c r="B45">
-        <f>B10*$B$11</f>
+        <f>B14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="C45">
-        <f>C10*$B$11</f>
+        <f>C14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D10*$B$11</f>
+        <f>D14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E10*$B$11</f>
+        <f>E14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F10*$B$11</f>
+        <f>F14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G10*$B$11</f>
+        <f>G14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H10*$B$11</f>
+        <f>H14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I10*$B$11</f>
+        <f>I14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J10*$B$11</f>
+        <f>J14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K10*$B$11</f>
+        <f>K14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L10*$B$11</f>
+        <f>L14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M10*$B$11</f>
+        <f>M14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="N45">
@@ -2098,119 +2049,119 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>B10*$B$11</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>C10*$B$11</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>D10*$B$11</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>E10*$B$11</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>F10*$B$11</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>G10*$B$11</f>
+        <v/>
+      </c>
+      <c r="H46">
+        <f>H10*$B$11</f>
+        <v/>
+      </c>
+      <c r="I46">
+        <f>I10*$B$11</f>
+        <v/>
+      </c>
+      <c r="J46">
+        <f>J10*$B$11</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>K10*$B$11</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>L10*$B$11</f>
+        <v/>
+      </c>
+      <c r="M46">
+        <f>M10*$B$11</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>SUM(B46:M46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Итого регистраций</t>
         </is>
       </c>
-      <c r="B46" s="6">
-        <f>B41+B42+B43+B44+B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>C41+C42+C43+C44+C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="6">
-        <f>D41+D42+D43+D44+D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="6">
-        <f>E41+E42+E43+E44+E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="6">
-        <f>F41+F42+F43+F44+F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="6">
-        <f>G41+G42+G43+G44+G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="6">
-        <f>H41+H42+H43+H44+H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>I41+I42+I43+I44+I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>J41+J42+J43+J44+J45</f>
-        <v/>
-      </c>
-      <c r="K46" s="6">
-        <f>K41+K42+K43+K44+K45</f>
-        <v/>
-      </c>
-      <c r="L46" s="6">
-        <f>L41+L42+L43+L44+L45</f>
-        <v/>
-      </c>
-      <c r="M46" s="6">
-        <f>M41+M42+M43+M44+M45</f>
-        <v/>
-      </c>
-      <c r="N46" s="6">
-        <f>SUM(B46:M46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Квалифицировано: paid</t>
-        </is>
-      </c>
-      <c r="B47">
-        <f>B41*$B$20</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>C41*$B$20</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>D41*$B$20</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>E41*$B$20</f>
-        <v/>
-      </c>
-      <c r="F47">
-        <f>F41*$B$20</f>
-        <v/>
-      </c>
-      <c r="G47">
-        <f>G41*$B$20</f>
-        <v/>
-      </c>
-      <c r="H47">
-        <f>H41*$B$20</f>
-        <v/>
-      </c>
-      <c r="I47">
-        <f>I41*$B$20</f>
-        <v/>
-      </c>
-      <c r="J47">
-        <f>J41*$B$20</f>
-        <v/>
-      </c>
-      <c r="K47">
-        <f>K41*$B$20</f>
-        <v/>
-      </c>
-      <c r="L47">
-        <f>L41*$B$20</f>
-        <v/>
-      </c>
-      <c r="M47">
-        <f>M41*$B$20</f>
-        <v/>
-      </c>
-      <c r="N47">
+      <c r="B47" s="6">
+        <f>B42+B43+B44+B45+B46</f>
+        <v/>
+      </c>
+      <c r="C47" s="6">
+        <f>C42+C43+C44+C45+C46</f>
+        <v/>
+      </c>
+      <c r="D47" s="6">
+        <f>D42+D43+D44+D45+D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="6">
+        <f>E42+E43+E44+E45+E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="6">
+        <f>F42+F43+F44+F45+F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="6">
+        <f>G42+G43+G44+G45+G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="6">
+        <f>H42+H43+H44+H45+H46</f>
+        <v/>
+      </c>
+      <c r="I47" s="6">
+        <f>I42+I43+I44+I45+I46</f>
+        <v/>
+      </c>
+      <c r="J47" s="6">
+        <f>J42+J43+J44+J45+J46</f>
+        <v/>
+      </c>
+      <c r="K47" s="6">
+        <f>K42+K43+K44+K45+K46</f>
+        <v/>
+      </c>
+      <c r="L47" s="6">
+        <f>L42+L43+L44+L45+L46</f>
+        <v/>
+      </c>
+      <c r="M47" s="6">
+        <f>M42+M43+M44+M45+M46</f>
+        <v/>
+      </c>
+      <c r="N47" s="6">
         <f>SUM(B47:M47)</f>
         <v/>
       </c>
@@ -2218,55 +2169,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Квалифицировано: комьюнити</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B48">
-        <f>B42*$B$21</f>
+        <f>B42*$B$20</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C42*$B$21</f>
+        <f>C42*$B$20</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D42*$B$21</f>
+        <f>D42*$B$20</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E42*$B$21</f>
+        <f>E42*$B$20</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F42*$B$21</f>
+        <f>F42*$B$20</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G42*$B$21</f>
+        <f>G42*$B$20</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H42*$B$21</f>
+        <f>H42*$B$20</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I42*$B$21</f>
+        <f>I42*$B$20</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J42*$B$21</f>
+        <f>J42*$B$20</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K42*$B$21</f>
+        <f>K42*$B$20</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L42*$B$21</f>
+        <f>L42*$B$20</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M42*$B$21</f>
+        <f>M42*$B$20</f>
         <v/>
       </c>
       <c r="N48">
@@ -2277,55 +2228,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Квалифицировано: SEO</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B49">
-        <f>B43*$B$23</f>
+        <f>B43*$B$21</f>
         <v/>
       </c>
       <c r="C49">
-        <f>C43*$B$23</f>
+        <f>C43*$B$21</f>
         <v/>
       </c>
       <c r="D49">
-        <f>D43*$B$23</f>
+        <f>D43*$B$21</f>
         <v/>
       </c>
       <c r="E49">
-        <f>E43*$B$23</f>
+        <f>E43*$B$21</f>
         <v/>
       </c>
       <c r="F49">
-        <f>F43*$B$23</f>
+        <f>F43*$B$21</f>
         <v/>
       </c>
       <c r="G49">
-        <f>G43*$B$23</f>
+        <f>G43*$B$21</f>
         <v/>
       </c>
       <c r="H49">
-        <f>H43*$B$23</f>
+        <f>H43*$B$21</f>
         <v/>
       </c>
       <c r="I49">
-        <f>I43*$B$23</f>
+        <f>I43*$B$21</f>
         <v/>
       </c>
       <c r="J49">
-        <f>J43*$B$23</f>
+        <f>J43*$B$21</f>
         <v/>
       </c>
       <c r="K49">
-        <f>K43*$B$23</f>
+        <f>K43*$B$21</f>
         <v/>
       </c>
       <c r="L49">
-        <f>L43*$B$23</f>
+        <f>L43*$B$21</f>
         <v/>
       </c>
       <c r="M49">
-        <f>M43*$B$23</f>
+        <f>M43*$B$21</f>
         <v/>
       </c>
       <c r="N49">
@@ -2336,55 +2287,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: SEO</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$25</f>
+        <f>B44*$B$23</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$25</f>
+        <f>C44*$B$23</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$25</f>
+        <f>D44*$B$23</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$25</f>
+        <f>E44*$B$23</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$25</f>
+        <f>F44*$B$23</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$25</f>
+        <f>G44*$B$23</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$25</f>
+        <f>H44*$B$23</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$25</f>
+        <f>I44*$B$23</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$25</f>
+        <f>J44*$B$23</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$25</f>
+        <f>K44*$B$23</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$25</f>
+        <f>L44*$B$23</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$25</f>
+        <f>M44*$B$23</f>
         <v/>
       </c>
       <c r="N50">
@@ -2395,55 +2346,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: агентства</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$22</f>
+        <f>B45*$B$25</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$22</f>
+        <f>C45*$B$25</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$22</f>
+        <f>D45*$B$25</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$22</f>
+        <f>E45*$B$25</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$22</f>
+        <f>F45*$B$25</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$22</f>
+        <f>G45*$B$25</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$22</f>
+        <f>H45*$B$25</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$22</f>
+        <f>I45*$B$25</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$22</f>
+        <f>J45*$B$25</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$22</f>
+        <f>K45*$B$25</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$22</f>
+        <f>L45*$B$25</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$22</f>
+        <f>M45*$B$25</f>
         <v/>
       </c>
       <c r="N51">
@@ -2454,54 +2405,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
+          <t>Квалифицировано: партнёры</t>
+        </is>
+      </c>
+      <c r="B52">
+        <f>B46*$B$22</f>
+        <v/>
       </c>
       <c r="C52">
-        <f>B56*$B$17*$B$24</f>
+        <f>C46*$B$22</f>
         <v/>
       </c>
       <c r="D52">
-        <f>C56*$B$17*$B$24</f>
+        <f>D46*$B$22</f>
         <v/>
       </c>
       <c r="E52">
-        <f>D56*$B$17*$B$24</f>
+        <f>E46*$B$22</f>
         <v/>
       </c>
       <c r="F52">
-        <f>E56*$B$17*$B$24</f>
+        <f>F46*$B$22</f>
         <v/>
       </c>
       <c r="G52">
-        <f>F56*$B$17*$B$24</f>
+        <f>G46*$B$22</f>
         <v/>
       </c>
       <c r="H52">
-        <f>G56*$B$17*$B$24</f>
+        <f>H46*$B$22</f>
         <v/>
       </c>
       <c r="I52">
-        <f>H56*$B$17*$B$24</f>
+        <f>I46*$B$22</f>
         <v/>
       </c>
       <c r="J52">
-        <f>I56*$B$17*$B$24</f>
+        <f>J46*$B$22</f>
         <v/>
       </c>
       <c r="K52">
-        <f>J56*$B$17*$B$24</f>
+        <f>K46*$B$22</f>
         <v/>
       </c>
       <c r="L52">
-        <f>K56*$B$17*$B$24</f>
+        <f>L46*$B$22</f>
         <v/>
       </c>
       <c r="M52">
-        <f>L56*$B$17*$B$24</f>
+        <f>M46*$B$22</f>
         <v/>
       </c>
       <c r="N52">
@@ -2510,119 +2462,118 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <f>B57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>C57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>D57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>E57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="H53">
+        <f>G57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="I53">
+        <f>H57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="J53">
+        <f>I57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="K53">
+        <f>J57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="L53">
+        <f>K57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="M53">
+        <f>L57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>SUM(B53:M53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Итого квалифицированных</t>
         </is>
       </c>
-      <c r="B53" s="6">
-        <f>B47+B48+B49+B50+B51+B52</f>
-        <v/>
-      </c>
-      <c r="C53" s="6">
-        <f>C47+C48+C49+C50+C51+C52</f>
-        <v/>
-      </c>
-      <c r="D53" s="6">
-        <f>D47+D48+D49+D50+D51+D52</f>
-        <v/>
-      </c>
-      <c r="E53" s="6">
-        <f>E47+E48+E49+E50+E51+E52</f>
-        <v/>
-      </c>
-      <c r="F53" s="6">
-        <f>F47+F48+F49+F50+F51+F52</f>
-        <v/>
-      </c>
-      <c r="G53" s="6">
-        <f>G47+G48+G49+G50+G51+G52</f>
-        <v/>
-      </c>
-      <c r="H53" s="6">
-        <f>H47+H48+H49+H50+H51+H52</f>
-        <v/>
-      </c>
-      <c r="I53" s="6">
-        <f>I47+I48+I49+I50+I51+I52</f>
-        <v/>
-      </c>
-      <c r="J53" s="6">
-        <f>J47+J48+J49+J50+J51+J52</f>
-        <v/>
-      </c>
-      <c r="K53" s="6">
-        <f>K47+K48+K49+K50+K51+K52</f>
-        <v/>
-      </c>
-      <c r="L53" s="6">
-        <f>L47+L48+L49+L50+L51+L52</f>
-        <v/>
-      </c>
-      <c r="M53" s="6">
-        <f>M47+M48+M49+M50+M51+M52</f>
-        <v/>
-      </c>
-      <c r="N53" s="6">
-        <f>SUM(B53:M53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Сделки через агентства</t>
-        </is>
-      </c>
-      <c r="B54">
-        <f>ROUND(MIN(B53*$B$28,B14*B30),0)</f>
-        <v/>
-      </c>
-      <c r="C54">
-        <f>ROUND(MIN(C53*$B$28,C14*C30),0)</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>ROUND(MIN(D53*$B$28,D14*D30),0)</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>ROUND(MIN(E53*$B$28,E14*E30),0)</f>
-        <v/>
-      </c>
-      <c r="F54">
-        <f>ROUND(MIN(F53*$B$28,F14*F30),0)</f>
-        <v/>
-      </c>
-      <c r="G54">
-        <f>ROUND(MIN(G53*$B$28,G14*G30),0)</f>
-        <v/>
-      </c>
-      <c r="H54">
-        <f>ROUND(MIN(H53*$B$28,H14*H30),0)</f>
-        <v/>
-      </c>
-      <c r="I54">
-        <f>ROUND(MIN(I53*$B$28,I14*I30),0)</f>
-        <v/>
-      </c>
-      <c r="J54">
-        <f>ROUND(MIN(J53*$B$28,J14*J30),0)</f>
-        <v/>
-      </c>
-      <c r="K54">
-        <f>ROUND(MIN(K53*$B$28,K14*K30),0)</f>
-        <v/>
-      </c>
-      <c r="L54">
-        <f>ROUND(MIN(L53*$B$28,L14*L30),0)</f>
-        <v/>
-      </c>
-      <c r="M54">
-        <f>ROUND(MIN(M53*$B$28,M14*M30),0)</f>
-        <v/>
-      </c>
-      <c r="N54">
+      <c r="B54" s="6">
+        <f>B48+B49+B50+B51+B52+B53</f>
+        <v/>
+      </c>
+      <c r="C54" s="6">
+        <f>C48+C49+C50+C51+C52+C53</f>
+        <v/>
+      </c>
+      <c r="D54" s="6">
+        <f>D48+D49+D50+D51+D52+D53</f>
+        <v/>
+      </c>
+      <c r="E54" s="6">
+        <f>E48+E49+E50+E51+E52+E53</f>
+        <v/>
+      </c>
+      <c r="F54" s="6">
+        <f>F48+F49+F50+F51+F52+F53</f>
+        <v/>
+      </c>
+      <c r="G54" s="6">
+        <f>G48+G49+G50+G51+G52+G53</f>
+        <v/>
+      </c>
+      <c r="H54" s="6">
+        <f>H48+H49+H50+H51+H52+H53</f>
+        <v/>
+      </c>
+      <c r="I54" s="6">
+        <f>I48+I49+I50+I51+I52+I53</f>
+        <v/>
+      </c>
+      <c r="J54" s="6">
+        <f>J48+J49+J50+J51+J52+J53</f>
+        <v/>
+      </c>
+      <c r="K54" s="6">
+        <f>K48+K49+K50+K51+K52+K53</f>
+        <v/>
+      </c>
+      <c r="L54" s="6">
+        <f>L48+L49+L50+L51+L52+L53</f>
+        <v/>
+      </c>
+      <c r="M54" s="6">
+        <f>M48+M49+M50+M51+M52+M53</f>
+        <v/>
+      </c>
+      <c r="N54" s="6">
         <f>SUM(B54:M54)</f>
         <v/>
       </c>
@@ -2630,55 +2581,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Сделки на каталоге IS24</t>
+          <t>Сделки через агентства</t>
         </is>
       </c>
       <c r="B55">
-        <f>ROUND(B53*$B$29,0)</f>
+        <f>ROUND(MIN(B54*$B$28,B14*B30),0)</f>
         <v/>
       </c>
       <c r="C55">
-        <f>ROUND(C53*$B$29,0)</f>
+        <f>ROUND(MIN(C54*$B$28,C14*C30),0)</f>
         <v/>
       </c>
       <c r="D55">
-        <f>ROUND(D53*$B$29,0)</f>
+        <f>ROUND(MIN(D54*$B$28,D14*D30),0)</f>
         <v/>
       </c>
       <c r="E55">
-        <f>ROUND(E53*$B$29,0)</f>
+        <f>ROUND(MIN(E54*$B$28,E14*E30),0)</f>
         <v/>
       </c>
       <c r="F55">
-        <f>ROUND(F53*$B$29,0)</f>
+        <f>ROUND(MIN(F54*$B$28,F14*F30),0)</f>
         <v/>
       </c>
       <c r="G55">
-        <f>ROUND(G53*$B$29,0)</f>
+        <f>ROUND(MIN(G54*$B$28,G14*G30),0)</f>
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(H53*$B$29,0)</f>
+        <f>ROUND(MIN(H54*$B$28,H14*H30),0)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(I53*$B$29,0)</f>
+        <f>ROUND(MIN(I54*$B$28,I14*I30),0)</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(J53*$B$29,0)</f>
+        <f>ROUND(MIN(J54*$B$28,J14*J30),0)</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(K53*$B$29,0)</f>
+        <f>ROUND(MIN(K54*$B$28,K14*K30),0)</f>
         <v/>
       </c>
       <c r="L55">
-        <f>ROUND(L53*$B$29,0)</f>
+        <f>ROUND(MIN(L54*$B$28,L14*L30),0)</f>
         <v/>
       </c>
       <c r="M55">
-        <f>ROUND(M53*$B$29,0)</f>
+        <f>ROUND(MIN(M54*$B$28,M14*M30),0)</f>
         <v/>
       </c>
       <c r="N55">
@@ -2687,241 +2638,241 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Сделки на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>ROUND(B54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>ROUND(C54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>ROUND(D54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>ROUND(E54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>ROUND(F54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>ROUND(G54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>ROUND(H54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>ROUND(I54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>ROUND(J54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>ROUND(K54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>ROUND(L54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>ROUND(M54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>SUM(B56:M56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Сделок всего</t>
         </is>
       </c>
-      <c r="B56" s="6">
-        <f>B54+B55</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>C54+C55</f>
-        <v/>
-      </c>
-      <c r="D56" s="6">
-        <f>D54+D55</f>
-        <v/>
-      </c>
-      <c r="E56" s="6">
-        <f>E54+E55</f>
-        <v/>
-      </c>
-      <c r="F56" s="6">
-        <f>F54+F55</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G54+G55</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H54+H55</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I54+I55</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J54+J55</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K54+K55</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L54+L55</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M54+M55</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>SUM(B56:M56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B57" s="6">
+        <f>B55+B56</f>
+        <v/>
+      </c>
+      <c r="C57" s="6">
+        <f>C55+C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="6">
+        <f>D55+D56</f>
+        <v/>
+      </c>
+      <c r="E57" s="6">
+        <f>E55+E56</f>
+        <v/>
+      </c>
+      <c r="F57" s="6">
+        <f>F55+F56</f>
+        <v/>
+      </c>
+      <c r="G57" s="6">
+        <f>G55+G56</f>
+        <v/>
+      </c>
+      <c r="H57" s="6">
+        <f>H55+H56</f>
+        <v/>
+      </c>
+      <c r="I57" s="6">
+        <f>I55+I56</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>J55+J56</f>
+        <v/>
+      </c>
+      <c r="K57" s="6">
+        <f>K55+K56</f>
+        <v/>
+      </c>
+      <c r="L57" s="6">
+        <f>L55+L56</f>
+        <v/>
+      </c>
+      <c r="M57" s="6">
+        <f>M55+M56</f>
+        <v/>
+      </c>
+      <c r="N57" s="6">
+        <f>SUM(B57:M57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Сделок с B2C fee</t>
         </is>
       </c>
-      <c r="B57">
-        <f>B55+ROUND(B54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>C55+ROUND(C54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>D55+ROUND(D54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>E55+ROUND(E54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>F55+ROUND(F54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="G57">
-        <f>G55+ROUND(G54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>H55+ROUND(H54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="I57">
-        <f>I55+ROUND(I54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="J57">
-        <f>J55+ROUND(J54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="K57">
-        <f>K55+ROUND(K54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="L57">
-        <f>L55+ROUND(L54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="M57">
-        <f>M55+ROUND(M54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="N57">
-        <f>SUM(B57:M57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B58">
+        <f>B56+ROUND(B55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>C56+ROUND(C55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>D56+ROUND(D55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>E56+ROUND(E55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>F56+ROUND(F55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>G56+ROUND(G55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>H56+ROUND(H55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>I56+ROUND(I55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>J56+ROUND(J55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>K56+ROUND(K55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>L56+ROUND(L55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>M56+ROUND(M55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>SUM(B58:M58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>ВЫРУЧКА</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
-        </is>
-      </c>
-      <c r="B60">
-        <f>ROUND(B54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>ROUND(C54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>ROUND(D54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>ROUND(E54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="F60">
-        <f>ROUND(F54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>ROUND(G54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="H60">
-        <f>ROUND(H54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="I60">
-        <f>ROUND(I54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="J60">
-        <f>ROUND(J54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="K60">
-        <f>ROUND(K54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="L60">
-        <f>ROUND(L54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="M60">
-        <f>ROUND(M54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="N60">
-        <f>SUM(B60:M60)</f>
-        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R3: B2C fee</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B61">
-        <f>B57*$B$36</f>
+        <f>ROUND(B55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="C61">
-        <f>C57*$B$36</f>
+        <f>ROUND(C55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="D61">
-        <f>D57*$B$36</f>
+        <f>ROUND(D55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="E61">
-        <f>E57*$B$36</f>
+        <f>ROUND(E55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>F57*$B$36</f>
+        <f>ROUND(F55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>G57*$B$36</f>
+        <f>ROUND(G55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>H57*$B$36</f>
+        <f>ROUND(H55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>I57*$B$36</f>
+        <f>ROUND(I55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="J61">
-        <f>J57*$B$36</f>
+        <f>ROUND(J55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>K57*$B$36</f>
+        <f>ROUND(K55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="L61">
-        <f>L57*$B$36</f>
+        <f>ROUND(L55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="M61">
-        <f>M57*$B$36</f>
+        <f>ROUND(M55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="N61">
@@ -2932,55 +2883,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R4: upsell</t>
+          <t>R3: B2C fee</t>
         </is>
       </c>
       <c r="B62">
-        <f>B38</f>
+        <f>B58*$B$36</f>
         <v/>
       </c>
       <c r="C62">
-        <f>C38</f>
+        <f>C58*$B$36</f>
         <v/>
       </c>
       <c r="D62">
-        <f>D38</f>
+        <f>D58*$B$36</f>
         <v/>
       </c>
       <c r="E62">
-        <f>E38</f>
+        <f>E58*$B$36</f>
         <v/>
       </c>
       <c r="F62">
-        <f>F38</f>
+        <f>F58*$B$36</f>
         <v/>
       </c>
       <c r="G62">
-        <f>G38</f>
+        <f>G58*$B$36</f>
         <v/>
       </c>
       <c r="H62">
-        <f>H38</f>
+        <f>H58*$B$36</f>
         <v/>
       </c>
       <c r="I62">
-        <f>I38</f>
+        <f>I58*$B$36</f>
         <v/>
       </c>
       <c r="J62">
-        <f>J38</f>
+        <f>J58*$B$36</f>
         <v/>
       </c>
       <c r="K62">
-        <f>K38</f>
+        <f>K58*$B$36</f>
         <v/>
       </c>
       <c r="L62">
-        <f>L38</f>
+        <f>L58*$B$36</f>
         <v/>
       </c>
       <c r="M62">
-        <f>M38</f>
+        <f>M58*$B$36</f>
         <v/>
       </c>
       <c r="N62">
@@ -2989,171 +2940,183 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B63">
+        <f>B39</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>C39</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>D39</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>G39</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>H39</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>I39</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>J39</f>
+        <v/>
+      </c>
+      <c r="K63">
+        <f>K39</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>L39</f>
+        <v/>
+      </c>
+      <c r="M63">
+        <f>M39</f>
+        <v/>
+      </c>
+      <c r="N63">
+        <f>SUM(B63:M63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B63" s="6">
-        <f>B60+B61+B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="6">
-        <f>C60+C61+C62</f>
-        <v/>
-      </c>
-      <c r="D63" s="6">
-        <f>D60+D61+D62</f>
-        <v/>
-      </c>
-      <c r="E63" s="6">
-        <f>E60+E61+E62</f>
-        <v/>
-      </c>
-      <c r="F63" s="6">
-        <f>F60+F61+F62</f>
-        <v/>
-      </c>
-      <c r="G63" s="6">
-        <f>G60+G61+G62</f>
-        <v/>
-      </c>
-      <c r="H63" s="6">
-        <f>H60+H61+H62</f>
-        <v/>
-      </c>
-      <c r="I63" s="6">
-        <f>I60+I61+I62</f>
-        <v/>
-      </c>
-      <c r="J63" s="6">
-        <f>J60+J61+J62</f>
-        <v/>
-      </c>
-      <c r="K63" s="6">
-        <f>K60+K61+K62</f>
-        <v/>
-      </c>
-      <c r="L63" s="6">
-        <f>L60+L61+L62</f>
-        <v/>
-      </c>
-      <c r="M63" s="6">
-        <f>M60+M61+M62</f>
-        <v/>
-      </c>
-      <c r="N63" s="6">
-        <f>SUM(B63:M63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="B64" s="6">
+        <f>B61+B62+B63</f>
+        <v/>
+      </c>
+      <c r="C64" s="6">
+        <f>C61+C62+C63</f>
+        <v/>
+      </c>
+      <c r="D64" s="6">
+        <f>D61+D62+D63</f>
+        <v/>
+      </c>
+      <c r="E64" s="6">
+        <f>E61+E62+E63</f>
+        <v/>
+      </c>
+      <c r="F64" s="6">
+        <f>F61+F62+F63</f>
+        <v/>
+      </c>
+      <c r="G64" s="6">
+        <f>G61+G62+G63</f>
+        <v/>
+      </c>
+      <c r="H64" s="6">
+        <f>H61+H62+H63</f>
+        <v/>
+      </c>
+      <c r="I64" s="6">
+        <f>I61+I62+I63</f>
+        <v/>
+      </c>
+      <c r="J64" s="6">
+        <f>J61+J62+J63</f>
+        <v/>
+      </c>
+      <c r="K64" s="6">
+        <f>K61+K62+K63</f>
+        <v/>
+      </c>
+      <c r="L64" s="6">
+        <f>L61+L62+L63</f>
+        <v/>
+      </c>
+      <c r="M64" s="6">
+        <f>M61+M62+M63</f>
+        <v/>
+      </c>
+      <c r="N64" s="6">
+        <f>SUM(B64:M64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B66">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C66">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D66">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E66">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F66">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G66">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H66">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I66">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J66">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K66">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L66">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M66">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N66">
-        <f>SUM(B66:M66)</f>
-        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M67" s="8" t="n">
-        <v>500</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M67">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N67">
         <f>SUM(B67:M67)</f>
@@ -3163,44 +3126,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BD: агентства + партнёрства + комьюнити</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="C68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="M68" s="8" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="N68">
         <f>SUM(B68:M68)</f>
@@ -3210,44 +3173,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>3000</v>
+        <v>1291</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3000</v>
+        <v>1382</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3500</v>
+        <v>1473</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>3500</v>
+        <v>1564</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>3500</v>
+        <v>1655</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>4000</v>
+        <v>1745</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>4000</v>
+        <v>1836</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>4000</v>
+        <v>1927</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>4500</v>
+        <v>2018</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>4500</v>
+        <v>2109</v>
       </c>
       <c r="M69" s="8" t="n">
-        <v>4500</v>
+        <v>2200</v>
       </c>
       <c r="N69">
         <f>SUM(B69:M69)</f>
@@ -3257,44 +3220,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Команда: dev / support (контракторы)</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="C70" s="8" t="n">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>850</v>
+        <v>3500</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>900</v>
+        <v>3500</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>950</v>
+        <v>3500</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>1050</v>
+        <v>4000</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>1150</v>
+        <v>4500</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>1200</v>
+        <v>4500</v>
       </c>
       <c r="M70" s="8" t="n">
-        <v>1250</v>
+        <v>4500</v>
       </c>
       <c r="N70">
         <f>SUM(B70:M70)</f>
@@ -3304,44 +3267,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Инфраструктура + AI API</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="N71">
         <f>SUM(B71:M71)</f>
@@ -3349,116 +3312,163 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="B72" s="6">
-        <f>B66+B67+B68+B69+B70+B71</f>
-        <v/>
-      </c>
-      <c r="C72" s="6">
-        <f>C66+C67+C68+C69+C70+C71</f>
-        <v/>
-      </c>
-      <c r="D72" s="6">
-        <f>D66+D67+D68+D69+D70+D71</f>
-        <v/>
-      </c>
-      <c r="E72" s="6">
-        <f>E66+E67+E68+E69+E70+E71</f>
-        <v/>
-      </c>
-      <c r="F72" s="6">
-        <f>F66+F67+F68+F69+F70+F71</f>
-        <v/>
-      </c>
-      <c r="G72" s="6">
-        <f>G66+G67+G68+G69+G70+G71</f>
-        <v/>
-      </c>
-      <c r="H72" s="6">
-        <f>H66+H67+H68+H69+H70+H71</f>
-        <v/>
-      </c>
-      <c r="I72" s="6">
-        <f>I66+I67+I68+I69+I70+I71</f>
-        <v/>
-      </c>
-      <c r="J72" s="6">
-        <f>J66+J67+J68+J69+J70+J71</f>
-        <v/>
-      </c>
-      <c r="K72" s="6">
-        <f>K66+K67+K68+K69+K70+K71</f>
-        <v/>
-      </c>
-      <c r="L72" s="6">
-        <f>L66+L67+L68+L69+L70+L71</f>
-        <v/>
-      </c>
-      <c r="M72" s="6">
-        <f>M66+M67+M68+M69+M70+M71</f>
-        <v/>
-      </c>
-      <c r="N72" s="6">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N72">
         <f>SUM(B72:M72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>ROUND(B61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>ROUND(C61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>ROUND(D61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>ROUND(E61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>ROUND(F61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>ROUND(G61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>ROUND(H61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>ROUND(I61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>ROUND(J61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>ROUND(K61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>ROUND(L61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M73">
+        <f>ROUND(M61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N73">
+        <f>SUM(B73:M73)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>TOTAL COSTS</t>
         </is>
       </c>
       <c r="B74" s="6">
-        <f>B63-B72</f>
+        <f>B67+B68+B69+B70+B71+B72+B73</f>
         <v/>
       </c>
       <c r="C74" s="6">
-        <f>C63-C72</f>
+        <f>C67+C68+C69+C70+C71+C72+C73</f>
         <v/>
       </c>
       <c r="D74" s="6">
-        <f>D63-D72</f>
+        <f>D67+D68+D69+D70+D71+D72+D73</f>
         <v/>
       </c>
       <c r="E74" s="6">
-        <f>E63-E72</f>
+        <f>E67+E68+E69+E70+E71+E72+E73</f>
         <v/>
       </c>
       <c r="F74" s="6">
-        <f>F63-F72</f>
+        <f>F67+F68+F69+F70+F71+F72+F73</f>
         <v/>
       </c>
       <c r="G74" s="6">
-        <f>G63-G72</f>
+        <f>G67+G68+G69+G70+G71+G72+G73</f>
         <v/>
       </c>
       <c r="H74" s="6">
-        <f>H63-H72</f>
+        <f>H67+H68+H69+H70+H71+H72+H73</f>
         <v/>
       </c>
       <c r="I74" s="6">
-        <f>I63-I72</f>
+        <f>I67+I68+I69+I70+I71+I72+I73</f>
         <v/>
       </c>
       <c r="J74" s="6">
-        <f>J63-J72</f>
+        <f>J67+J68+J69+J70+J71+J72+J73</f>
         <v/>
       </c>
       <c r="K74" s="6">
-        <f>K63-K72</f>
+        <f>K67+K68+K69+K70+K71+K72+K73</f>
         <v/>
       </c>
       <c r="L74" s="6">
-        <f>L63-L72</f>
+        <f>L67+L68+L69+L70+L71+L72+L73</f>
         <v/>
       </c>
       <c r="M74" s="6">
-        <f>M63-M72</f>
+        <f>M67+M68+M69+M70+M71+M72+M73</f>
         <v/>
       </c>
       <c r="N74" s="6">
@@ -3466,109 +3476,168 @@
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B76" s="6">
+        <f>B64-B74</f>
+        <v/>
+      </c>
+      <c r="C76" s="6">
+        <f>C64-C74</f>
+        <v/>
+      </c>
+      <c r="D76" s="6">
+        <f>D64-D74</f>
+        <v/>
+      </c>
+      <c r="E76" s="6">
+        <f>E64-E74</f>
+        <v/>
+      </c>
+      <c r="F76" s="6">
+        <f>F64-F74</f>
+        <v/>
+      </c>
+      <c r="G76" s="6">
+        <f>G64-G74</f>
+        <v/>
+      </c>
+      <c r="H76" s="6">
+        <f>H64-H74</f>
+        <v/>
+      </c>
+      <c r="I76" s="6">
+        <f>I64-I74</f>
+        <v/>
+      </c>
+      <c r="J76" s="6">
+        <f>J64-J74</f>
+        <v/>
+      </c>
+      <c r="K76" s="6">
+        <f>K64-K74</f>
+        <v/>
+      </c>
+      <c r="L76" s="6">
+        <f>L64-L74</f>
+        <v/>
+      </c>
+      <c r="M76" s="6">
+        <f>M64-M74</f>
+        <v/>
+      </c>
+      <c r="N76" s="6">
+        <f>SUM(B76:M76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Кэш (старт €18,000)</t>
         </is>
       </c>
-      <c r="B75">
-        <f>18000+B74</f>
-        <v/>
-      </c>
-      <c r="C75">
-        <f>B75+C74</f>
-        <v/>
-      </c>
-      <c r="D75">
-        <f>C75+D74</f>
-        <v/>
-      </c>
-      <c r="E75">
-        <f>D75+E74</f>
-        <v/>
-      </c>
-      <c r="F75">
-        <f>E75+F74</f>
-        <v/>
-      </c>
-      <c r="G75">
-        <f>F75+G74</f>
-        <v/>
-      </c>
-      <c r="H75">
-        <f>G75+H74</f>
-        <v/>
-      </c>
-      <c r="I75">
-        <f>H75+I74</f>
-        <v/>
-      </c>
-      <c r="J75">
-        <f>I75+J74</f>
-        <v/>
-      </c>
-      <c r="K75">
-        <f>J75+K74</f>
-        <v/>
-      </c>
-      <c r="L75">
-        <f>K75+L74</f>
-        <v/>
-      </c>
-      <c r="M75">
-        <f>L75+M74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B77">
+        <f>18000+B76</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>B77+C76</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>C77+D76</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>D77+E76</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>E77+F76</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>F77+G76</f>
+        <v/>
+      </c>
+      <c r="H77">
+        <f>G77+H76</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>H77+I76</f>
+        <v/>
+      </c>
+      <c r="J77">
+        <f>I77+J76</f>
+        <v/>
+      </c>
+      <c r="K77">
+        <f>J77+K76</f>
+        <v/>
+      </c>
+      <c r="L77">
+        <f>K77+L76</f>
+        <v/>
+      </c>
+      <c r="M77">
+        <f>L77+M76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>ЮНИТ-ЭКОНОМИКА (год)</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CAC на квалифицированного лида, €</t>
-        </is>
-      </c>
-      <c r="B78">
-        <f>ROUND(N6/N53,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B79">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Выручка на агентскую сделку, €</t>
+          <t>CAC на квалифицированного лида, €</t>
         </is>
       </c>
       <c r="B80">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <f>ROUND(N6/N54,0)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>ROUND(N6/N57,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B82">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B81">
-        <f>ROUND(B80/B79,1)</f>
+      <c r="B83">
+        <f>ROUND(B82/B81,1)</f>
         <v/>
       </c>
     </row>
@@ -3583,7 +3652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4185,168 +4254,119 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Продажник: % от выручки агентских сделок</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="8" t="n">
+      <c r="J39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="8" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="L39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N38">
-        <f>SUM(B38:M38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="N39">
+        <f>SUM(B39:M39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F41">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I41">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J41">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K41">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L41">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M41">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N41">
-        <f>SUM(B41:M41)</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Регистрации: комьюнити</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B42">
-        <f>B9</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C42">
-        <f>C9</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D42">
-        <f>D9</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E42">
-        <f>E9</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F42">
-        <f>F9</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G42">
-        <f>G9</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H42">
-        <f>H9</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I42">
-        <f>I9</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J42">
-        <f>J9</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K42">
-        <f>K9</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L42">
-        <f>L9</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M42">
-        <f>M9</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N42">
@@ -4357,55 +4377,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B43">
-        <f>B12*$B$13</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C43">
-        <f>C12*$B$13</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D43">
-        <f>D12*$B$13</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E43">
-        <f>E12*$B$13</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F43">
-        <f>F12*$B$13</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G43">
-        <f>G12*$B$13</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H43">
-        <f>H12*$B$13</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I43">
-        <f>I12*$B$13</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J43">
-        <f>J12*$B$13</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K43">
-        <f>K12*$B$13</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L43">
-        <f>L12*$B$13</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M43">
-        <f>M12*$B$13</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N43">
@@ -4416,55 +4436,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: SEO</t>
         </is>
       </c>
       <c r="B44">
-        <f>B14*$B$15*$B$16</f>
+        <f>B12*$B$13</f>
         <v/>
       </c>
       <c r="C44">
-        <f>C14*$B$15*$B$16</f>
+        <f>C12*$B$13</f>
         <v/>
       </c>
       <c r="D44">
-        <f>D14*$B$15*$B$16</f>
+        <f>D12*$B$13</f>
         <v/>
       </c>
       <c r="E44">
-        <f>E14*$B$15*$B$16</f>
+        <f>E12*$B$13</f>
         <v/>
       </c>
       <c r="F44">
-        <f>F14*$B$15*$B$16</f>
+        <f>F12*$B$13</f>
         <v/>
       </c>
       <c r="G44">
-        <f>G14*$B$15*$B$16</f>
+        <f>G12*$B$13</f>
         <v/>
       </c>
       <c r="H44">
-        <f>H14*$B$15*$B$16</f>
+        <f>H12*$B$13</f>
         <v/>
       </c>
       <c r="I44">
-        <f>I14*$B$15*$B$16</f>
+        <f>I12*$B$13</f>
         <v/>
       </c>
       <c r="J44">
-        <f>J14*$B$15*$B$16</f>
+        <f>J12*$B$13</f>
         <v/>
       </c>
       <c r="K44">
-        <f>K14*$B$15*$B$16</f>
+        <f>K12*$B$13</f>
         <v/>
       </c>
       <c r="L44">
-        <f>L14*$B$15*$B$16</f>
+        <f>L12*$B$13</f>
         <v/>
       </c>
       <c r="M44">
-        <f>M14*$B$15*$B$16</f>
+        <f>M12*$B$13</f>
         <v/>
       </c>
       <c r="N44">
@@ -4475,55 +4495,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: агентства</t>
         </is>
       </c>
       <c r="B45">
-        <f>B10*$B$11</f>
+        <f>B14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="C45">
-        <f>C10*$B$11</f>
+        <f>C14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D10*$B$11</f>
+        <f>D14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E10*$B$11</f>
+        <f>E14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F10*$B$11</f>
+        <f>F14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G10*$B$11</f>
+        <f>G14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H10*$B$11</f>
+        <f>H14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I10*$B$11</f>
+        <f>I14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J10*$B$11</f>
+        <f>J14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K10*$B$11</f>
+        <f>K14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L10*$B$11</f>
+        <f>L14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M10*$B$11</f>
+        <f>M14*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="N45">
@@ -4532,119 +4552,119 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>B10*$B$11</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>C10*$B$11</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>D10*$B$11</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>E10*$B$11</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>F10*$B$11</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>G10*$B$11</f>
+        <v/>
+      </c>
+      <c r="H46">
+        <f>H10*$B$11</f>
+        <v/>
+      </c>
+      <c r="I46">
+        <f>I10*$B$11</f>
+        <v/>
+      </c>
+      <c r="J46">
+        <f>J10*$B$11</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>K10*$B$11</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>L10*$B$11</f>
+        <v/>
+      </c>
+      <c r="M46">
+        <f>M10*$B$11</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>SUM(B46:M46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Итого регистраций</t>
         </is>
       </c>
-      <c r="B46" s="6">
-        <f>B41+B42+B43+B44+B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>C41+C42+C43+C44+C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="6">
-        <f>D41+D42+D43+D44+D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="6">
-        <f>E41+E42+E43+E44+E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="6">
-        <f>F41+F42+F43+F44+F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="6">
-        <f>G41+G42+G43+G44+G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="6">
-        <f>H41+H42+H43+H44+H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>I41+I42+I43+I44+I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>J41+J42+J43+J44+J45</f>
-        <v/>
-      </c>
-      <c r="K46" s="6">
-        <f>K41+K42+K43+K44+K45</f>
-        <v/>
-      </c>
-      <c r="L46" s="6">
-        <f>L41+L42+L43+L44+L45</f>
-        <v/>
-      </c>
-      <c r="M46" s="6">
-        <f>M41+M42+M43+M44+M45</f>
-        <v/>
-      </c>
-      <c r="N46" s="6">
-        <f>SUM(B46:M46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Квалифицировано: paid</t>
-        </is>
-      </c>
-      <c r="B47">
-        <f>B41*$B$20</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>C41*$B$20</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>D41*$B$20</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>E41*$B$20</f>
-        <v/>
-      </c>
-      <c r="F47">
-        <f>F41*$B$20</f>
-        <v/>
-      </c>
-      <c r="G47">
-        <f>G41*$B$20</f>
-        <v/>
-      </c>
-      <c r="H47">
-        <f>H41*$B$20</f>
-        <v/>
-      </c>
-      <c r="I47">
-        <f>I41*$B$20</f>
-        <v/>
-      </c>
-      <c r="J47">
-        <f>J41*$B$20</f>
-        <v/>
-      </c>
-      <c r="K47">
-        <f>K41*$B$20</f>
-        <v/>
-      </c>
-      <c r="L47">
-        <f>L41*$B$20</f>
-        <v/>
-      </c>
-      <c r="M47">
-        <f>M41*$B$20</f>
-        <v/>
-      </c>
-      <c r="N47">
+      <c r="B47" s="6">
+        <f>B42+B43+B44+B45+B46</f>
+        <v/>
+      </c>
+      <c r="C47" s="6">
+        <f>C42+C43+C44+C45+C46</f>
+        <v/>
+      </c>
+      <c r="D47" s="6">
+        <f>D42+D43+D44+D45+D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="6">
+        <f>E42+E43+E44+E45+E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="6">
+        <f>F42+F43+F44+F45+F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="6">
+        <f>G42+G43+G44+G45+G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="6">
+        <f>H42+H43+H44+H45+H46</f>
+        <v/>
+      </c>
+      <c r="I47" s="6">
+        <f>I42+I43+I44+I45+I46</f>
+        <v/>
+      </c>
+      <c r="J47" s="6">
+        <f>J42+J43+J44+J45+J46</f>
+        <v/>
+      </c>
+      <c r="K47" s="6">
+        <f>K42+K43+K44+K45+K46</f>
+        <v/>
+      </c>
+      <c r="L47" s="6">
+        <f>L42+L43+L44+L45+L46</f>
+        <v/>
+      </c>
+      <c r="M47" s="6">
+        <f>M42+M43+M44+M45+M46</f>
+        <v/>
+      </c>
+      <c r="N47" s="6">
         <f>SUM(B47:M47)</f>
         <v/>
       </c>
@@ -4652,55 +4672,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Квалифицировано: комьюнити</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B48">
-        <f>B42*$B$21</f>
+        <f>B42*$B$20</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C42*$B$21</f>
+        <f>C42*$B$20</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D42*$B$21</f>
+        <f>D42*$B$20</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E42*$B$21</f>
+        <f>E42*$B$20</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F42*$B$21</f>
+        <f>F42*$B$20</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G42*$B$21</f>
+        <f>G42*$B$20</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H42*$B$21</f>
+        <f>H42*$B$20</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I42*$B$21</f>
+        <f>I42*$B$20</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J42*$B$21</f>
+        <f>J42*$B$20</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K42*$B$21</f>
+        <f>K42*$B$20</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L42*$B$21</f>
+        <f>L42*$B$20</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M42*$B$21</f>
+        <f>M42*$B$20</f>
         <v/>
       </c>
       <c r="N48">
@@ -4711,55 +4731,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Квалифицировано: SEO</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B49">
-        <f>B43*$B$23</f>
+        <f>B43*$B$21</f>
         <v/>
       </c>
       <c r="C49">
-        <f>C43*$B$23</f>
+        <f>C43*$B$21</f>
         <v/>
       </c>
       <c r="D49">
-        <f>D43*$B$23</f>
+        <f>D43*$B$21</f>
         <v/>
       </c>
       <c r="E49">
-        <f>E43*$B$23</f>
+        <f>E43*$B$21</f>
         <v/>
       </c>
       <c r="F49">
-        <f>F43*$B$23</f>
+        <f>F43*$B$21</f>
         <v/>
       </c>
       <c r="G49">
-        <f>G43*$B$23</f>
+        <f>G43*$B$21</f>
         <v/>
       </c>
       <c r="H49">
-        <f>H43*$B$23</f>
+        <f>H43*$B$21</f>
         <v/>
       </c>
       <c r="I49">
-        <f>I43*$B$23</f>
+        <f>I43*$B$21</f>
         <v/>
       </c>
       <c r="J49">
-        <f>J43*$B$23</f>
+        <f>J43*$B$21</f>
         <v/>
       </c>
       <c r="K49">
-        <f>K43*$B$23</f>
+        <f>K43*$B$21</f>
         <v/>
       </c>
       <c r="L49">
-        <f>L43*$B$23</f>
+        <f>L43*$B$21</f>
         <v/>
       </c>
       <c r="M49">
-        <f>M43*$B$23</f>
+        <f>M43*$B$21</f>
         <v/>
       </c>
       <c r="N49">
@@ -4770,55 +4790,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: SEO</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$25</f>
+        <f>B44*$B$23</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$25</f>
+        <f>C44*$B$23</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$25</f>
+        <f>D44*$B$23</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$25</f>
+        <f>E44*$B$23</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$25</f>
+        <f>F44*$B$23</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$25</f>
+        <f>G44*$B$23</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$25</f>
+        <f>H44*$B$23</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$25</f>
+        <f>I44*$B$23</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$25</f>
+        <f>J44*$B$23</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$25</f>
+        <f>K44*$B$23</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$25</f>
+        <f>L44*$B$23</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$25</f>
+        <f>M44*$B$23</f>
         <v/>
       </c>
       <c r="N50">
@@ -4829,55 +4849,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: агентства</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$22</f>
+        <f>B45*$B$25</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$22</f>
+        <f>C45*$B$25</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$22</f>
+        <f>D45*$B$25</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$22</f>
+        <f>E45*$B$25</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$22</f>
+        <f>F45*$B$25</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$22</f>
+        <f>G45*$B$25</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$22</f>
+        <f>H45*$B$25</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$22</f>
+        <f>I45*$B$25</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$22</f>
+        <f>J45*$B$25</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$22</f>
+        <f>K45*$B$25</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$22</f>
+        <f>L45*$B$25</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$22</f>
+        <f>M45*$B$25</f>
         <v/>
       </c>
       <c r="N51">
@@ -4888,54 +4908,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
+          <t>Квалифицировано: партнёры</t>
+        </is>
+      </c>
+      <c r="B52">
+        <f>B46*$B$22</f>
+        <v/>
       </c>
       <c r="C52">
-        <f>B56*$B$17*$B$24</f>
+        <f>C46*$B$22</f>
         <v/>
       </c>
       <c r="D52">
-        <f>C56*$B$17*$B$24</f>
+        <f>D46*$B$22</f>
         <v/>
       </c>
       <c r="E52">
-        <f>D56*$B$17*$B$24</f>
+        <f>E46*$B$22</f>
         <v/>
       </c>
       <c r="F52">
-        <f>E56*$B$17*$B$24</f>
+        <f>F46*$B$22</f>
         <v/>
       </c>
       <c r="G52">
-        <f>F56*$B$17*$B$24</f>
+        <f>G46*$B$22</f>
         <v/>
       </c>
       <c r="H52">
-        <f>G56*$B$17*$B$24</f>
+        <f>H46*$B$22</f>
         <v/>
       </c>
       <c r="I52">
-        <f>H56*$B$17*$B$24</f>
+        <f>I46*$B$22</f>
         <v/>
       </c>
       <c r="J52">
-        <f>I56*$B$17*$B$24</f>
+        <f>J46*$B$22</f>
         <v/>
       </c>
       <c r="K52">
-        <f>J56*$B$17*$B$24</f>
+        <f>K46*$B$22</f>
         <v/>
       </c>
       <c r="L52">
-        <f>K56*$B$17*$B$24</f>
+        <f>L46*$B$22</f>
         <v/>
       </c>
       <c r="M52">
-        <f>L56*$B$17*$B$24</f>
+        <f>M46*$B$22</f>
         <v/>
       </c>
       <c r="N52">
@@ -4944,119 +4965,118 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <f>B57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>C57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>D57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>E57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="H53">
+        <f>G57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="I53">
+        <f>H57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="J53">
+        <f>I57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="K53">
+        <f>J57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="L53">
+        <f>K57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="M53">
+        <f>L57*$B$17*$B$24</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>SUM(B53:M53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Итого квалифицированных</t>
         </is>
       </c>
-      <c r="B53" s="6">
-        <f>B47+B48+B49+B50+B51+B52</f>
-        <v/>
-      </c>
-      <c r="C53" s="6">
-        <f>C47+C48+C49+C50+C51+C52</f>
-        <v/>
-      </c>
-      <c r="D53" s="6">
-        <f>D47+D48+D49+D50+D51+D52</f>
-        <v/>
-      </c>
-      <c r="E53" s="6">
-        <f>E47+E48+E49+E50+E51+E52</f>
-        <v/>
-      </c>
-      <c r="F53" s="6">
-        <f>F47+F48+F49+F50+F51+F52</f>
-        <v/>
-      </c>
-      <c r="G53" s="6">
-        <f>G47+G48+G49+G50+G51+G52</f>
-        <v/>
-      </c>
-      <c r="H53" s="6">
-        <f>H47+H48+H49+H50+H51+H52</f>
-        <v/>
-      </c>
-      <c r="I53" s="6">
-        <f>I47+I48+I49+I50+I51+I52</f>
-        <v/>
-      </c>
-      <c r="J53" s="6">
-        <f>J47+J48+J49+J50+J51+J52</f>
-        <v/>
-      </c>
-      <c r="K53" s="6">
-        <f>K47+K48+K49+K50+K51+K52</f>
-        <v/>
-      </c>
-      <c r="L53" s="6">
-        <f>L47+L48+L49+L50+L51+L52</f>
-        <v/>
-      </c>
-      <c r="M53" s="6">
-        <f>M47+M48+M49+M50+M51+M52</f>
-        <v/>
-      </c>
-      <c r="N53" s="6">
-        <f>SUM(B53:M53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Сделки через агентства</t>
-        </is>
-      </c>
-      <c r="B54">
-        <f>ROUND(MIN(B53*$B$28,B14*B30),0)</f>
-        <v/>
-      </c>
-      <c r="C54">
-        <f>ROUND(MIN(C53*$B$28,C14*C30),0)</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>ROUND(MIN(D53*$B$28,D14*D30),0)</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>ROUND(MIN(E53*$B$28,E14*E30),0)</f>
-        <v/>
-      </c>
-      <c r="F54">
-        <f>ROUND(MIN(F53*$B$28,F14*F30),0)</f>
-        <v/>
-      </c>
-      <c r="G54">
-        <f>ROUND(MIN(G53*$B$28,G14*G30),0)</f>
-        <v/>
-      </c>
-      <c r="H54">
-        <f>ROUND(MIN(H53*$B$28,H14*H30),0)</f>
-        <v/>
-      </c>
-      <c r="I54">
-        <f>ROUND(MIN(I53*$B$28,I14*I30),0)</f>
-        <v/>
-      </c>
-      <c r="J54">
-        <f>ROUND(MIN(J53*$B$28,J14*J30),0)</f>
-        <v/>
-      </c>
-      <c r="K54">
-        <f>ROUND(MIN(K53*$B$28,K14*K30),0)</f>
-        <v/>
-      </c>
-      <c r="L54">
-        <f>ROUND(MIN(L53*$B$28,L14*L30),0)</f>
-        <v/>
-      </c>
-      <c r="M54">
-        <f>ROUND(MIN(M53*$B$28,M14*M30),0)</f>
-        <v/>
-      </c>
-      <c r="N54">
+      <c r="B54" s="6">
+        <f>B48+B49+B50+B51+B52+B53</f>
+        <v/>
+      </c>
+      <c r="C54" s="6">
+        <f>C48+C49+C50+C51+C52+C53</f>
+        <v/>
+      </c>
+      <c r="D54" s="6">
+        <f>D48+D49+D50+D51+D52+D53</f>
+        <v/>
+      </c>
+      <c r="E54" s="6">
+        <f>E48+E49+E50+E51+E52+E53</f>
+        <v/>
+      </c>
+      <c r="F54" s="6">
+        <f>F48+F49+F50+F51+F52+F53</f>
+        <v/>
+      </c>
+      <c r="G54" s="6">
+        <f>G48+G49+G50+G51+G52+G53</f>
+        <v/>
+      </c>
+      <c r="H54" s="6">
+        <f>H48+H49+H50+H51+H52+H53</f>
+        <v/>
+      </c>
+      <c r="I54" s="6">
+        <f>I48+I49+I50+I51+I52+I53</f>
+        <v/>
+      </c>
+      <c r="J54" s="6">
+        <f>J48+J49+J50+J51+J52+J53</f>
+        <v/>
+      </c>
+      <c r="K54" s="6">
+        <f>K48+K49+K50+K51+K52+K53</f>
+        <v/>
+      </c>
+      <c r="L54" s="6">
+        <f>L48+L49+L50+L51+L52+L53</f>
+        <v/>
+      </c>
+      <c r="M54" s="6">
+        <f>M48+M49+M50+M51+M52+M53</f>
+        <v/>
+      </c>
+      <c r="N54" s="6">
         <f>SUM(B54:M54)</f>
         <v/>
       </c>
@@ -5064,55 +5084,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Сделки на каталоге IS24</t>
+          <t>Сделки через агентства</t>
         </is>
       </c>
       <c r="B55">
-        <f>ROUND(B53*$B$29,0)</f>
+        <f>ROUND(MIN(B54*$B$28,B14*B30),0)</f>
         <v/>
       </c>
       <c r="C55">
-        <f>ROUND(C53*$B$29,0)</f>
+        <f>ROUND(MIN(C54*$B$28,C14*C30),0)</f>
         <v/>
       </c>
       <c r="D55">
-        <f>ROUND(D53*$B$29,0)</f>
+        <f>ROUND(MIN(D54*$B$28,D14*D30),0)</f>
         <v/>
       </c>
       <c r="E55">
-        <f>ROUND(E53*$B$29,0)</f>
+        <f>ROUND(MIN(E54*$B$28,E14*E30),0)</f>
         <v/>
       </c>
       <c r="F55">
-        <f>ROUND(F53*$B$29,0)</f>
+        <f>ROUND(MIN(F54*$B$28,F14*F30),0)</f>
         <v/>
       </c>
       <c r="G55">
-        <f>ROUND(G53*$B$29,0)</f>
+        <f>ROUND(MIN(G54*$B$28,G14*G30),0)</f>
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(H53*$B$29,0)</f>
+        <f>ROUND(MIN(H54*$B$28,H14*H30),0)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(I53*$B$29,0)</f>
+        <f>ROUND(MIN(I54*$B$28,I14*I30),0)</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(J53*$B$29,0)</f>
+        <f>ROUND(MIN(J54*$B$28,J14*J30),0)</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(K53*$B$29,0)</f>
+        <f>ROUND(MIN(K54*$B$28,K14*K30),0)</f>
         <v/>
       </c>
       <c r="L55">
-        <f>ROUND(L53*$B$29,0)</f>
+        <f>ROUND(MIN(L54*$B$28,L14*L30),0)</f>
         <v/>
       </c>
       <c r="M55">
-        <f>ROUND(M53*$B$29,0)</f>
+        <f>ROUND(MIN(M54*$B$28,M14*M30),0)</f>
         <v/>
       </c>
       <c r="N55">
@@ -5121,241 +5141,241 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Сделки на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>ROUND(B54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>ROUND(C54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>ROUND(D54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>ROUND(E54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>ROUND(F54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>ROUND(G54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>ROUND(H54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>ROUND(I54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>ROUND(J54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>ROUND(K54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>ROUND(L54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>ROUND(M54*$B$29,0)</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>SUM(B56:M56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Сделок всего</t>
         </is>
       </c>
-      <c r="B56" s="6">
-        <f>B54+B55</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>C54+C55</f>
-        <v/>
-      </c>
-      <c r="D56" s="6">
-        <f>D54+D55</f>
-        <v/>
-      </c>
-      <c r="E56" s="6">
-        <f>E54+E55</f>
-        <v/>
-      </c>
-      <c r="F56" s="6">
-        <f>F54+F55</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G54+G55</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H54+H55</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I54+I55</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J54+J55</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K54+K55</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L54+L55</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M54+M55</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>SUM(B56:M56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B57" s="6">
+        <f>B55+B56</f>
+        <v/>
+      </c>
+      <c r="C57" s="6">
+        <f>C55+C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="6">
+        <f>D55+D56</f>
+        <v/>
+      </c>
+      <c r="E57" s="6">
+        <f>E55+E56</f>
+        <v/>
+      </c>
+      <c r="F57" s="6">
+        <f>F55+F56</f>
+        <v/>
+      </c>
+      <c r="G57" s="6">
+        <f>G55+G56</f>
+        <v/>
+      </c>
+      <c r="H57" s="6">
+        <f>H55+H56</f>
+        <v/>
+      </c>
+      <c r="I57" s="6">
+        <f>I55+I56</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>J55+J56</f>
+        <v/>
+      </c>
+      <c r="K57" s="6">
+        <f>K55+K56</f>
+        <v/>
+      </c>
+      <c r="L57" s="6">
+        <f>L55+L56</f>
+        <v/>
+      </c>
+      <c r="M57" s="6">
+        <f>M55+M56</f>
+        <v/>
+      </c>
+      <c r="N57" s="6">
+        <f>SUM(B57:M57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Сделок с B2C fee</t>
         </is>
       </c>
-      <c r="B57">
-        <f>B55+ROUND(B54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>C55+ROUND(C54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>D55+ROUND(D54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>E55+ROUND(E54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>F55+ROUND(F54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="G57">
-        <f>G55+ROUND(G54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>H55+ROUND(H54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="I57">
-        <f>I55+ROUND(I54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="J57">
-        <f>J55+ROUND(J54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="K57">
-        <f>K55+ROUND(K54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="L57">
-        <f>L55+ROUND(L54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="M57">
-        <f>M55+ROUND(M54*$B$37,0)</f>
-        <v/>
-      </c>
-      <c r="N57">
-        <f>SUM(B57:M57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B58">
+        <f>B56+ROUND(B55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>C56+ROUND(C55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>D56+ROUND(D55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>E56+ROUND(E55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>F56+ROUND(F55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>G56+ROUND(G55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>H56+ROUND(H55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>I56+ROUND(I55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>J56+ROUND(J55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>K56+ROUND(K55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>L56+ROUND(L55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>M56+ROUND(M55*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>SUM(B58:M58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>ВЫРУЧКА</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
-        </is>
-      </c>
-      <c r="B60">
-        <f>ROUND(B54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>ROUND(C54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>ROUND(D54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>ROUND(E54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="F60">
-        <f>ROUND(F54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>ROUND(G54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="H60">
-        <f>ROUND(H54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="I60">
-        <f>ROUND(I54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="J60">
-        <f>ROUND(J54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="K60">
-        <f>ROUND(K54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="L60">
-        <f>ROUND(L54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="M60">
-        <f>ROUND(M54*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="N60">
-        <f>SUM(B60:M60)</f>
-        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R3: B2C fee</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B61">
-        <f>B57*$B$36</f>
+        <f>ROUND(B55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="C61">
-        <f>C57*$B$36</f>
+        <f>ROUND(C55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="D61">
-        <f>D57*$B$36</f>
+        <f>ROUND(D55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="E61">
-        <f>E57*$B$36</f>
+        <f>ROUND(E55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>F57*$B$36</f>
+        <f>ROUND(F55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>G57*$B$36</f>
+        <f>ROUND(G55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>H57*$B$36</f>
+        <f>ROUND(H55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>I57*$B$36</f>
+        <f>ROUND(I55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="J61">
-        <f>J57*$B$36</f>
+        <f>ROUND(J55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>K57*$B$36</f>
+        <f>ROUND(K55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="L61">
-        <f>L57*$B$36</f>
+        <f>ROUND(L55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="M61">
-        <f>M57*$B$36</f>
+        <f>ROUND(M55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="N61">
@@ -5366,55 +5386,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R4: upsell</t>
+          <t>R3: B2C fee</t>
         </is>
       </c>
       <c r="B62">
-        <f>B38</f>
+        <f>B58*$B$36</f>
         <v/>
       </c>
       <c r="C62">
-        <f>C38</f>
+        <f>C58*$B$36</f>
         <v/>
       </c>
       <c r="D62">
-        <f>D38</f>
+        <f>D58*$B$36</f>
         <v/>
       </c>
       <c r="E62">
-        <f>E38</f>
+        <f>E58*$B$36</f>
         <v/>
       </c>
       <c r="F62">
-        <f>F38</f>
+        <f>F58*$B$36</f>
         <v/>
       </c>
       <c r="G62">
-        <f>G38</f>
+        <f>G58*$B$36</f>
         <v/>
       </c>
       <c r="H62">
-        <f>H38</f>
+        <f>H58*$B$36</f>
         <v/>
       </c>
       <c r="I62">
-        <f>I38</f>
+        <f>I58*$B$36</f>
         <v/>
       </c>
       <c r="J62">
-        <f>J38</f>
+        <f>J58*$B$36</f>
         <v/>
       </c>
       <c r="K62">
-        <f>K38</f>
+        <f>K58*$B$36</f>
         <v/>
       </c>
       <c r="L62">
-        <f>L38</f>
+        <f>L58*$B$36</f>
         <v/>
       </c>
       <c r="M62">
-        <f>M38</f>
+        <f>M58*$B$36</f>
         <v/>
       </c>
       <c r="N62">
@@ -5423,171 +5443,183 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B63">
+        <f>B39</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>C39</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>D39</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>G39</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>H39</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>I39</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>J39</f>
+        <v/>
+      </c>
+      <c r="K63">
+        <f>K39</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>L39</f>
+        <v/>
+      </c>
+      <c r="M63">
+        <f>M39</f>
+        <v/>
+      </c>
+      <c r="N63">
+        <f>SUM(B63:M63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B63" s="6">
-        <f>B60+B61+B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="6">
-        <f>C60+C61+C62</f>
-        <v/>
-      </c>
-      <c r="D63" s="6">
-        <f>D60+D61+D62</f>
-        <v/>
-      </c>
-      <c r="E63" s="6">
-        <f>E60+E61+E62</f>
-        <v/>
-      </c>
-      <c r="F63" s="6">
-        <f>F60+F61+F62</f>
-        <v/>
-      </c>
-      <c r="G63" s="6">
-        <f>G60+G61+G62</f>
-        <v/>
-      </c>
-      <c r="H63" s="6">
-        <f>H60+H61+H62</f>
-        <v/>
-      </c>
-      <c r="I63" s="6">
-        <f>I60+I61+I62</f>
-        <v/>
-      </c>
-      <c r="J63" s="6">
-        <f>J60+J61+J62</f>
-        <v/>
-      </c>
-      <c r="K63" s="6">
-        <f>K60+K61+K62</f>
-        <v/>
-      </c>
-      <c r="L63" s="6">
-        <f>L60+L61+L62</f>
-        <v/>
-      </c>
-      <c r="M63" s="6">
-        <f>M60+M61+M62</f>
-        <v/>
-      </c>
-      <c r="N63" s="6">
-        <f>SUM(B63:M63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="B64" s="6">
+        <f>B61+B62+B63</f>
+        <v/>
+      </c>
+      <c r="C64" s="6">
+        <f>C61+C62+C63</f>
+        <v/>
+      </c>
+      <c r="D64" s="6">
+        <f>D61+D62+D63</f>
+        <v/>
+      </c>
+      <c r="E64" s="6">
+        <f>E61+E62+E63</f>
+        <v/>
+      </c>
+      <c r="F64" s="6">
+        <f>F61+F62+F63</f>
+        <v/>
+      </c>
+      <c r="G64" s="6">
+        <f>G61+G62+G63</f>
+        <v/>
+      </c>
+      <c r="H64" s="6">
+        <f>H61+H62+H63</f>
+        <v/>
+      </c>
+      <c r="I64" s="6">
+        <f>I61+I62+I63</f>
+        <v/>
+      </c>
+      <c r="J64" s="6">
+        <f>J61+J62+J63</f>
+        <v/>
+      </c>
+      <c r="K64" s="6">
+        <f>K61+K62+K63</f>
+        <v/>
+      </c>
+      <c r="L64" s="6">
+        <f>L61+L62+L63</f>
+        <v/>
+      </c>
+      <c r="M64" s="6">
+        <f>M61+M62+M63</f>
+        <v/>
+      </c>
+      <c r="N64" s="6">
+        <f>SUM(B64:M64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B66">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C66">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D66">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E66">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F66">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G66">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H66">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I66">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J66">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K66">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L66">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M66">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N66">
-        <f>SUM(B66:M66)</f>
-        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M67" s="8" t="n">
-        <v>500</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M67">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N67">
         <f>SUM(B67:M67)</f>
@@ -5597,44 +5629,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BD: агентства + партнёрства + комьюнити</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="C68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="M68" s="8" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="N68">
         <f>SUM(B68:M68)</f>
@@ -5644,44 +5676,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>3000</v>
+        <v>1073</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3000</v>
+        <v>1145</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3500</v>
+        <v>1218</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>3500</v>
+        <v>1291</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>3500</v>
+        <v>1364</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>4000</v>
+        <v>1436</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>4000</v>
+        <v>1509</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>4000</v>
+        <v>1582</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>4500</v>
+        <v>1655</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>4500</v>
+        <v>1727</v>
       </c>
       <c r="M69" s="8" t="n">
-        <v>4500</v>
+        <v>1800</v>
       </c>
       <c r="N69">
         <f>SUM(B69:M69)</f>
@@ -5691,44 +5723,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Команда: dev / support (контракторы)</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="C70" s="8" t="n">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>850</v>
+        <v>3500</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>900</v>
+        <v>3500</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>950</v>
+        <v>3500</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>1050</v>
+        <v>4000</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>1150</v>
+        <v>4500</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>1200</v>
+        <v>4500</v>
       </c>
       <c r="M70" s="8" t="n">
-        <v>1250</v>
+        <v>4500</v>
       </c>
       <c r="N70">
         <f>SUM(B70:M70)</f>
@@ -5738,44 +5770,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Инфраструктура + AI API</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="N71">
         <f>SUM(B71:M71)</f>
@@ -5783,116 +5815,163 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="B72" s="6">
-        <f>B66+B67+B68+B69+B70+B71</f>
-        <v/>
-      </c>
-      <c r="C72" s="6">
-        <f>C66+C67+C68+C69+C70+C71</f>
-        <v/>
-      </c>
-      <c r="D72" s="6">
-        <f>D66+D67+D68+D69+D70+D71</f>
-        <v/>
-      </c>
-      <c r="E72" s="6">
-        <f>E66+E67+E68+E69+E70+E71</f>
-        <v/>
-      </c>
-      <c r="F72" s="6">
-        <f>F66+F67+F68+F69+F70+F71</f>
-        <v/>
-      </c>
-      <c r="G72" s="6">
-        <f>G66+G67+G68+G69+G70+G71</f>
-        <v/>
-      </c>
-      <c r="H72" s="6">
-        <f>H66+H67+H68+H69+H70+H71</f>
-        <v/>
-      </c>
-      <c r="I72" s="6">
-        <f>I66+I67+I68+I69+I70+I71</f>
-        <v/>
-      </c>
-      <c r="J72" s="6">
-        <f>J66+J67+J68+J69+J70+J71</f>
-        <v/>
-      </c>
-      <c r="K72" s="6">
-        <f>K66+K67+K68+K69+K70+K71</f>
-        <v/>
-      </c>
-      <c r="L72" s="6">
-        <f>L66+L67+L68+L69+L70+L71</f>
-        <v/>
-      </c>
-      <c r="M72" s="6">
-        <f>M66+M67+M68+M69+M70+M71</f>
-        <v/>
-      </c>
-      <c r="N72" s="6">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N72">
         <f>SUM(B72:M72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>ROUND(B61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>ROUND(C61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>ROUND(D61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>ROUND(E61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>ROUND(F61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>ROUND(G61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>ROUND(H61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>ROUND(I61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>ROUND(J61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>ROUND(K61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>ROUND(L61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M73">
+        <f>ROUND(M61*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N73">
+        <f>SUM(B73:M73)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>TOTAL COSTS</t>
         </is>
       </c>
       <c r="B74" s="6">
-        <f>B63-B72</f>
+        <f>B67+B68+B69+B70+B71+B72+B73</f>
         <v/>
       </c>
       <c r="C74" s="6">
-        <f>C63-C72</f>
+        <f>C67+C68+C69+C70+C71+C72+C73</f>
         <v/>
       </c>
       <c r="D74" s="6">
-        <f>D63-D72</f>
+        <f>D67+D68+D69+D70+D71+D72+D73</f>
         <v/>
       </c>
       <c r="E74" s="6">
-        <f>E63-E72</f>
+        <f>E67+E68+E69+E70+E71+E72+E73</f>
         <v/>
       </c>
       <c r="F74" s="6">
-        <f>F63-F72</f>
+        <f>F67+F68+F69+F70+F71+F72+F73</f>
         <v/>
       </c>
       <c r="G74" s="6">
-        <f>G63-G72</f>
+        <f>G67+G68+G69+G70+G71+G72+G73</f>
         <v/>
       </c>
       <c r="H74" s="6">
-        <f>H63-H72</f>
+        <f>H67+H68+H69+H70+H71+H72+H73</f>
         <v/>
       </c>
       <c r="I74" s="6">
-        <f>I63-I72</f>
+        <f>I67+I68+I69+I70+I71+I72+I73</f>
         <v/>
       </c>
       <c r="J74" s="6">
-        <f>J63-J72</f>
+        <f>J67+J68+J69+J70+J71+J72+J73</f>
         <v/>
       </c>
       <c r="K74" s="6">
-        <f>K63-K72</f>
+        <f>K67+K68+K69+K70+K71+K72+K73</f>
         <v/>
       </c>
       <c r="L74" s="6">
-        <f>L63-L72</f>
+        <f>L67+L68+L69+L70+L71+L72+L73</f>
         <v/>
       </c>
       <c r="M74" s="6">
-        <f>M63-M72</f>
+        <f>M67+M68+M69+M70+M71+M72+M73</f>
         <v/>
       </c>
       <c r="N74" s="6">
@@ -5900,109 +5979,168 @@
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B76" s="6">
+        <f>B64-B74</f>
+        <v/>
+      </c>
+      <c r="C76" s="6">
+        <f>C64-C74</f>
+        <v/>
+      </c>
+      <c r="D76" s="6">
+        <f>D64-D74</f>
+        <v/>
+      </c>
+      <c r="E76" s="6">
+        <f>E64-E74</f>
+        <v/>
+      </c>
+      <c r="F76" s="6">
+        <f>F64-F74</f>
+        <v/>
+      </c>
+      <c r="G76" s="6">
+        <f>G64-G74</f>
+        <v/>
+      </c>
+      <c r="H76" s="6">
+        <f>H64-H74</f>
+        <v/>
+      </c>
+      <c r="I76" s="6">
+        <f>I64-I74</f>
+        <v/>
+      </c>
+      <c r="J76" s="6">
+        <f>J64-J74</f>
+        <v/>
+      </c>
+      <c r="K76" s="6">
+        <f>K64-K74</f>
+        <v/>
+      </c>
+      <c r="L76" s="6">
+        <f>L64-L74</f>
+        <v/>
+      </c>
+      <c r="M76" s="6">
+        <f>M64-M74</f>
+        <v/>
+      </c>
+      <c r="N76" s="6">
+        <f>SUM(B76:M76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Кэш (старт €18,000)</t>
         </is>
       </c>
-      <c r="B75">
-        <f>18000+B74</f>
-        <v/>
-      </c>
-      <c r="C75">
-        <f>B75+C74</f>
-        <v/>
-      </c>
-      <c r="D75">
-        <f>C75+D74</f>
-        <v/>
-      </c>
-      <c r="E75">
-        <f>D75+E74</f>
-        <v/>
-      </c>
-      <c r="F75">
-        <f>E75+F74</f>
-        <v/>
-      </c>
-      <c r="G75">
-        <f>F75+G74</f>
-        <v/>
-      </c>
-      <c r="H75">
-        <f>G75+H74</f>
-        <v/>
-      </c>
-      <c r="I75">
-        <f>H75+I74</f>
-        <v/>
-      </c>
-      <c r="J75">
-        <f>I75+J74</f>
-        <v/>
-      </c>
-      <c r="K75">
-        <f>J75+K74</f>
-        <v/>
-      </c>
-      <c r="L75">
-        <f>K75+L74</f>
-        <v/>
-      </c>
-      <c r="M75">
-        <f>L75+M74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B77">
+        <f>18000+B76</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>B77+C76</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>C77+D76</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>D77+E76</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>E77+F76</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>F77+G76</f>
+        <v/>
+      </c>
+      <c r="H77">
+        <f>G77+H76</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>H77+I76</f>
+        <v/>
+      </c>
+      <c r="J77">
+        <f>I77+J76</f>
+        <v/>
+      </c>
+      <c r="K77">
+        <f>J77+K76</f>
+        <v/>
+      </c>
+      <c r="L77">
+        <f>K77+L76</f>
+        <v/>
+      </c>
+      <c r="M77">
+        <f>L77+M76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>ЮНИТ-ЭКОНОМИКА (год)</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CAC на квалифицированного лида, €</t>
-        </is>
-      </c>
-      <c r="B78">
-        <f>ROUND(N6/N53,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B79">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Выручка на агентскую сделку, €</t>
+          <t>CAC на квалифицированного лида, €</t>
         </is>
       </c>
       <c r="B80">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <f>ROUND(N6/N54,0)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>ROUND(N6/N57,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B82">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B81">
-        <f>ROUND(B80/B79,1)</f>
+      <c r="B83">
+        <f>ROUND(B82/B81,1)</f>
         <v/>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -586,12 +586,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEO на каталоге IS24/Immowelt</t>
+          <t>SEO: гео-страницы на базе каталога</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 40%] Страницы район × комнаты × бюджет, DE + EN. Каталог IS24 — для полноты и трафика, не для сделок: туда доходят остатки, не разобранные внутри CRM агентств.</t>
+          <t>[квалификация 40%] Программные страницы район × комнаты × бюджет (DE + EN) на данных парсинга IS24/Immowelt — это как человек нас находит через поиск, а не то, что он снимет. Внутри у него доступ и к каталогу, и к эксклюзивам агентств — сам каталог для сделок слабый (остатки, не разобранные в CRM), но именно поэтому большинство таких лидов закрывается через эксклюзив, а не через объявление, которое их привело.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEO на каталоге IS24/Immowelt</t>
+          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -4097,7 +4097,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEO на каталоге IS24/Immowelt</t>
+          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1761,227 +1761,129 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Zolak: средний чек мебели, €</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Zolak: наша доля от мебели</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I41" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="J41" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="K39" s="8" t="n">
+      <c r="K41" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L41" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M41" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="N39">
-        <f>SUM(B39:M39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="N41">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B42">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C42">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F42">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I42">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J42">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K42">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L42">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M42">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N42">
-        <f>SUM(B42:M42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Регистрации: комьюнити</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>E9</f>
-        <v/>
-      </c>
-      <c r="F43">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="G43">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="I43">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="J43">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="K43">
-        <f>K9</f>
-        <v/>
-      </c>
-      <c r="L43">
-        <f>L9</f>
-        <v/>
-      </c>
-      <c r="M43">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N43">
-        <f>SUM(B43:M43)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B44">
-        <f>B12*$B$13</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C44">
-        <f>C12*$B$13</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D44">
-        <f>D12*$B$13</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E44">
-        <f>E12*$B$13</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F44">
-        <f>F12*$B$13</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G44">
-        <f>G12*$B$13</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H44">
-        <f>H12*$B$13</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I44">
-        <f>I12*$B$13</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J44">
-        <f>J12*$B$13</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K44">
-        <f>K12*$B$13</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L44">
-        <f>L12*$B$13</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M44">
-        <f>M12*$B$13</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N44">
@@ -1992,55 +1894,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B45">
-        <f>B14*$B$15*$B$16</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C45">
-        <f>C14*$B$15*$B$16</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D14*$B$15*$B$16</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E14*$B$15*$B$16</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F14*$B$15*$B$16</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G14*$B$15*$B$16</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H14*$B$15*$B$16</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I14*$B$15*$B$16</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J14*$B$15*$B$16</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K14*$B$15*$B$16</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L14*$B$15*$B$16</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M14*$B$15*$B$16</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N45">
@@ -2051,55 +1953,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: SEO</t>
         </is>
       </c>
       <c r="B46">
-        <f>B10*$B$11</f>
+        <f>B12*$B$13</f>
         <v/>
       </c>
       <c r="C46">
-        <f>C10*$B$11</f>
+        <f>C12*$B$13</f>
         <v/>
       </c>
       <c r="D46">
-        <f>D10*$B$11</f>
+        <f>D12*$B$13</f>
         <v/>
       </c>
       <c r="E46">
-        <f>E10*$B$11</f>
+        <f>E12*$B$13</f>
         <v/>
       </c>
       <c r="F46">
-        <f>F10*$B$11</f>
+        <f>F12*$B$13</f>
         <v/>
       </c>
       <c r="G46">
-        <f>G10*$B$11</f>
+        <f>G12*$B$13</f>
         <v/>
       </c>
       <c r="H46">
-        <f>H10*$B$11</f>
+        <f>H12*$B$13</f>
         <v/>
       </c>
       <c r="I46">
-        <f>I10*$B$11</f>
+        <f>I12*$B$13</f>
         <v/>
       </c>
       <c r="J46">
-        <f>J10*$B$11</f>
+        <f>J12*$B$13</f>
         <v/>
       </c>
       <c r="K46">
-        <f>K10*$B$11</f>
+        <f>K12*$B$13</f>
         <v/>
       </c>
       <c r="L46">
-        <f>L10*$B$11</f>
+        <f>L12*$B$13</f>
         <v/>
       </c>
       <c r="M46">
-        <f>M10*$B$11</f>
+        <f>M12*$B$13</f>
         <v/>
       </c>
       <c r="N46">
@@ -2108,60 +2010,60 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Итого регистраций</t>
-        </is>
-      </c>
-      <c r="B47" s="6">
-        <f>B42+B43+B44+B45+B46</f>
-        <v/>
-      </c>
-      <c r="C47" s="6">
-        <f>C42+C43+C44+C45+C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="6">
-        <f>D42+D43+D44+D45+D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="6">
-        <f>E42+E43+E44+E45+E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="6">
-        <f>F42+F43+F44+F45+F46</f>
-        <v/>
-      </c>
-      <c r="G47" s="6">
-        <f>G42+G43+G44+G45+G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="6">
-        <f>H42+H43+H44+H45+H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="6">
-        <f>I42+I43+I44+I45+I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="6">
-        <f>J42+J43+J44+J45+J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="6">
-        <f>K42+K43+K44+K45+K46</f>
-        <v/>
-      </c>
-      <c r="L47" s="6">
-        <f>L42+L43+L44+L45+L46</f>
-        <v/>
-      </c>
-      <c r="M47" s="6">
-        <f>M42+M43+M44+M45+M46</f>
-        <v/>
-      </c>
-      <c r="N47" s="6">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Регистрации: агентства</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>B14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>C14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>D14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>E14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>F14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>G14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>H14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="I47">
+        <f>I14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="J47">
+        <f>J14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>K14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>L14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="M47">
+        <f>M14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="N47">
         <f>SUM(B47:M47)</f>
         <v/>
       </c>
@@ -2169,55 +2071,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Квалифицировано: paid</t>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
         </is>
       </c>
       <c r="B48">
-        <f>B42*$B$20</f>
+        <f>B10*$B$11</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C42*$B$20</f>
+        <f>C10*$B$11</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D42*$B$20</f>
+        <f>D10*$B$11</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E42*$B$20</f>
+        <f>E10*$B$11</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F42*$B$20</f>
+        <f>F10*$B$11</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G42*$B$20</f>
+        <f>G10*$B$11</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H42*$B$20</f>
+        <f>H10*$B$11</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I42*$B$20</f>
+        <f>I10*$B$11</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J42*$B$20</f>
+        <f>J10*$B$11</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K42*$B$20</f>
+        <f>K10*$B$11</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L42*$B$20</f>
+        <f>L10*$B$11</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M42*$B$20</f>
+        <f>M10*$B$11</f>
         <v/>
       </c>
       <c r="N48">
@@ -2226,60 +2128,60 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Квалифицировано: комьюнити</t>
-        </is>
-      </c>
-      <c r="B49">
-        <f>B43*$B$21</f>
-        <v/>
-      </c>
-      <c r="C49">
-        <f>C43*$B$21</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>D43*$B$21</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>E43*$B$21</f>
-        <v/>
-      </c>
-      <c r="F49">
-        <f>F43*$B$21</f>
-        <v/>
-      </c>
-      <c r="G49">
-        <f>G43*$B$21</f>
-        <v/>
-      </c>
-      <c r="H49">
-        <f>H43*$B$21</f>
-        <v/>
-      </c>
-      <c r="I49">
-        <f>I43*$B$21</f>
-        <v/>
-      </c>
-      <c r="J49">
-        <f>J43*$B$21</f>
-        <v/>
-      </c>
-      <c r="K49">
-        <f>K43*$B$21</f>
-        <v/>
-      </c>
-      <c r="L49">
-        <f>L43*$B$21</f>
-        <v/>
-      </c>
-      <c r="M49">
-        <f>M43*$B$21</f>
-        <v/>
-      </c>
-      <c r="N49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Итого регистраций</t>
+        </is>
+      </c>
+      <c r="B49" s="6">
+        <f>B44+B45+B46+B47+B48</f>
+        <v/>
+      </c>
+      <c r="C49" s="6">
+        <f>C44+C45+C46+C47+C48</f>
+        <v/>
+      </c>
+      <c r="D49" s="6">
+        <f>D44+D45+D46+D47+D48</f>
+        <v/>
+      </c>
+      <c r="E49" s="6">
+        <f>E44+E45+E46+E47+E48</f>
+        <v/>
+      </c>
+      <c r="F49" s="6">
+        <f>F44+F45+F46+F47+F48</f>
+        <v/>
+      </c>
+      <c r="G49" s="6">
+        <f>G44+G45+G46+G47+G48</f>
+        <v/>
+      </c>
+      <c r="H49" s="6">
+        <f>H44+H45+H46+H47+H48</f>
+        <v/>
+      </c>
+      <c r="I49" s="6">
+        <f>I44+I45+I46+I47+I48</f>
+        <v/>
+      </c>
+      <c r="J49" s="6">
+        <f>J44+J45+J46+J47+J48</f>
+        <v/>
+      </c>
+      <c r="K49" s="6">
+        <f>K44+K45+K46+K47+K48</f>
+        <v/>
+      </c>
+      <c r="L49" s="6">
+        <f>L44+L45+L46+L47+L48</f>
+        <v/>
+      </c>
+      <c r="M49" s="6">
+        <f>M44+M45+M46+M47+M48</f>
+        <v/>
+      </c>
+      <c r="N49" s="6">
         <f>SUM(B49:M49)</f>
         <v/>
       </c>
@@ -2287,55 +2189,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: SEO</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$23</f>
+        <f>B44*$B$20</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$23</f>
+        <f>C44*$B$20</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$23</f>
+        <f>D44*$B$20</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$23</f>
+        <f>E44*$B$20</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$23</f>
+        <f>F44*$B$20</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$23</f>
+        <f>G44*$B$20</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$23</f>
+        <f>H44*$B$20</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$23</f>
+        <f>I44*$B$20</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$23</f>
+        <f>J44*$B$20</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$23</f>
+        <f>K44*$B$20</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$23</f>
+        <f>L44*$B$20</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$23</f>
+        <f>M44*$B$20</f>
         <v/>
       </c>
       <c r="N50">
@@ -2346,55 +2248,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$25</f>
+        <f>B45*$B$21</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$25</f>
+        <f>C45*$B$21</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$25</f>
+        <f>D45*$B$21</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$25</f>
+        <f>E45*$B$21</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$25</f>
+        <f>F45*$B$21</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$25</f>
+        <f>G45*$B$21</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$25</f>
+        <f>H45*$B$21</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$25</f>
+        <f>I45*$B$21</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$25</f>
+        <f>J45*$B$21</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$25</f>
+        <f>K45*$B$21</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$25</f>
+        <f>L45*$B$21</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$25</f>
+        <f>M45*$B$21</f>
         <v/>
       </c>
       <c r="N51">
@@ -2405,55 +2307,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: SEO</t>
         </is>
       </c>
       <c r="B52">
-        <f>B46*$B$22</f>
+        <f>B46*$B$23</f>
         <v/>
       </c>
       <c r="C52">
-        <f>C46*$B$22</f>
+        <f>C46*$B$23</f>
         <v/>
       </c>
       <c r="D52">
-        <f>D46*$B$22</f>
+        <f>D46*$B$23</f>
         <v/>
       </c>
       <c r="E52">
-        <f>E46*$B$22</f>
+        <f>E46*$B$23</f>
         <v/>
       </c>
       <c r="F52">
-        <f>F46*$B$22</f>
+        <f>F46*$B$23</f>
         <v/>
       </c>
       <c r="G52">
-        <f>G46*$B$22</f>
+        <f>G46*$B$23</f>
         <v/>
       </c>
       <c r="H52">
-        <f>H46*$B$22</f>
+        <f>H46*$B$23</f>
         <v/>
       </c>
       <c r="I52">
-        <f>I46*$B$22</f>
+        <f>I46*$B$23</f>
         <v/>
       </c>
       <c r="J52">
-        <f>J46*$B$22</f>
+        <f>J46*$B$23</f>
         <v/>
       </c>
       <c r="K52">
-        <f>K46*$B$22</f>
+        <f>K46*$B$23</f>
         <v/>
       </c>
       <c r="L52">
-        <f>L46*$B$22</f>
+        <f>L46*$B$23</f>
         <v/>
       </c>
       <c r="M52">
-        <f>M46*$B$22</f>
+        <f>M46*$B$23</f>
         <v/>
       </c>
       <c r="N52">
@@ -2464,54 +2366,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
+          <t>Квалифицировано: агентства</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>B47*$B$25</f>
+        <v/>
       </c>
       <c r="C53">
-        <f>B57*$B$17*$B$24</f>
+        <f>C47*$B$25</f>
         <v/>
       </c>
       <c r="D53">
-        <f>C57*$B$17*$B$24</f>
+        <f>D47*$B$25</f>
         <v/>
       </c>
       <c r="E53">
-        <f>D57*$B$17*$B$24</f>
+        <f>E47*$B$25</f>
         <v/>
       </c>
       <c r="F53">
-        <f>E57*$B$17*$B$24</f>
+        <f>F47*$B$25</f>
         <v/>
       </c>
       <c r="G53">
-        <f>F57*$B$17*$B$24</f>
+        <f>G47*$B$25</f>
         <v/>
       </c>
       <c r="H53">
-        <f>G57*$B$17*$B$24</f>
+        <f>H47*$B$25</f>
         <v/>
       </c>
       <c r="I53">
-        <f>H57*$B$17*$B$24</f>
+        <f>I47*$B$25</f>
         <v/>
       </c>
       <c r="J53">
-        <f>I57*$B$17*$B$24</f>
+        <f>J47*$B$25</f>
         <v/>
       </c>
       <c r="K53">
-        <f>J57*$B$17*$B$24</f>
+        <f>K47*$B$25</f>
         <v/>
       </c>
       <c r="L53">
-        <f>K57*$B$17*$B$24</f>
+        <f>L47*$B$25</f>
         <v/>
       </c>
       <c r="M53">
-        <f>L57*$B$17*$B$24</f>
+        <f>M47*$B$25</f>
         <v/>
       </c>
       <c r="N53">
@@ -2520,60 +2423,60 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Итого квалифицированных</t>
-        </is>
-      </c>
-      <c r="B54" s="6">
-        <f>B48+B49+B50+B51+B52+B53</f>
-        <v/>
-      </c>
-      <c r="C54" s="6">
-        <f>C48+C49+C50+C51+C52+C53</f>
-        <v/>
-      </c>
-      <c r="D54" s="6">
-        <f>D48+D49+D50+D51+D52+D53</f>
-        <v/>
-      </c>
-      <c r="E54" s="6">
-        <f>E48+E49+E50+E51+E52+E53</f>
-        <v/>
-      </c>
-      <c r="F54" s="6">
-        <f>F48+F49+F50+F51+F52+F53</f>
-        <v/>
-      </c>
-      <c r="G54" s="6">
-        <f>G48+G49+G50+G51+G52+G53</f>
-        <v/>
-      </c>
-      <c r="H54" s="6">
-        <f>H48+H49+H50+H51+H52+H53</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>I48+I49+I50+I51+I52+I53</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>J48+J49+J50+J51+J52+J53</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>K48+K49+K50+K51+K52+K53</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>L48+L49+L50+L51+L52+L53</f>
-        <v/>
-      </c>
-      <c r="M54" s="6">
-        <f>M48+M49+M50+M51+M52+M53</f>
-        <v/>
-      </c>
-      <c r="N54" s="6">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Квалифицировано: партнёры</t>
+        </is>
+      </c>
+      <c r="B54">
+        <f>B48*$B$22</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>C48*$B$22</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>D48*$B$22</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>E48*$B$22</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>F48*$B$22</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>G48*$B$22</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>H48*$B$22</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>I48*$B$22</f>
+        <v/>
+      </c>
+      <c r="J54">
+        <f>J48*$B$22</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>K48*$B$22</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>L48*$B$22</f>
+        <v/>
+      </c>
+      <c r="M54">
+        <f>M48*$B$22</f>
+        <v/>
+      </c>
+      <c r="N54">
         <f>SUM(B54:M54)</f>
         <v/>
       </c>
@@ -2581,55 +2484,54 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Сделки через агентства</t>
-        </is>
-      </c>
-      <c r="B55">
-        <f>ROUND(MIN(B54*$B$28,B14*B30),0)</f>
-        <v/>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
       </c>
       <c r="C55">
-        <f>ROUND(MIN(C54*$B$28,C14*C30),0)</f>
+        <f>B59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="D55">
-        <f>ROUND(MIN(D54*$B$28,D14*D30),0)</f>
+        <f>C59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="E55">
-        <f>ROUND(MIN(E54*$B$28,E14*E30),0)</f>
+        <f>D59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="F55">
-        <f>ROUND(MIN(F54*$B$28,F14*F30),0)</f>
+        <f>E59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="G55">
-        <f>ROUND(MIN(G54*$B$28,G14*G30),0)</f>
+        <f>F59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(MIN(H54*$B$28,H14*H30),0)</f>
+        <f>G59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(MIN(I54*$B$28,I14*I30),0)</f>
+        <f>H59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(MIN(J54*$B$28,J14*J30),0)</f>
+        <f>I59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(MIN(K54*$B$28,K14*K30),0)</f>
+        <f>J59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="L55">
-        <f>ROUND(MIN(L54*$B$28,L14*L30),0)</f>
+        <f>K59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="M55">
-        <f>ROUND(MIN(M54*$B$28,M14*M30),0)</f>
+        <f>L59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="N55">
@@ -2638,119 +2540,119 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Сделки на каталоге IS24</t>
-        </is>
-      </c>
-      <c r="B56">
-        <f>ROUND(B54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="C56">
-        <f>ROUND(C54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>ROUND(D54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>ROUND(E54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>ROUND(F54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>ROUND(G54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>ROUND(H54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="I56">
-        <f>ROUND(I54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="J56">
-        <f>ROUND(J54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="K56">
-        <f>ROUND(K54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="L56">
-        <f>ROUND(L54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="M56">
-        <f>ROUND(M54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="N56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Итого квалифицированных</t>
+        </is>
+      </c>
+      <c r="B56" s="6">
+        <f>B50+B51+B52+B53+B54+B55</f>
+        <v/>
+      </c>
+      <c r="C56" s="6">
+        <f>C50+C51+C52+C53+C54+C55</f>
+        <v/>
+      </c>
+      <c r="D56" s="6">
+        <f>D50+D51+D52+D53+D54+D55</f>
+        <v/>
+      </c>
+      <c r="E56" s="6">
+        <f>E50+E51+E52+E53+E54+E55</f>
+        <v/>
+      </c>
+      <c r="F56" s="6">
+        <f>F50+F51+F52+F53+F54+F55</f>
+        <v/>
+      </c>
+      <c r="G56" s="6">
+        <f>G50+G51+G52+G53+G54+G55</f>
+        <v/>
+      </c>
+      <c r="H56" s="6">
+        <f>H50+H51+H52+H53+H54+H55</f>
+        <v/>
+      </c>
+      <c r="I56" s="6">
+        <f>I50+I51+I52+I53+I54+I55</f>
+        <v/>
+      </c>
+      <c r="J56" s="6">
+        <f>J50+J51+J52+J53+J54+J55</f>
+        <v/>
+      </c>
+      <c r="K56" s="6">
+        <f>K50+K51+K52+K53+K54+K55</f>
+        <v/>
+      </c>
+      <c r="L56" s="6">
+        <f>L50+L51+L52+L53+L54+L55</f>
+        <v/>
+      </c>
+      <c r="M56" s="6">
+        <f>M50+M51+M52+M53+M54+M55</f>
+        <v/>
+      </c>
+      <c r="N56" s="6">
         <f>SUM(B56:M56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Сделок всего</t>
-        </is>
-      </c>
-      <c r="B57" s="6">
-        <f>B55+B56</f>
-        <v/>
-      </c>
-      <c r="C57" s="6">
-        <f>C55+C56</f>
-        <v/>
-      </c>
-      <c r="D57" s="6">
-        <f>D55+D56</f>
-        <v/>
-      </c>
-      <c r="E57" s="6">
-        <f>E55+E56</f>
-        <v/>
-      </c>
-      <c r="F57" s="6">
-        <f>F55+F56</f>
-        <v/>
-      </c>
-      <c r="G57" s="6">
-        <f>G55+G56</f>
-        <v/>
-      </c>
-      <c r="H57" s="6">
-        <f>H55+H56</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>I55+I56</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>J55+J56</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>K55+K56</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>L55+L56</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>M55+M56</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Сделки через агентства</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>ROUND(MIN(B56*$B$28,B14*B30),0)</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>ROUND(MIN(C56*$B$28,C14*C30),0)</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>ROUND(MIN(D56*$B$28,D14*D30),0)</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>ROUND(MIN(E56*$B$28,E14*E30),0)</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>ROUND(MIN(F56*$B$28,F14*F30),0)</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>ROUND(MIN(G56*$B$28,G14*G30),0)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>ROUND(MIN(H56*$B$28,H14*H30),0)</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>ROUND(MIN(I56*$B$28,I14*I30),0)</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>ROUND(MIN(J56*$B$28,J14*J30),0)</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>ROUND(MIN(K56*$B$28,K14*K30),0)</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>ROUND(MIN(L56*$B$28,L14*L30),0)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>ROUND(MIN(M56*$B$28,M14*M30),0)</f>
+        <v/>
+      </c>
+      <c r="N57">
         <f>SUM(B57:M57)</f>
         <v/>
       </c>
@@ -2758,55 +2660,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Сделок с B2C fee</t>
+          <t>Сделки на каталоге IS24</t>
         </is>
       </c>
       <c r="B58">
-        <f>B56+ROUND(B55*$B$37,0)</f>
+        <f>ROUND(B56*$B$29,0)</f>
         <v/>
       </c>
       <c r="C58">
-        <f>C56+ROUND(C55*$B$37,0)</f>
+        <f>ROUND(C56*$B$29,0)</f>
         <v/>
       </c>
       <c r="D58">
-        <f>D56+ROUND(D55*$B$37,0)</f>
+        <f>ROUND(D56*$B$29,0)</f>
         <v/>
       </c>
       <c r="E58">
-        <f>E56+ROUND(E55*$B$37,0)</f>
+        <f>ROUND(E56*$B$29,0)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>F56+ROUND(F55*$B$37,0)</f>
+        <f>ROUND(F56*$B$29,0)</f>
         <v/>
       </c>
       <c r="G58">
-        <f>G56+ROUND(G55*$B$37,0)</f>
+        <f>ROUND(G56*$B$29,0)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>H56+ROUND(H55*$B$37,0)</f>
+        <f>ROUND(H56*$B$29,0)</f>
         <v/>
       </c>
       <c r="I58">
-        <f>I56+ROUND(I55*$B$37,0)</f>
+        <f>ROUND(I56*$B$29,0)</f>
         <v/>
       </c>
       <c r="J58">
-        <f>J56+ROUND(J55*$B$37,0)</f>
+        <f>ROUND(J56*$B$29,0)</f>
         <v/>
       </c>
       <c r="K58">
-        <f>K56+ROUND(K55*$B$37,0)</f>
+        <f>ROUND(K56*$B$29,0)</f>
         <v/>
       </c>
       <c r="L58">
-        <f>L56+ROUND(L55*$B$37,0)</f>
+        <f>ROUND(L56*$B$29,0)</f>
         <v/>
       </c>
       <c r="M58">
-        <f>M56+ROUND(M55*$B$37,0)</f>
+        <f>ROUND(M56*$B$29,0)</f>
         <v/>
       </c>
       <c r="N58">
@@ -2814,183 +2716,183 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Сделок всего</t>
+        </is>
+      </c>
+      <c r="B59" s="6">
+        <f>B57+B58</f>
+        <v/>
+      </c>
+      <c r="C59" s="6">
+        <f>C57+C58</f>
+        <v/>
+      </c>
+      <c r="D59" s="6">
+        <f>D57+D58</f>
+        <v/>
+      </c>
+      <c r="E59" s="6">
+        <f>E57+E58</f>
+        <v/>
+      </c>
+      <c r="F59" s="6">
+        <f>F57+F58</f>
+        <v/>
+      </c>
+      <c r="G59" s="6">
+        <f>G57+G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="6">
+        <f>H57+H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="6">
+        <f>I57+I58</f>
+        <v/>
+      </c>
+      <c r="J59" s="6">
+        <f>J57+J58</f>
+        <v/>
+      </c>
+      <c r="K59" s="6">
+        <f>K57+K58</f>
+        <v/>
+      </c>
+      <c r="L59" s="6">
+        <f>L57+L58</f>
+        <v/>
+      </c>
+      <c r="M59" s="6">
+        <f>M57+M58</f>
+        <v/>
+      </c>
+      <c r="N59" s="6">
+        <f>SUM(B59:M59)</f>
+        <v/>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Сделок с B2C fee</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>B58+ROUND(B57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>C58+ROUND(C57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>D58+ROUND(D57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>E58+ROUND(E57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>F58+ROUND(F57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>G58+ROUND(G57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>H58+ROUND(H57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>I58+ROUND(I57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>J58+ROUND(J57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>K58+ROUND(K57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>L58+ROUND(L57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="M60">
+        <f>M58+ROUND(M57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>SUM(B60:M60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>ВЫРУЧКА</t>
         </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
-        </is>
-      </c>
-      <c r="B61">
-        <f>ROUND(B55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>ROUND(C55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>ROUND(D55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>ROUND(E55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="F61">
-        <f>ROUND(F55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="G61">
-        <f>ROUND(G55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="H61">
-        <f>ROUND(H55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="I61">
-        <f>ROUND(I55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="J61">
-        <f>ROUND(J55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="K61">
-        <f>ROUND(K55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="L61">
-        <f>ROUND(L55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="M61">
-        <f>ROUND(M55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="N61">
-        <f>SUM(B61:M61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>R3: B2C fee</t>
-        </is>
-      </c>
-      <c r="B62">
-        <f>B58*$B$36</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>C58*$B$36</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>D58*$B$36</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>E58*$B$36</f>
-        <v/>
-      </c>
-      <c r="F62">
-        <f>F58*$B$36</f>
-        <v/>
-      </c>
-      <c r="G62">
-        <f>G58*$B$36</f>
-        <v/>
-      </c>
-      <c r="H62">
-        <f>H58*$B$36</f>
-        <v/>
-      </c>
-      <c r="I62">
-        <f>I58*$B$36</f>
-        <v/>
-      </c>
-      <c r="J62">
-        <f>J58*$B$36</f>
-        <v/>
-      </c>
-      <c r="K62">
-        <f>K58*$B$36</f>
-        <v/>
-      </c>
-      <c r="L62">
-        <f>L58*$B$36</f>
-        <v/>
-      </c>
-      <c r="M62">
-        <f>M58*$B$36</f>
-        <v/>
-      </c>
-      <c r="N62">
-        <f>SUM(B62:M62)</f>
-        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R4: upsell</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B63">
-        <f>B39</f>
+        <f>ROUND(B57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>C39</f>
+        <f>ROUND(C57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="D63">
-        <f>D39</f>
+        <f>ROUND(D57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>E39</f>
+        <f>ROUND(E57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>F39</f>
+        <f>ROUND(F57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>G39</f>
+        <f>ROUND(G57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>H39</f>
+        <f>ROUND(H57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>I39</f>
+        <f>ROUND(I57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>J39</f>
+        <f>ROUND(J57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>K39</f>
+        <f>ROUND(K57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="L63">
-        <f>L39</f>
+        <f>ROUND(L57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="M63">
-        <f>M39</f>
+        <f>ROUND(M57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="N63">
@@ -2999,265 +2901,301 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R3: B2C fee</t>
+        </is>
+      </c>
+      <c r="B64">
+        <f>B60*$B$36</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>C60*$B$36</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>D60*$B$36</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>E60*$B$36</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>F60*$B$36</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>G60*$B$36</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>H60*$B$36</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>I60*$B$36</f>
+        <v/>
+      </c>
+      <c r="J64">
+        <f>J60*$B$36</f>
+        <v/>
+      </c>
+      <c r="K64">
+        <f>K60*$B$36</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>L60*$B$36</f>
+        <v/>
+      </c>
+      <c r="M64">
+        <f>M60*$B$36</f>
+        <v/>
+      </c>
+      <c r="N64">
+        <f>SUM(B64:M64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>B41</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>D41</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>F41</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>G41</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>H41</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>I41</f>
+        <v/>
+      </c>
+      <c r="J65">
+        <f>J41</f>
+        <v/>
+      </c>
+      <c r="K65">
+        <f>K41</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>L41</f>
+        <v/>
+      </c>
+      <c r="M65">
+        <f>M41</f>
+        <v/>
+      </c>
+      <c r="N65">
+        <f>SUM(B65:M65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>R5: реферал на мебель (Zolak)</t>
+        </is>
+      </c>
+      <c r="B66">
+        <f>ROUND(B59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>ROUND(C59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>ROUND(D59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>ROUND(E59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>ROUND(F59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>ROUND(G59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="H66">
+        <f>ROUND(H59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="I66">
+        <f>ROUND(I59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="J66">
+        <f>ROUND(J59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="K66">
+        <f>ROUND(K59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>ROUND(L59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="M66">
+        <f>ROUND(M59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="N66">
+        <f>SUM(B66:M66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B64" s="6">
-        <f>B61+B62+B63</f>
-        <v/>
-      </c>
-      <c r="C64" s="6">
-        <f>C61+C62+C63</f>
-        <v/>
-      </c>
-      <c r="D64" s="6">
-        <f>D61+D62+D63</f>
-        <v/>
-      </c>
-      <c r="E64" s="6">
-        <f>E61+E62+E63</f>
-        <v/>
-      </c>
-      <c r="F64" s="6">
-        <f>F61+F62+F63</f>
-        <v/>
-      </c>
-      <c r="G64" s="6">
-        <f>G61+G62+G63</f>
-        <v/>
-      </c>
-      <c r="H64" s="6">
-        <f>H61+H62+H63</f>
-        <v/>
-      </c>
-      <c r="I64" s="6">
-        <f>I61+I62+I63</f>
-        <v/>
-      </c>
-      <c r="J64" s="6">
-        <f>J61+J62+J63</f>
-        <v/>
-      </c>
-      <c r="K64" s="6">
-        <f>K61+K62+K63</f>
-        <v/>
-      </c>
-      <c r="L64" s="6">
-        <f>L61+L62+L63</f>
-        <v/>
-      </c>
-      <c r="M64" s="6">
-        <f>M61+M62+M63</f>
-        <v/>
-      </c>
-      <c r="N64" s="6">
-        <f>SUM(B64:M64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B67" s="6">
+        <f>B63+B64+B65+B66</f>
+        <v/>
+      </c>
+      <c r="C67" s="6">
+        <f>C63+C64+C65+C66</f>
+        <v/>
+      </c>
+      <c r="D67" s="6">
+        <f>D63+D64+D65+D66</f>
+        <v/>
+      </c>
+      <c r="E67" s="6">
+        <f>E63+E64+E65+E66</f>
+        <v/>
+      </c>
+      <c r="F67" s="6">
+        <f>F63+F64+F65+F66</f>
+        <v/>
+      </c>
+      <c r="G67" s="6">
+        <f>G63+G64+G65+G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="6">
+        <f>H63+H64+H65+H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="6">
+        <f>I63+I64+I65+I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="6">
+        <f>J63+J64+J65+J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="6">
+        <f>K63+K64+K65+K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="6">
+        <f>L63+L64+L65+L66</f>
+        <v/>
+      </c>
+      <c r="M67" s="6">
+        <f>M63+M64+M65+M66</f>
+        <v/>
+      </c>
+      <c r="N67" s="6">
+        <f>SUM(B67:M67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B67">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C67">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D67">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E67">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F67">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G67">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H67">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I67">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J67">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K67">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L67">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M67">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N67">
-        <f>SUM(B67:M67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="N68">
-        <f>SUM(B68:M68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>1291</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>1382</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>1473</v>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>1564</v>
-      </c>
-      <c r="G69" s="8" t="n">
-        <v>1655</v>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>1745</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>1836</v>
-      </c>
-      <c r="J69" s="8" t="n">
-        <v>1927</v>
-      </c>
-      <c r="K69" s="8" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L69" s="8" t="n">
-        <v>2109</v>
-      </c>
-      <c r="M69" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="N69">
-        <f>SUM(B69:M69)</f>
-        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K70" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="L70" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M70" s="8" t="n">
-        <v>4500</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B70">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H70">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J70">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K70">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M70">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N70">
         <f>SUM(B70:M70)</f>
@@ -3267,44 +3205,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>1150</v>
+        <v>500</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="N71">
         <f>SUM(B71:M71)</f>
@@ -3314,44 +3252,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C72" s="8" t="n">
-        <v>500</v>
+        <v>1291</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>500</v>
+        <v>1382</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>600</v>
+        <v>1473</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>600</v>
+        <v>1564</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>600</v>
+        <v>1655</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>700</v>
+        <v>1745</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>700</v>
+        <v>1836</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>700</v>
+        <v>1927</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>800</v>
+        <v>2018</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>800</v>
+        <v>2109</v>
       </c>
       <c r="M72" s="8" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="N72">
         <f>SUM(B72:M72)</f>
@@ -3361,56 +3299,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B73">
-        <f>ROUND(B61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C73">
-        <f>ROUND(C61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D73">
-        <f>ROUND(D61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E73">
-        <f>ROUND(E61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F73">
-        <f>ROUND(F61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G73">
-        <f>ROUND(G61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H73">
-        <f>ROUND(H61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I73">
-        <f>ROUND(I61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J73">
-        <f>ROUND(J61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K73">
-        <f>ROUND(K61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L73">
-        <f>ROUND(L61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M73">
-        <f>ROUND(M61*$B$38,0)</f>
-        <v/>
+          <t>Команда: dev / support (контракторы)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>4500</v>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -3418,226 +3344,379 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N74">
+        <f>SUM(B74:M74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N75">
+        <f>SUM(B75:M75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B76">
+        <f>ROUND(B63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>ROUND(C63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>ROUND(D63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>ROUND(E63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>ROUND(F63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>ROUND(G63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>ROUND(H63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>ROUND(I63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>ROUND(J63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K76">
+        <f>ROUND(K63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>ROUND(L63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M76">
+        <f>ROUND(M63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N76">
+        <f>SUM(B76:M76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>TOTAL COSTS</t>
         </is>
       </c>
-      <c r="B74" s="6">
-        <f>B67+B68+B69+B70+B71+B72+B73</f>
-        <v/>
-      </c>
-      <c r="C74" s="6">
-        <f>C67+C68+C69+C70+C71+C72+C73</f>
-        <v/>
-      </c>
-      <c r="D74" s="6">
-        <f>D67+D68+D69+D70+D71+D72+D73</f>
-        <v/>
-      </c>
-      <c r="E74" s="6">
-        <f>E67+E68+E69+E70+E71+E72+E73</f>
-        <v/>
-      </c>
-      <c r="F74" s="6">
-        <f>F67+F68+F69+F70+F71+F72+F73</f>
-        <v/>
-      </c>
-      <c r="G74" s="6">
-        <f>G67+G68+G69+G70+G71+G72+G73</f>
-        <v/>
-      </c>
-      <c r="H74" s="6">
-        <f>H67+H68+H69+H70+H71+H72+H73</f>
-        <v/>
-      </c>
-      <c r="I74" s="6">
-        <f>I67+I68+I69+I70+I71+I72+I73</f>
-        <v/>
-      </c>
-      <c r="J74" s="6">
-        <f>J67+J68+J69+J70+J71+J72+J73</f>
-        <v/>
-      </c>
-      <c r="K74" s="6">
-        <f>K67+K68+K69+K70+K71+K72+K73</f>
-        <v/>
-      </c>
-      <c r="L74" s="6">
-        <f>L67+L68+L69+L70+L71+L72+L73</f>
-        <v/>
-      </c>
-      <c r="M74" s="6">
-        <f>M67+M68+M69+M70+M71+M72+M73</f>
-        <v/>
-      </c>
-      <c r="N74" s="6">
-        <f>SUM(B74:M74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="B77" s="6">
+        <f>B70+B71+B72+B73+B74+B75+B76</f>
+        <v/>
+      </c>
+      <c r="C77" s="6">
+        <f>C70+C71+C72+C73+C74+C75+C76</f>
+        <v/>
+      </c>
+      <c r="D77" s="6">
+        <f>D70+D71+D72+D73+D74+D75+D76</f>
+        <v/>
+      </c>
+      <c r="E77" s="6">
+        <f>E70+E71+E72+E73+E74+E75+E76</f>
+        <v/>
+      </c>
+      <c r="F77" s="6">
+        <f>F70+F71+F72+F73+F74+F75+F76</f>
+        <v/>
+      </c>
+      <c r="G77" s="6">
+        <f>G70+G71+G72+G73+G74+G75+G76</f>
+        <v/>
+      </c>
+      <c r="H77" s="6">
+        <f>H70+H71+H72+H73+H74+H75+H76</f>
+        <v/>
+      </c>
+      <c r="I77" s="6">
+        <f>I70+I71+I72+I73+I74+I75+I76</f>
+        <v/>
+      </c>
+      <c r="J77" s="6">
+        <f>J70+J71+J72+J73+J74+J75+J76</f>
+        <v/>
+      </c>
+      <c r="K77" s="6">
+        <f>K70+K71+K72+K73+K74+K75+K76</f>
+        <v/>
+      </c>
+      <c r="L77" s="6">
+        <f>L70+L71+L72+L73+L74+L75+L76</f>
+        <v/>
+      </c>
+      <c r="M77" s="6">
+        <f>M70+M71+M72+M73+M74+M75+M76</f>
+        <v/>
+      </c>
+      <c r="N77" s="6">
+        <f>SUM(B77:M77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B76" s="6">
-        <f>B64-B74</f>
-        <v/>
-      </c>
-      <c r="C76" s="6">
-        <f>C64-C74</f>
-        <v/>
-      </c>
-      <c r="D76" s="6">
-        <f>D64-D74</f>
-        <v/>
-      </c>
-      <c r="E76" s="6">
-        <f>E64-E74</f>
-        <v/>
-      </c>
-      <c r="F76" s="6">
-        <f>F64-F74</f>
-        <v/>
-      </c>
-      <c r="G76" s="6">
-        <f>G64-G74</f>
-        <v/>
-      </c>
-      <c r="H76" s="6">
-        <f>H64-H74</f>
-        <v/>
-      </c>
-      <c r="I76" s="6">
-        <f>I64-I74</f>
-        <v/>
-      </c>
-      <c r="J76" s="6">
-        <f>J64-J74</f>
-        <v/>
-      </c>
-      <c r="K76" s="6">
-        <f>K64-K74</f>
-        <v/>
-      </c>
-      <c r="L76" s="6">
-        <f>L64-L74</f>
-        <v/>
-      </c>
-      <c r="M76" s="6">
-        <f>M64-M74</f>
-        <v/>
-      </c>
-      <c r="N76" s="6">
-        <f>SUM(B76:M76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Кэш (старт €18,000)</t>
-        </is>
-      </c>
-      <c r="B77">
-        <f>18000+B76</f>
-        <v/>
-      </c>
-      <c r="C77">
-        <f>B77+C76</f>
-        <v/>
-      </c>
-      <c r="D77">
-        <f>C77+D76</f>
-        <v/>
-      </c>
-      <c r="E77">
-        <f>D77+E76</f>
-        <v/>
-      </c>
-      <c r="F77">
-        <f>E77+F76</f>
-        <v/>
-      </c>
-      <c r="G77">
-        <f>F77+G76</f>
-        <v/>
-      </c>
-      <c r="H77">
-        <f>G77+H76</f>
-        <v/>
-      </c>
-      <c r="I77">
-        <f>H77+I76</f>
-        <v/>
-      </c>
-      <c r="J77">
-        <f>I77+J76</f>
-        <v/>
-      </c>
-      <c r="K77">
-        <f>J77+K76</f>
-        <v/>
-      </c>
-      <c r="L77">
-        <f>K77+L76</f>
-        <v/>
-      </c>
-      <c r="M77">
-        <f>L77+M76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
-        </is>
+      <c r="B79" s="6">
+        <f>B67-B77</f>
+        <v/>
+      </c>
+      <c r="C79" s="6">
+        <f>C67-C77</f>
+        <v/>
+      </c>
+      <c r="D79" s="6">
+        <f>D67-D77</f>
+        <v/>
+      </c>
+      <c r="E79" s="6">
+        <f>E67-E77</f>
+        <v/>
+      </c>
+      <c r="F79" s="6">
+        <f>F67-F77</f>
+        <v/>
+      </c>
+      <c r="G79" s="6">
+        <f>G67-G77</f>
+        <v/>
+      </c>
+      <c r="H79" s="6">
+        <f>H67-H77</f>
+        <v/>
+      </c>
+      <c r="I79" s="6">
+        <f>I67-I77</f>
+        <v/>
+      </c>
+      <c r="J79" s="6">
+        <f>J67-J77</f>
+        <v/>
+      </c>
+      <c r="K79" s="6">
+        <f>K67-K77</f>
+        <v/>
+      </c>
+      <c r="L79" s="6">
+        <f>L67-L77</f>
+        <v/>
+      </c>
+      <c r="M79" s="6">
+        <f>M67-M77</f>
+        <v/>
+      </c>
+      <c r="N79" s="6">
+        <f>SUM(B79:M79)</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAC на квалифицированного лида, €</t>
+          <t>Кэш (старт €18,000)</t>
         </is>
       </c>
       <c r="B80">
-        <f>ROUND(N6/N54,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B81">
-        <f>ROUND(N6/N57,0)</f>
+        <f>18000+B79</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>B80+C79</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>C80+D79</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>D80+E79</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>E80+F79</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>F80+G79</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>G80+H79</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>H80+I79</f>
+        <v/>
+      </c>
+      <c r="J80">
+        <f>I80+J79</f>
+        <v/>
+      </c>
+      <c r="K80">
+        <f>J80+K79</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>K80+L79</f>
+        <v/>
+      </c>
+      <c r="M80">
+        <f>L80+M79</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Выручка на агентскую сделку, €</t>
-        </is>
-      </c>
-      <c r="B82">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
-        <v/>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>CAC на квалифицированного лида, €</t>
+        </is>
+      </c>
+      <c r="B83">
+        <f>ROUND(N6/N56,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B84">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B85">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B83">
-        <f>ROUND(B82/B81,1)</f>
+      <c r="B86">
+        <f>ROUND(B85/B84,1)</f>
         <v/>
       </c>
     </row>
@@ -3652,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4264,227 +4343,129 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Zolak: средний чек мебели, €</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Zolak: наша доля от мебели</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="8" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N39">
-        <f>SUM(B39:M39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="N41">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B42">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C42">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F42">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I42">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J42">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K42">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L42">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M42">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N42">
-        <f>SUM(B42:M42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Регистрации: комьюнити</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>E9</f>
-        <v/>
-      </c>
-      <c r="F43">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="G43">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="I43">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="J43">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="K43">
-        <f>K9</f>
-        <v/>
-      </c>
-      <c r="L43">
-        <f>L9</f>
-        <v/>
-      </c>
-      <c r="M43">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N43">
-        <f>SUM(B43:M43)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B44">
-        <f>B12*$B$13</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C44">
-        <f>C12*$B$13</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D44">
-        <f>D12*$B$13</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E44">
-        <f>E12*$B$13</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F44">
-        <f>F12*$B$13</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G44">
-        <f>G12*$B$13</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H44">
-        <f>H12*$B$13</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I44">
-        <f>I12*$B$13</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J44">
-        <f>J12*$B$13</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K44">
-        <f>K12*$B$13</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L44">
-        <f>L12*$B$13</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M44">
-        <f>M12*$B$13</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N44">
@@ -4495,55 +4476,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B45">
-        <f>B14*$B$15*$B$16</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C45">
-        <f>C14*$B$15*$B$16</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D14*$B$15*$B$16</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E14*$B$15*$B$16</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F14*$B$15*$B$16</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G14*$B$15*$B$16</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H14*$B$15*$B$16</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I14*$B$15*$B$16</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J14*$B$15*$B$16</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K14*$B$15*$B$16</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L14*$B$15*$B$16</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M14*$B$15*$B$16</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N45">
@@ -4554,55 +4535,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: SEO</t>
         </is>
       </c>
       <c r="B46">
-        <f>B10*$B$11</f>
+        <f>B12*$B$13</f>
         <v/>
       </c>
       <c r="C46">
-        <f>C10*$B$11</f>
+        <f>C12*$B$13</f>
         <v/>
       </c>
       <c r="D46">
-        <f>D10*$B$11</f>
+        <f>D12*$B$13</f>
         <v/>
       </c>
       <c r="E46">
-        <f>E10*$B$11</f>
+        <f>E12*$B$13</f>
         <v/>
       </c>
       <c r="F46">
-        <f>F10*$B$11</f>
+        <f>F12*$B$13</f>
         <v/>
       </c>
       <c r="G46">
-        <f>G10*$B$11</f>
+        <f>G12*$B$13</f>
         <v/>
       </c>
       <c r="H46">
-        <f>H10*$B$11</f>
+        <f>H12*$B$13</f>
         <v/>
       </c>
       <c r="I46">
-        <f>I10*$B$11</f>
+        <f>I12*$B$13</f>
         <v/>
       </c>
       <c r="J46">
-        <f>J10*$B$11</f>
+        <f>J12*$B$13</f>
         <v/>
       </c>
       <c r="K46">
-        <f>K10*$B$11</f>
+        <f>K12*$B$13</f>
         <v/>
       </c>
       <c r="L46">
-        <f>L10*$B$11</f>
+        <f>L12*$B$13</f>
         <v/>
       </c>
       <c r="M46">
-        <f>M10*$B$11</f>
+        <f>M12*$B$13</f>
         <v/>
       </c>
       <c r="N46">
@@ -4611,60 +4592,60 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Итого регистраций</t>
-        </is>
-      </c>
-      <c r="B47" s="6">
-        <f>B42+B43+B44+B45+B46</f>
-        <v/>
-      </c>
-      <c r="C47" s="6">
-        <f>C42+C43+C44+C45+C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="6">
-        <f>D42+D43+D44+D45+D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="6">
-        <f>E42+E43+E44+E45+E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="6">
-        <f>F42+F43+F44+F45+F46</f>
-        <v/>
-      </c>
-      <c r="G47" s="6">
-        <f>G42+G43+G44+G45+G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="6">
-        <f>H42+H43+H44+H45+H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="6">
-        <f>I42+I43+I44+I45+I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="6">
-        <f>J42+J43+J44+J45+J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="6">
-        <f>K42+K43+K44+K45+K46</f>
-        <v/>
-      </c>
-      <c r="L47" s="6">
-        <f>L42+L43+L44+L45+L46</f>
-        <v/>
-      </c>
-      <c r="M47" s="6">
-        <f>M42+M43+M44+M45+M46</f>
-        <v/>
-      </c>
-      <c r="N47" s="6">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Регистрации: агентства</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>B14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>C14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>D14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>E14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>F14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>G14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>H14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="I47">
+        <f>I14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="J47">
+        <f>J14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>K14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>L14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="M47">
+        <f>M14*$B$15*$B$16</f>
+        <v/>
+      </c>
+      <c r="N47">
         <f>SUM(B47:M47)</f>
         <v/>
       </c>
@@ -4672,55 +4653,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Квалифицировано: paid</t>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
         </is>
       </c>
       <c r="B48">
-        <f>B42*$B$20</f>
+        <f>B10*$B$11</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C42*$B$20</f>
+        <f>C10*$B$11</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D42*$B$20</f>
+        <f>D10*$B$11</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E42*$B$20</f>
+        <f>E10*$B$11</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F42*$B$20</f>
+        <f>F10*$B$11</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G42*$B$20</f>
+        <f>G10*$B$11</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H42*$B$20</f>
+        <f>H10*$B$11</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I42*$B$20</f>
+        <f>I10*$B$11</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J42*$B$20</f>
+        <f>J10*$B$11</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K42*$B$20</f>
+        <f>K10*$B$11</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L42*$B$20</f>
+        <f>L10*$B$11</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M42*$B$20</f>
+        <f>M10*$B$11</f>
         <v/>
       </c>
       <c r="N48">
@@ -4729,60 +4710,60 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Квалифицировано: комьюнити</t>
-        </is>
-      </c>
-      <c r="B49">
-        <f>B43*$B$21</f>
-        <v/>
-      </c>
-      <c r="C49">
-        <f>C43*$B$21</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>D43*$B$21</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>E43*$B$21</f>
-        <v/>
-      </c>
-      <c r="F49">
-        <f>F43*$B$21</f>
-        <v/>
-      </c>
-      <c r="G49">
-        <f>G43*$B$21</f>
-        <v/>
-      </c>
-      <c r="H49">
-        <f>H43*$B$21</f>
-        <v/>
-      </c>
-      <c r="I49">
-        <f>I43*$B$21</f>
-        <v/>
-      </c>
-      <c r="J49">
-        <f>J43*$B$21</f>
-        <v/>
-      </c>
-      <c r="K49">
-        <f>K43*$B$21</f>
-        <v/>
-      </c>
-      <c r="L49">
-        <f>L43*$B$21</f>
-        <v/>
-      </c>
-      <c r="M49">
-        <f>M43*$B$21</f>
-        <v/>
-      </c>
-      <c r="N49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Итого регистраций</t>
+        </is>
+      </c>
+      <c r="B49" s="6">
+        <f>B44+B45+B46+B47+B48</f>
+        <v/>
+      </c>
+      <c r="C49" s="6">
+        <f>C44+C45+C46+C47+C48</f>
+        <v/>
+      </c>
+      <c r="D49" s="6">
+        <f>D44+D45+D46+D47+D48</f>
+        <v/>
+      </c>
+      <c r="E49" s="6">
+        <f>E44+E45+E46+E47+E48</f>
+        <v/>
+      </c>
+      <c r="F49" s="6">
+        <f>F44+F45+F46+F47+F48</f>
+        <v/>
+      </c>
+      <c r="G49" s="6">
+        <f>G44+G45+G46+G47+G48</f>
+        <v/>
+      </c>
+      <c r="H49" s="6">
+        <f>H44+H45+H46+H47+H48</f>
+        <v/>
+      </c>
+      <c r="I49" s="6">
+        <f>I44+I45+I46+I47+I48</f>
+        <v/>
+      </c>
+      <c r="J49" s="6">
+        <f>J44+J45+J46+J47+J48</f>
+        <v/>
+      </c>
+      <c r="K49" s="6">
+        <f>K44+K45+K46+K47+K48</f>
+        <v/>
+      </c>
+      <c r="L49" s="6">
+        <f>L44+L45+L46+L47+L48</f>
+        <v/>
+      </c>
+      <c r="M49" s="6">
+        <f>M44+M45+M46+M47+M48</f>
+        <v/>
+      </c>
+      <c r="N49" s="6">
         <f>SUM(B49:M49)</f>
         <v/>
       </c>
@@ -4790,55 +4771,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: SEO</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$23</f>
+        <f>B44*$B$20</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$23</f>
+        <f>C44*$B$20</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$23</f>
+        <f>D44*$B$20</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$23</f>
+        <f>E44*$B$20</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$23</f>
+        <f>F44*$B$20</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$23</f>
+        <f>G44*$B$20</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$23</f>
+        <f>H44*$B$20</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$23</f>
+        <f>I44*$B$20</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$23</f>
+        <f>J44*$B$20</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$23</f>
+        <f>K44*$B$20</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$23</f>
+        <f>L44*$B$20</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$23</f>
+        <f>M44*$B$20</f>
         <v/>
       </c>
       <c r="N50">
@@ -4849,55 +4830,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$25</f>
+        <f>B45*$B$21</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$25</f>
+        <f>C45*$B$21</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$25</f>
+        <f>D45*$B$21</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$25</f>
+        <f>E45*$B$21</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$25</f>
+        <f>F45*$B$21</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$25</f>
+        <f>G45*$B$21</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$25</f>
+        <f>H45*$B$21</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$25</f>
+        <f>I45*$B$21</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$25</f>
+        <f>J45*$B$21</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$25</f>
+        <f>K45*$B$21</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$25</f>
+        <f>L45*$B$21</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$25</f>
+        <f>M45*$B$21</f>
         <v/>
       </c>
       <c r="N51">
@@ -4908,55 +4889,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: SEO</t>
         </is>
       </c>
       <c r="B52">
-        <f>B46*$B$22</f>
+        <f>B46*$B$23</f>
         <v/>
       </c>
       <c r="C52">
-        <f>C46*$B$22</f>
+        <f>C46*$B$23</f>
         <v/>
       </c>
       <c r="D52">
-        <f>D46*$B$22</f>
+        <f>D46*$B$23</f>
         <v/>
       </c>
       <c r="E52">
-        <f>E46*$B$22</f>
+        <f>E46*$B$23</f>
         <v/>
       </c>
       <c r="F52">
-        <f>F46*$B$22</f>
+        <f>F46*$B$23</f>
         <v/>
       </c>
       <c r="G52">
-        <f>G46*$B$22</f>
+        <f>G46*$B$23</f>
         <v/>
       </c>
       <c r="H52">
-        <f>H46*$B$22</f>
+        <f>H46*$B$23</f>
         <v/>
       </c>
       <c r="I52">
-        <f>I46*$B$22</f>
+        <f>I46*$B$23</f>
         <v/>
       </c>
       <c r="J52">
-        <f>J46*$B$22</f>
+        <f>J46*$B$23</f>
         <v/>
       </c>
       <c r="K52">
-        <f>K46*$B$22</f>
+        <f>K46*$B$23</f>
         <v/>
       </c>
       <c r="L52">
-        <f>L46*$B$22</f>
+        <f>L46*$B$23</f>
         <v/>
       </c>
       <c r="M52">
-        <f>M46*$B$22</f>
+        <f>M46*$B$23</f>
         <v/>
       </c>
       <c r="N52">
@@ -4967,54 +4948,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
+          <t>Квалифицировано: агентства</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>B47*$B$25</f>
+        <v/>
       </c>
       <c r="C53">
-        <f>B57*$B$17*$B$24</f>
+        <f>C47*$B$25</f>
         <v/>
       </c>
       <c r="D53">
-        <f>C57*$B$17*$B$24</f>
+        <f>D47*$B$25</f>
         <v/>
       </c>
       <c r="E53">
-        <f>D57*$B$17*$B$24</f>
+        <f>E47*$B$25</f>
         <v/>
       </c>
       <c r="F53">
-        <f>E57*$B$17*$B$24</f>
+        <f>F47*$B$25</f>
         <v/>
       </c>
       <c r="G53">
-        <f>F57*$B$17*$B$24</f>
+        <f>G47*$B$25</f>
         <v/>
       </c>
       <c r="H53">
-        <f>G57*$B$17*$B$24</f>
+        <f>H47*$B$25</f>
         <v/>
       </c>
       <c r="I53">
-        <f>H57*$B$17*$B$24</f>
+        <f>I47*$B$25</f>
         <v/>
       </c>
       <c r="J53">
-        <f>I57*$B$17*$B$24</f>
+        <f>J47*$B$25</f>
         <v/>
       </c>
       <c r="K53">
-        <f>J57*$B$17*$B$24</f>
+        <f>K47*$B$25</f>
         <v/>
       </c>
       <c r="L53">
-        <f>K57*$B$17*$B$24</f>
+        <f>L47*$B$25</f>
         <v/>
       </c>
       <c r="M53">
-        <f>L57*$B$17*$B$24</f>
+        <f>M47*$B$25</f>
         <v/>
       </c>
       <c r="N53">
@@ -5023,60 +5005,60 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Итого квалифицированных</t>
-        </is>
-      </c>
-      <c r="B54" s="6">
-        <f>B48+B49+B50+B51+B52+B53</f>
-        <v/>
-      </c>
-      <c r="C54" s="6">
-        <f>C48+C49+C50+C51+C52+C53</f>
-        <v/>
-      </c>
-      <c r="D54" s="6">
-        <f>D48+D49+D50+D51+D52+D53</f>
-        <v/>
-      </c>
-      <c r="E54" s="6">
-        <f>E48+E49+E50+E51+E52+E53</f>
-        <v/>
-      </c>
-      <c r="F54" s="6">
-        <f>F48+F49+F50+F51+F52+F53</f>
-        <v/>
-      </c>
-      <c r="G54" s="6">
-        <f>G48+G49+G50+G51+G52+G53</f>
-        <v/>
-      </c>
-      <c r="H54" s="6">
-        <f>H48+H49+H50+H51+H52+H53</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>I48+I49+I50+I51+I52+I53</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>J48+J49+J50+J51+J52+J53</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>K48+K49+K50+K51+K52+K53</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>L48+L49+L50+L51+L52+L53</f>
-        <v/>
-      </c>
-      <c r="M54" s="6">
-        <f>M48+M49+M50+M51+M52+M53</f>
-        <v/>
-      </c>
-      <c r="N54" s="6">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Квалифицировано: партнёры</t>
+        </is>
+      </c>
+      <c r="B54">
+        <f>B48*$B$22</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>C48*$B$22</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>D48*$B$22</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>E48*$B$22</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>F48*$B$22</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>G48*$B$22</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>H48*$B$22</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>I48*$B$22</f>
+        <v/>
+      </c>
+      <c r="J54">
+        <f>J48*$B$22</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>K48*$B$22</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>L48*$B$22</f>
+        <v/>
+      </c>
+      <c r="M54">
+        <f>M48*$B$22</f>
+        <v/>
+      </c>
+      <c r="N54">
         <f>SUM(B54:M54)</f>
         <v/>
       </c>
@@ -5084,55 +5066,54 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Сделки через агентства</t>
-        </is>
-      </c>
-      <c r="B55">
-        <f>ROUND(MIN(B54*$B$28,B14*B30),0)</f>
-        <v/>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
       </c>
       <c r="C55">
-        <f>ROUND(MIN(C54*$B$28,C14*C30),0)</f>
+        <f>B59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="D55">
-        <f>ROUND(MIN(D54*$B$28,D14*D30),0)</f>
+        <f>C59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="E55">
-        <f>ROUND(MIN(E54*$B$28,E14*E30),0)</f>
+        <f>D59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="F55">
-        <f>ROUND(MIN(F54*$B$28,F14*F30),0)</f>
+        <f>E59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="G55">
-        <f>ROUND(MIN(G54*$B$28,G14*G30),0)</f>
+        <f>F59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(MIN(H54*$B$28,H14*H30),0)</f>
+        <f>G59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(MIN(I54*$B$28,I14*I30),0)</f>
+        <f>H59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(MIN(J54*$B$28,J14*J30),0)</f>
+        <f>I59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(MIN(K54*$B$28,K14*K30),0)</f>
+        <f>J59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="L55">
-        <f>ROUND(MIN(L54*$B$28,L14*L30),0)</f>
+        <f>K59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="M55">
-        <f>ROUND(MIN(M54*$B$28,M14*M30),0)</f>
+        <f>L59*$B$17*$B$24</f>
         <v/>
       </c>
       <c r="N55">
@@ -5141,119 +5122,119 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Сделки на каталоге IS24</t>
-        </is>
-      </c>
-      <c r="B56">
-        <f>ROUND(B54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="C56">
-        <f>ROUND(C54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>ROUND(D54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>ROUND(E54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>ROUND(F54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>ROUND(G54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>ROUND(H54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="I56">
-        <f>ROUND(I54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="J56">
-        <f>ROUND(J54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="K56">
-        <f>ROUND(K54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="L56">
-        <f>ROUND(L54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="M56">
-        <f>ROUND(M54*$B$29,0)</f>
-        <v/>
-      </c>
-      <c r="N56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Итого квалифицированных</t>
+        </is>
+      </c>
+      <c r="B56" s="6">
+        <f>B50+B51+B52+B53+B54+B55</f>
+        <v/>
+      </c>
+      <c r="C56" s="6">
+        <f>C50+C51+C52+C53+C54+C55</f>
+        <v/>
+      </c>
+      <c r="D56" s="6">
+        <f>D50+D51+D52+D53+D54+D55</f>
+        <v/>
+      </c>
+      <c r="E56" s="6">
+        <f>E50+E51+E52+E53+E54+E55</f>
+        <v/>
+      </c>
+      <c r="F56" s="6">
+        <f>F50+F51+F52+F53+F54+F55</f>
+        <v/>
+      </c>
+      <c r="G56" s="6">
+        <f>G50+G51+G52+G53+G54+G55</f>
+        <v/>
+      </c>
+      <c r="H56" s="6">
+        <f>H50+H51+H52+H53+H54+H55</f>
+        <v/>
+      </c>
+      <c r="I56" s="6">
+        <f>I50+I51+I52+I53+I54+I55</f>
+        <v/>
+      </c>
+      <c r="J56" s="6">
+        <f>J50+J51+J52+J53+J54+J55</f>
+        <v/>
+      </c>
+      <c r="K56" s="6">
+        <f>K50+K51+K52+K53+K54+K55</f>
+        <v/>
+      </c>
+      <c r="L56" s="6">
+        <f>L50+L51+L52+L53+L54+L55</f>
+        <v/>
+      </c>
+      <c r="M56" s="6">
+        <f>M50+M51+M52+M53+M54+M55</f>
+        <v/>
+      </c>
+      <c r="N56" s="6">
         <f>SUM(B56:M56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Сделок всего</t>
-        </is>
-      </c>
-      <c r="B57" s="6">
-        <f>B55+B56</f>
-        <v/>
-      </c>
-      <c r="C57" s="6">
-        <f>C55+C56</f>
-        <v/>
-      </c>
-      <c r="D57" s="6">
-        <f>D55+D56</f>
-        <v/>
-      </c>
-      <c r="E57" s="6">
-        <f>E55+E56</f>
-        <v/>
-      </c>
-      <c r="F57" s="6">
-        <f>F55+F56</f>
-        <v/>
-      </c>
-      <c r="G57" s="6">
-        <f>G55+G56</f>
-        <v/>
-      </c>
-      <c r="H57" s="6">
-        <f>H55+H56</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>I55+I56</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>J55+J56</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>K55+K56</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>L55+L56</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>M55+M56</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Сделки через агентства</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>ROUND(MIN(B56*$B$28,B14*B30),0)</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>ROUND(MIN(C56*$B$28,C14*C30),0)</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>ROUND(MIN(D56*$B$28,D14*D30),0)</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>ROUND(MIN(E56*$B$28,E14*E30),0)</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>ROUND(MIN(F56*$B$28,F14*F30),0)</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>ROUND(MIN(G56*$B$28,G14*G30),0)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>ROUND(MIN(H56*$B$28,H14*H30),0)</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>ROUND(MIN(I56*$B$28,I14*I30),0)</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>ROUND(MIN(J56*$B$28,J14*J30),0)</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>ROUND(MIN(K56*$B$28,K14*K30),0)</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>ROUND(MIN(L56*$B$28,L14*L30),0)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>ROUND(MIN(M56*$B$28,M14*M30),0)</f>
+        <v/>
+      </c>
+      <c r="N57">
         <f>SUM(B57:M57)</f>
         <v/>
       </c>
@@ -5261,55 +5242,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Сделок с B2C fee</t>
+          <t>Сделки на каталоге IS24</t>
         </is>
       </c>
       <c r="B58">
-        <f>B56+ROUND(B55*$B$37,0)</f>
+        <f>ROUND(B56*$B$29,0)</f>
         <v/>
       </c>
       <c r="C58">
-        <f>C56+ROUND(C55*$B$37,0)</f>
+        <f>ROUND(C56*$B$29,0)</f>
         <v/>
       </c>
       <c r="D58">
-        <f>D56+ROUND(D55*$B$37,0)</f>
+        <f>ROUND(D56*$B$29,0)</f>
         <v/>
       </c>
       <c r="E58">
-        <f>E56+ROUND(E55*$B$37,0)</f>
+        <f>ROUND(E56*$B$29,0)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>F56+ROUND(F55*$B$37,0)</f>
+        <f>ROUND(F56*$B$29,0)</f>
         <v/>
       </c>
       <c r="G58">
-        <f>G56+ROUND(G55*$B$37,0)</f>
+        <f>ROUND(G56*$B$29,0)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>H56+ROUND(H55*$B$37,0)</f>
+        <f>ROUND(H56*$B$29,0)</f>
         <v/>
       </c>
       <c r="I58">
-        <f>I56+ROUND(I55*$B$37,0)</f>
+        <f>ROUND(I56*$B$29,0)</f>
         <v/>
       </c>
       <c r="J58">
-        <f>J56+ROUND(J55*$B$37,0)</f>
+        <f>ROUND(J56*$B$29,0)</f>
         <v/>
       </c>
       <c r="K58">
-        <f>K56+ROUND(K55*$B$37,0)</f>
+        <f>ROUND(K56*$B$29,0)</f>
         <v/>
       </c>
       <c r="L58">
-        <f>L56+ROUND(L55*$B$37,0)</f>
+        <f>ROUND(L56*$B$29,0)</f>
         <v/>
       </c>
       <c r="M58">
-        <f>M56+ROUND(M55*$B$37,0)</f>
+        <f>ROUND(M56*$B$29,0)</f>
         <v/>
       </c>
       <c r="N58">
@@ -5317,183 +5298,183 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Сделок всего</t>
+        </is>
+      </c>
+      <c r="B59" s="6">
+        <f>B57+B58</f>
+        <v/>
+      </c>
+      <c r="C59" s="6">
+        <f>C57+C58</f>
+        <v/>
+      </c>
+      <c r="D59" s="6">
+        <f>D57+D58</f>
+        <v/>
+      </c>
+      <c r="E59" s="6">
+        <f>E57+E58</f>
+        <v/>
+      </c>
+      <c r="F59" s="6">
+        <f>F57+F58</f>
+        <v/>
+      </c>
+      <c r="G59" s="6">
+        <f>G57+G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="6">
+        <f>H57+H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="6">
+        <f>I57+I58</f>
+        <v/>
+      </c>
+      <c r="J59" s="6">
+        <f>J57+J58</f>
+        <v/>
+      </c>
+      <c r="K59" s="6">
+        <f>K57+K58</f>
+        <v/>
+      </c>
+      <c r="L59" s="6">
+        <f>L57+L58</f>
+        <v/>
+      </c>
+      <c r="M59" s="6">
+        <f>M57+M58</f>
+        <v/>
+      </c>
+      <c r="N59" s="6">
+        <f>SUM(B59:M59)</f>
+        <v/>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Сделок с B2C fee</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>B58+ROUND(B57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>C58+ROUND(C57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>D58+ROUND(D57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>E58+ROUND(E57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>F58+ROUND(F57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>G58+ROUND(G57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>H58+ROUND(H57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>I58+ROUND(I57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>J58+ROUND(J57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>K58+ROUND(K57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>L58+ROUND(L57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="M60">
+        <f>M58+ROUND(M57*$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>SUM(B60:M60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>ВЫРУЧКА</t>
         </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
-        </is>
-      </c>
-      <c r="B61">
-        <f>ROUND(B55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>ROUND(C55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>ROUND(D55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>ROUND(E55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="F61">
-        <f>ROUND(F55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="G61">
-        <f>ROUND(G55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="H61">
-        <f>ROUND(H55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="I61">
-        <f>ROUND(I55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="J61">
-        <f>ROUND(J55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="K61">
-        <f>ROUND(K55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="L61">
-        <f>ROUND(L55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="M61">
-        <f>ROUND(M55*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
-        <v/>
-      </c>
-      <c r="N61">
-        <f>SUM(B61:M61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>R3: B2C fee</t>
-        </is>
-      </c>
-      <c r="B62">
-        <f>B58*$B$36</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>C58*$B$36</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>D58*$B$36</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>E58*$B$36</f>
-        <v/>
-      </c>
-      <c r="F62">
-        <f>F58*$B$36</f>
-        <v/>
-      </c>
-      <c r="G62">
-        <f>G58*$B$36</f>
-        <v/>
-      </c>
-      <c r="H62">
-        <f>H58*$B$36</f>
-        <v/>
-      </c>
-      <c r="I62">
-        <f>I58*$B$36</f>
-        <v/>
-      </c>
-      <c r="J62">
-        <f>J58*$B$36</f>
-        <v/>
-      </c>
-      <c r="K62">
-        <f>K58*$B$36</f>
-        <v/>
-      </c>
-      <c r="L62">
-        <f>L58*$B$36</f>
-        <v/>
-      </c>
-      <c r="M62">
-        <f>M58*$B$36</f>
-        <v/>
-      </c>
-      <c r="N62">
-        <f>SUM(B62:M62)</f>
-        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R4: upsell</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B63">
-        <f>B39</f>
+        <f>ROUND(B57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>C39</f>
+        <f>ROUND(C57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="D63">
-        <f>D39</f>
+        <f>ROUND(D57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>E39</f>
+        <f>ROUND(E57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>F39</f>
+        <f>ROUND(F57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>G39</f>
+        <f>ROUND(G57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>H39</f>
+        <f>ROUND(H57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>I39</f>
+        <f>ROUND(I57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>J39</f>
+        <f>ROUND(J57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>K39</f>
+        <f>ROUND(K57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="L63">
-        <f>L39</f>
+        <f>ROUND(L57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="M63">
-        <f>M39</f>
+        <f>ROUND(M57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
         <v/>
       </c>
       <c r="N63">
@@ -5502,265 +5483,301 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R3: B2C fee</t>
+        </is>
+      </c>
+      <c r="B64">
+        <f>B60*$B$36</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>C60*$B$36</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>D60*$B$36</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>E60*$B$36</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>F60*$B$36</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>G60*$B$36</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>H60*$B$36</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>I60*$B$36</f>
+        <v/>
+      </c>
+      <c r="J64">
+        <f>J60*$B$36</f>
+        <v/>
+      </c>
+      <c r="K64">
+        <f>K60*$B$36</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>L60*$B$36</f>
+        <v/>
+      </c>
+      <c r="M64">
+        <f>M60*$B$36</f>
+        <v/>
+      </c>
+      <c r="N64">
+        <f>SUM(B64:M64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>B41</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>D41</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>F41</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>G41</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>H41</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>I41</f>
+        <v/>
+      </c>
+      <c r="J65">
+        <f>J41</f>
+        <v/>
+      </c>
+      <c r="K65">
+        <f>K41</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>L41</f>
+        <v/>
+      </c>
+      <c r="M65">
+        <f>M41</f>
+        <v/>
+      </c>
+      <c r="N65">
+        <f>SUM(B65:M65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>R5: реферал на мебель (Zolak)</t>
+        </is>
+      </c>
+      <c r="B66">
+        <f>ROUND(B59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>ROUND(C59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>ROUND(D59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>ROUND(E59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>ROUND(F59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>ROUND(G59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="H66">
+        <f>ROUND(H59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="I66">
+        <f>ROUND(I59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="J66">
+        <f>ROUND(J59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="K66">
+        <f>ROUND(K59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>ROUND(L59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="M66">
+        <f>ROUND(M59*$B$39*$B$40,0)</f>
+        <v/>
+      </c>
+      <c r="N66">
+        <f>SUM(B66:M66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B64" s="6">
-        <f>B61+B62+B63</f>
-        <v/>
-      </c>
-      <c r="C64" s="6">
-        <f>C61+C62+C63</f>
-        <v/>
-      </c>
-      <c r="D64" s="6">
-        <f>D61+D62+D63</f>
-        <v/>
-      </c>
-      <c r="E64" s="6">
-        <f>E61+E62+E63</f>
-        <v/>
-      </c>
-      <c r="F64" s="6">
-        <f>F61+F62+F63</f>
-        <v/>
-      </c>
-      <c r="G64" s="6">
-        <f>G61+G62+G63</f>
-        <v/>
-      </c>
-      <c r="H64" s="6">
-        <f>H61+H62+H63</f>
-        <v/>
-      </c>
-      <c r="I64" s="6">
-        <f>I61+I62+I63</f>
-        <v/>
-      </c>
-      <c r="J64" s="6">
-        <f>J61+J62+J63</f>
-        <v/>
-      </c>
-      <c r="K64" s="6">
-        <f>K61+K62+K63</f>
-        <v/>
-      </c>
-      <c r="L64" s="6">
-        <f>L61+L62+L63</f>
-        <v/>
-      </c>
-      <c r="M64" s="6">
-        <f>M61+M62+M63</f>
-        <v/>
-      </c>
-      <c r="N64" s="6">
-        <f>SUM(B64:M64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B67" s="6">
+        <f>B63+B64+B65+B66</f>
+        <v/>
+      </c>
+      <c r="C67" s="6">
+        <f>C63+C64+C65+C66</f>
+        <v/>
+      </c>
+      <c r="D67" s="6">
+        <f>D63+D64+D65+D66</f>
+        <v/>
+      </c>
+      <c r="E67" s="6">
+        <f>E63+E64+E65+E66</f>
+        <v/>
+      </c>
+      <c r="F67" s="6">
+        <f>F63+F64+F65+F66</f>
+        <v/>
+      </c>
+      <c r="G67" s="6">
+        <f>G63+G64+G65+G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="6">
+        <f>H63+H64+H65+H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="6">
+        <f>I63+I64+I65+I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="6">
+        <f>J63+J64+J65+J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="6">
+        <f>K63+K64+K65+K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="6">
+        <f>L63+L64+L65+L66</f>
+        <v/>
+      </c>
+      <c r="M67" s="6">
+        <f>M63+M64+M65+M66</f>
+        <v/>
+      </c>
+      <c r="N67" s="6">
+        <f>SUM(B67:M67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B67">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C67">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D67">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E67">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F67">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G67">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H67">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I67">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J67">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K67">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L67">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M67">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N67">
-        <f>SUM(B67:M67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M68" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="N68">
-        <f>SUM(B68:M68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>1073</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>1218</v>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>1291</v>
-      </c>
-      <c r="G69" s="8" t="n">
-        <v>1364</v>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>1436</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>1509</v>
-      </c>
-      <c r="J69" s="8" t="n">
-        <v>1582</v>
-      </c>
-      <c r="K69" s="8" t="n">
-        <v>1655</v>
-      </c>
-      <c r="L69" s="8" t="n">
-        <v>1727</v>
-      </c>
-      <c r="M69" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N69">
-        <f>SUM(B69:M69)</f>
-        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J70" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K70" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="L70" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M70" s="8" t="n">
-        <v>4500</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B70">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H70">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J70">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K70">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M70">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N70">
         <f>SUM(B70:M70)</f>
@@ -5770,44 +5787,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>1150</v>
+        <v>500</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="N71">
         <f>SUM(B71:M71)</f>
@@ -5817,44 +5834,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C72" s="8" t="n">
-        <v>500</v>
+        <v>1073</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>500</v>
+        <v>1145</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>600</v>
+        <v>1218</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>600</v>
+        <v>1291</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>600</v>
+        <v>1364</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>700</v>
+        <v>1436</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>700</v>
+        <v>1509</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>700</v>
+        <v>1582</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>800</v>
+        <v>1655</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>800</v>
+        <v>1727</v>
       </c>
       <c r="M72" s="8" t="n">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="N72">
         <f>SUM(B72:M72)</f>
@@ -5864,56 +5881,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B73">
-        <f>ROUND(B61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C73">
-        <f>ROUND(C61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D73">
-        <f>ROUND(D61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E73">
-        <f>ROUND(E61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F73">
-        <f>ROUND(F61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G73">
-        <f>ROUND(G61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H73">
-        <f>ROUND(H61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I73">
-        <f>ROUND(I61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J73">
-        <f>ROUND(J61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K73">
-        <f>ROUND(K61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L73">
-        <f>ROUND(L61*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M73">
-        <f>ROUND(M61*$B$38,0)</f>
-        <v/>
+          <t>Команда: dev / support (контракторы)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>4500</v>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -5921,226 +5926,379 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N74">
+        <f>SUM(B74:M74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N75">
+        <f>SUM(B75:M75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B76">
+        <f>ROUND(B63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>ROUND(C63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>ROUND(D63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>ROUND(E63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>ROUND(F63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>ROUND(G63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>ROUND(H63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>ROUND(I63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>ROUND(J63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K76">
+        <f>ROUND(K63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>ROUND(L63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M76">
+        <f>ROUND(M63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N76">
+        <f>SUM(B76:M76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>TOTAL COSTS</t>
         </is>
       </c>
-      <c r="B74" s="6">
-        <f>B67+B68+B69+B70+B71+B72+B73</f>
-        <v/>
-      </c>
-      <c r="C74" s="6">
-        <f>C67+C68+C69+C70+C71+C72+C73</f>
-        <v/>
-      </c>
-      <c r="D74" s="6">
-        <f>D67+D68+D69+D70+D71+D72+D73</f>
-        <v/>
-      </c>
-      <c r="E74" s="6">
-        <f>E67+E68+E69+E70+E71+E72+E73</f>
-        <v/>
-      </c>
-      <c r="F74" s="6">
-        <f>F67+F68+F69+F70+F71+F72+F73</f>
-        <v/>
-      </c>
-      <c r="G74" s="6">
-        <f>G67+G68+G69+G70+G71+G72+G73</f>
-        <v/>
-      </c>
-      <c r="H74" s="6">
-        <f>H67+H68+H69+H70+H71+H72+H73</f>
-        <v/>
-      </c>
-      <c r="I74" s="6">
-        <f>I67+I68+I69+I70+I71+I72+I73</f>
-        <v/>
-      </c>
-      <c r="J74" s="6">
-        <f>J67+J68+J69+J70+J71+J72+J73</f>
-        <v/>
-      </c>
-      <c r="K74" s="6">
-        <f>K67+K68+K69+K70+K71+K72+K73</f>
-        <v/>
-      </c>
-      <c r="L74" s="6">
-        <f>L67+L68+L69+L70+L71+L72+L73</f>
-        <v/>
-      </c>
-      <c r="M74" s="6">
-        <f>M67+M68+M69+M70+M71+M72+M73</f>
-        <v/>
-      </c>
-      <c r="N74" s="6">
-        <f>SUM(B74:M74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="B77" s="6">
+        <f>B70+B71+B72+B73+B74+B75+B76</f>
+        <v/>
+      </c>
+      <c r="C77" s="6">
+        <f>C70+C71+C72+C73+C74+C75+C76</f>
+        <v/>
+      </c>
+      <c r="D77" s="6">
+        <f>D70+D71+D72+D73+D74+D75+D76</f>
+        <v/>
+      </c>
+      <c r="E77" s="6">
+        <f>E70+E71+E72+E73+E74+E75+E76</f>
+        <v/>
+      </c>
+      <c r="F77" s="6">
+        <f>F70+F71+F72+F73+F74+F75+F76</f>
+        <v/>
+      </c>
+      <c r="G77" s="6">
+        <f>G70+G71+G72+G73+G74+G75+G76</f>
+        <v/>
+      </c>
+      <c r="H77" s="6">
+        <f>H70+H71+H72+H73+H74+H75+H76</f>
+        <v/>
+      </c>
+      <c r="I77" s="6">
+        <f>I70+I71+I72+I73+I74+I75+I76</f>
+        <v/>
+      </c>
+      <c r="J77" s="6">
+        <f>J70+J71+J72+J73+J74+J75+J76</f>
+        <v/>
+      </c>
+      <c r="K77" s="6">
+        <f>K70+K71+K72+K73+K74+K75+K76</f>
+        <v/>
+      </c>
+      <c r="L77" s="6">
+        <f>L70+L71+L72+L73+L74+L75+L76</f>
+        <v/>
+      </c>
+      <c r="M77" s="6">
+        <f>M70+M71+M72+M73+M74+M75+M76</f>
+        <v/>
+      </c>
+      <c r="N77" s="6">
+        <f>SUM(B77:M77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B76" s="6">
-        <f>B64-B74</f>
-        <v/>
-      </c>
-      <c r="C76" s="6">
-        <f>C64-C74</f>
-        <v/>
-      </c>
-      <c r="D76" s="6">
-        <f>D64-D74</f>
-        <v/>
-      </c>
-      <c r="E76" s="6">
-        <f>E64-E74</f>
-        <v/>
-      </c>
-      <c r="F76" s="6">
-        <f>F64-F74</f>
-        <v/>
-      </c>
-      <c r="G76" s="6">
-        <f>G64-G74</f>
-        <v/>
-      </c>
-      <c r="H76" s="6">
-        <f>H64-H74</f>
-        <v/>
-      </c>
-      <c r="I76" s="6">
-        <f>I64-I74</f>
-        <v/>
-      </c>
-      <c r="J76" s="6">
-        <f>J64-J74</f>
-        <v/>
-      </c>
-      <c r="K76" s="6">
-        <f>K64-K74</f>
-        <v/>
-      </c>
-      <c r="L76" s="6">
-        <f>L64-L74</f>
-        <v/>
-      </c>
-      <c r="M76" s="6">
-        <f>M64-M74</f>
-        <v/>
-      </c>
-      <c r="N76" s="6">
-        <f>SUM(B76:M76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Кэш (старт €18,000)</t>
-        </is>
-      </c>
-      <c r="B77">
-        <f>18000+B76</f>
-        <v/>
-      </c>
-      <c r="C77">
-        <f>B77+C76</f>
-        <v/>
-      </c>
-      <c r="D77">
-        <f>C77+D76</f>
-        <v/>
-      </c>
-      <c r="E77">
-        <f>D77+E76</f>
-        <v/>
-      </c>
-      <c r="F77">
-        <f>E77+F76</f>
-        <v/>
-      </c>
-      <c r="G77">
-        <f>F77+G76</f>
-        <v/>
-      </c>
-      <c r="H77">
-        <f>G77+H76</f>
-        <v/>
-      </c>
-      <c r="I77">
-        <f>H77+I76</f>
-        <v/>
-      </c>
-      <c r="J77">
-        <f>I77+J76</f>
-        <v/>
-      </c>
-      <c r="K77">
-        <f>J77+K76</f>
-        <v/>
-      </c>
-      <c r="L77">
-        <f>K77+L76</f>
-        <v/>
-      </c>
-      <c r="M77">
-        <f>L77+M76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
-        </is>
+      <c r="B79" s="6">
+        <f>B67-B77</f>
+        <v/>
+      </c>
+      <c r="C79" s="6">
+        <f>C67-C77</f>
+        <v/>
+      </c>
+      <c r="D79" s="6">
+        <f>D67-D77</f>
+        <v/>
+      </c>
+      <c r="E79" s="6">
+        <f>E67-E77</f>
+        <v/>
+      </c>
+      <c r="F79" s="6">
+        <f>F67-F77</f>
+        <v/>
+      </c>
+      <c r="G79" s="6">
+        <f>G67-G77</f>
+        <v/>
+      </c>
+      <c r="H79" s="6">
+        <f>H67-H77</f>
+        <v/>
+      </c>
+      <c r="I79" s="6">
+        <f>I67-I77</f>
+        <v/>
+      </c>
+      <c r="J79" s="6">
+        <f>J67-J77</f>
+        <v/>
+      </c>
+      <c r="K79" s="6">
+        <f>K67-K77</f>
+        <v/>
+      </c>
+      <c r="L79" s="6">
+        <f>L67-L77</f>
+        <v/>
+      </c>
+      <c r="M79" s="6">
+        <f>M67-M77</f>
+        <v/>
+      </c>
+      <c r="N79" s="6">
+        <f>SUM(B79:M79)</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAC на квалифицированного лида, €</t>
+          <t>Кэш (старт €18,000)</t>
         </is>
       </c>
       <c r="B80">
-        <f>ROUND(N6/N54,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B81">
-        <f>ROUND(N6/N57,0)</f>
+        <f>18000+B79</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>B80+C79</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>C80+D79</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>D80+E79</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>E80+F79</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>F80+G79</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>G80+H79</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>H80+I79</f>
+        <v/>
+      </c>
+      <c r="J80">
+        <f>I80+J79</f>
+        <v/>
+      </c>
+      <c r="K80">
+        <f>J80+K79</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>K80+L79</f>
+        <v/>
+      </c>
+      <c r="M80">
+        <f>L80+M79</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Выручка на агентскую сделку, €</t>
-        </is>
-      </c>
-      <c r="B82">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
-        <v/>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>CAC на квалифицированного лида, €</t>
+        </is>
+      </c>
+      <c r="B83">
+        <f>ROUND(N6/N56,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B84">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B85">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B83">
-        <f>ROUND(B82/B81,1)</f>
+      <c r="B86">
+        <f>ROUND(B85/B84,1)</f>
         <v/>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3299,44 +3299,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
+          <t>Backend-контрактор (доработки, фичи)</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="M73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -3346,44 +3346,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E74" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="C74" s="8" t="n">
-        <v>750</v>
-      </c>
-      <c r="D74" s="8" t="n">
+      <c r="F74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H74" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="E74" s="8" t="n">
-        <v>850</v>
-      </c>
-      <c r="F74" s="8" t="n">
+      <c r="I74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="K74" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="G74" s="8" t="n">
-        <v>950</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="J74" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>1150</v>
-      </c>
       <c r="L74" s="8" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>1250</v>
+        <v>900</v>
       </c>
       <c r="N74">
         <f>SUM(B74:M74)</f>
@@ -3393,44 +3393,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Support/ops (B2C + агентства)</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N75">
         <f>SUM(B75:M75)</f>
@@ -3440,56 +3440,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B76">
-        <f>ROUND(B63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C76">
-        <f>ROUND(C63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D76">
-        <f>ROUND(D63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E76">
-        <f>ROUND(E63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F76">
-        <f>ROUND(F63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G76">
-        <f>ROUND(G63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H76">
-        <f>ROUND(H63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I76">
-        <f>ROUND(I63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J76">
-        <f>ROUND(J63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K76">
-        <f>ROUND(K63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L76">
-        <f>ROUND(L63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M76">
-        <f>ROUND(M63*$B$38,0)</f>
-        <v/>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K76" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M76" s="8" t="n">
+        <v>1250</v>
       </c>
       <c r="N76">
         <f>SUM(B76:M76)</f>
@@ -3497,116 +3485,163 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="B77" s="6">
-        <f>B70+B71+B72+B73+B74+B75+B76</f>
-        <v/>
-      </c>
-      <c r="C77" s="6">
-        <f>C70+C71+C72+C73+C74+C75+C76</f>
-        <v/>
-      </c>
-      <c r="D77" s="6">
-        <f>D70+D71+D72+D73+D74+D75+D76</f>
-        <v/>
-      </c>
-      <c r="E77" s="6">
-        <f>E70+E71+E72+E73+E74+E75+E76</f>
-        <v/>
-      </c>
-      <c r="F77" s="6">
-        <f>F70+F71+F72+F73+F74+F75+F76</f>
-        <v/>
-      </c>
-      <c r="G77" s="6">
-        <f>G70+G71+G72+G73+G74+G75+G76</f>
-        <v/>
-      </c>
-      <c r="H77" s="6">
-        <f>H70+H71+H72+H73+H74+H75+H76</f>
-        <v/>
-      </c>
-      <c r="I77" s="6">
-        <f>I70+I71+I72+I73+I74+I75+I76</f>
-        <v/>
-      </c>
-      <c r="J77" s="6">
-        <f>J70+J71+J72+J73+J74+J75+J76</f>
-        <v/>
-      </c>
-      <c r="K77" s="6">
-        <f>K70+K71+K72+K73+K74+K75+K76</f>
-        <v/>
-      </c>
-      <c r="L77" s="6">
-        <f>L70+L71+L72+L73+L74+L75+L76</f>
-        <v/>
-      </c>
-      <c r="M77" s="6">
-        <f>M70+M71+M72+M73+M74+M75+M76</f>
-        <v/>
-      </c>
-      <c r="N77" s="6">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N77">
         <f>SUM(B77:M77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B78">
+        <f>ROUND(B63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>ROUND(C63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>ROUND(D63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>ROUND(E63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>ROUND(F63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>ROUND(G63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>ROUND(H63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>ROUND(I63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J78">
+        <f>ROUND(J63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K78">
+        <f>ROUND(K63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>ROUND(L63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M78">
+        <f>ROUND(M63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N78">
+        <f>SUM(B78:M78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>TOTAL COSTS</t>
         </is>
       </c>
       <c r="B79" s="6">
-        <f>B67-B77</f>
+        <f>B70+B71+B72+B73+B74+B75+B76+B77+B78</f>
         <v/>
       </c>
       <c r="C79" s="6">
-        <f>C67-C77</f>
+        <f>C70+C71+C72+C73+C74+C75+C76+C77+C78</f>
         <v/>
       </c>
       <c r="D79" s="6">
-        <f>D67-D77</f>
+        <f>D70+D71+D72+D73+D74+D75+D76+D77+D78</f>
         <v/>
       </c>
       <c r="E79" s="6">
-        <f>E67-E77</f>
+        <f>E70+E71+E72+E73+E74+E75+E76+E77+E78</f>
         <v/>
       </c>
       <c r="F79" s="6">
-        <f>F67-F77</f>
+        <f>F70+F71+F72+F73+F74+F75+F76+F77+F78</f>
         <v/>
       </c>
       <c r="G79" s="6">
-        <f>G67-G77</f>
+        <f>G70+G71+G72+G73+G74+G75+G76+G77+G78</f>
         <v/>
       </c>
       <c r="H79" s="6">
-        <f>H67-H77</f>
+        <f>H70+H71+H72+H73+H74+H75+H76+H77+H78</f>
         <v/>
       </c>
       <c r="I79" s="6">
-        <f>I67-I77</f>
+        <f>I70+I71+I72+I73+I74+I75+I76+I77+I78</f>
         <v/>
       </c>
       <c r="J79" s="6">
-        <f>J67-J77</f>
+        <f>J70+J71+J72+J73+J74+J75+J76+J77+J78</f>
         <v/>
       </c>
       <c r="K79" s="6">
-        <f>K67-K77</f>
+        <f>K70+K71+K72+K73+K74+K75+K76+K77+K78</f>
         <v/>
       </c>
       <c r="L79" s="6">
-        <f>L67-L77</f>
+        <f>L70+L71+L72+L73+L74+L75+L76+L77+L78</f>
         <v/>
       </c>
       <c r="M79" s="6">
-        <f>M67-M77</f>
+        <f>M70+M71+M72+M73+M74+M75+M76+M77+M78</f>
         <v/>
       </c>
       <c r="N79" s="6">
@@ -3614,109 +3649,168 @@
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B81" s="6">
+        <f>B67-B79</f>
+        <v/>
+      </c>
+      <c r="C81" s="6">
+        <f>C67-C79</f>
+        <v/>
+      </c>
+      <c r="D81" s="6">
+        <f>D67-D79</f>
+        <v/>
+      </c>
+      <c r="E81" s="6">
+        <f>E67-E79</f>
+        <v/>
+      </c>
+      <c r="F81" s="6">
+        <f>F67-F79</f>
+        <v/>
+      </c>
+      <c r="G81" s="6">
+        <f>G67-G79</f>
+        <v/>
+      </c>
+      <c r="H81" s="6">
+        <f>H67-H79</f>
+        <v/>
+      </c>
+      <c r="I81" s="6">
+        <f>I67-I79</f>
+        <v/>
+      </c>
+      <c r="J81" s="6">
+        <f>J67-J79</f>
+        <v/>
+      </c>
+      <c r="K81" s="6">
+        <f>K67-K79</f>
+        <v/>
+      </c>
+      <c r="L81" s="6">
+        <f>L67-L79</f>
+        <v/>
+      </c>
+      <c r="M81" s="6">
+        <f>M67-M79</f>
+        <v/>
+      </c>
+      <c r="N81" s="6">
+        <f>SUM(B81:M81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Кэш (старт €18,000)</t>
         </is>
       </c>
-      <c r="B80">
-        <f>18000+B79</f>
-        <v/>
-      </c>
-      <c r="C80">
-        <f>B80+C79</f>
-        <v/>
-      </c>
-      <c r="D80">
-        <f>C80+D79</f>
-        <v/>
-      </c>
-      <c r="E80">
-        <f>D80+E79</f>
-        <v/>
-      </c>
-      <c r="F80">
-        <f>E80+F79</f>
-        <v/>
-      </c>
-      <c r="G80">
-        <f>F80+G79</f>
-        <v/>
-      </c>
-      <c r="H80">
-        <f>G80+H79</f>
-        <v/>
-      </c>
-      <c r="I80">
-        <f>H80+I79</f>
-        <v/>
-      </c>
-      <c r="J80">
-        <f>I80+J79</f>
-        <v/>
-      </c>
-      <c r="K80">
-        <f>J80+K79</f>
-        <v/>
-      </c>
-      <c r="L80">
-        <f>K80+L79</f>
-        <v/>
-      </c>
-      <c r="M80">
-        <f>L80+M79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B82">
+        <f>18000+B81</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>B82+C81</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>C82+D81</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>D82+E81</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>E82+F81</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>F82+G81</f>
+        <v/>
+      </c>
+      <c r="H82">
+        <f>G82+H81</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>H82+I81</f>
+        <v/>
+      </c>
+      <c r="J82">
+        <f>I82+J81</f>
+        <v/>
+      </c>
+      <c r="K82">
+        <f>J82+K81</f>
+        <v/>
+      </c>
+      <c r="L82">
+        <f>K82+L81</f>
+        <v/>
+      </c>
+      <c r="M82">
+        <f>L82+M81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>ЮНИТ-ЭКОНОМИКА (год)</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>CAC на квалифицированного лида, €</t>
-        </is>
-      </c>
-      <c r="B83">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B84">
-        <f>ROUND(N6/N59,0)</f>
-        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Выручка на агентскую сделку, €</t>
+          <t>CAC на квалифицированного лида, €</t>
         </is>
       </c>
       <c r="B85">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <f>ROUND(N6/N56,0)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B86">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B87">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B86">
-        <f>ROUND(B85/B84,1)</f>
+      <c r="B88">
+        <f>ROUND(B87/B86,1)</f>
         <v/>
       </c>
     </row>
@@ -3731,7 +3825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5881,44 +5975,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Команда: dev / support (контракторы)</t>
+          <t>Backend-контрактор (доработки, фичи)</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>3500</v>
+        <v>2100</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="M73" s="8" t="n">
-        <v>4500</v>
+        <v>2700</v>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -5928,44 +6022,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E74" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="C74" s="8" t="n">
-        <v>750</v>
-      </c>
-      <c r="D74" s="8" t="n">
+      <c r="F74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H74" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="E74" s="8" t="n">
-        <v>850</v>
-      </c>
-      <c r="F74" s="8" t="n">
+      <c r="I74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="K74" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="G74" s="8" t="n">
-        <v>950</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="J74" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>1150</v>
-      </c>
       <c r="L74" s="8" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>1250</v>
+        <v>900</v>
       </c>
       <c r="N74">
         <f>SUM(B74:M74)</f>
@@ -5975,44 +6069,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Support/ops (B2C + агентства)</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M75" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N75">
         <f>SUM(B75:M75)</f>
@@ -6022,56 +6116,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B76">
-        <f>ROUND(B63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C76">
-        <f>ROUND(C63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D76">
-        <f>ROUND(D63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E76">
-        <f>ROUND(E63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F76">
-        <f>ROUND(F63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G76">
-        <f>ROUND(G63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H76">
-        <f>ROUND(H63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I76">
-        <f>ROUND(I63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J76">
-        <f>ROUND(J63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K76">
-        <f>ROUND(K63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L76">
-        <f>ROUND(L63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M76">
-        <f>ROUND(M63*$B$38,0)</f>
-        <v/>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K76" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M76" s="8" t="n">
+        <v>1250</v>
       </c>
       <c r="N76">
         <f>SUM(B76:M76)</f>
@@ -6079,116 +6161,163 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="B77" s="6">
-        <f>B70+B71+B72+B73+B74+B75+B76</f>
-        <v/>
-      </c>
-      <c r="C77" s="6">
-        <f>C70+C71+C72+C73+C74+C75+C76</f>
-        <v/>
-      </c>
-      <c r="D77" s="6">
-        <f>D70+D71+D72+D73+D74+D75+D76</f>
-        <v/>
-      </c>
-      <c r="E77" s="6">
-        <f>E70+E71+E72+E73+E74+E75+E76</f>
-        <v/>
-      </c>
-      <c r="F77" s="6">
-        <f>F70+F71+F72+F73+F74+F75+F76</f>
-        <v/>
-      </c>
-      <c r="G77" s="6">
-        <f>G70+G71+G72+G73+G74+G75+G76</f>
-        <v/>
-      </c>
-      <c r="H77" s="6">
-        <f>H70+H71+H72+H73+H74+H75+H76</f>
-        <v/>
-      </c>
-      <c r="I77" s="6">
-        <f>I70+I71+I72+I73+I74+I75+I76</f>
-        <v/>
-      </c>
-      <c r="J77" s="6">
-        <f>J70+J71+J72+J73+J74+J75+J76</f>
-        <v/>
-      </c>
-      <c r="K77" s="6">
-        <f>K70+K71+K72+K73+K74+K75+K76</f>
-        <v/>
-      </c>
-      <c r="L77" s="6">
-        <f>L70+L71+L72+L73+L74+L75+L76</f>
-        <v/>
-      </c>
-      <c r="M77" s="6">
-        <f>M70+M71+M72+M73+M74+M75+M76</f>
-        <v/>
-      </c>
-      <c r="N77" s="6">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N77">
         <f>SUM(B77:M77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B78">
+        <f>ROUND(B63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>ROUND(C63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>ROUND(D63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>ROUND(E63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>ROUND(F63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>ROUND(G63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>ROUND(H63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>ROUND(I63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="J78">
+        <f>ROUND(J63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="K78">
+        <f>ROUND(K63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>ROUND(L63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="M78">
+        <f>ROUND(M63*$B$38,0)</f>
+        <v/>
+      </c>
+      <c r="N78">
+        <f>SUM(B78:M78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>TOTAL COSTS</t>
         </is>
       </c>
       <c r="B79" s="6">
-        <f>B67-B77</f>
+        <f>B70+B71+B72+B73+B74+B75+B76+B77+B78</f>
         <v/>
       </c>
       <c r="C79" s="6">
-        <f>C67-C77</f>
+        <f>C70+C71+C72+C73+C74+C75+C76+C77+C78</f>
         <v/>
       </c>
       <c r="D79" s="6">
-        <f>D67-D77</f>
+        <f>D70+D71+D72+D73+D74+D75+D76+D77+D78</f>
         <v/>
       </c>
       <c r="E79" s="6">
-        <f>E67-E77</f>
+        <f>E70+E71+E72+E73+E74+E75+E76+E77+E78</f>
         <v/>
       </c>
       <c r="F79" s="6">
-        <f>F67-F77</f>
+        <f>F70+F71+F72+F73+F74+F75+F76+F77+F78</f>
         <v/>
       </c>
       <c r="G79" s="6">
-        <f>G67-G77</f>
+        <f>G70+G71+G72+G73+G74+G75+G76+G77+G78</f>
         <v/>
       </c>
       <c r="H79" s="6">
-        <f>H67-H77</f>
+        <f>H70+H71+H72+H73+H74+H75+H76+H77+H78</f>
         <v/>
       </c>
       <c r="I79" s="6">
-        <f>I67-I77</f>
+        <f>I70+I71+I72+I73+I74+I75+I76+I77+I78</f>
         <v/>
       </c>
       <c r="J79" s="6">
-        <f>J67-J77</f>
+        <f>J70+J71+J72+J73+J74+J75+J76+J77+J78</f>
         <v/>
       </c>
       <c r="K79" s="6">
-        <f>K67-K77</f>
+        <f>K70+K71+K72+K73+K74+K75+K76+K77+K78</f>
         <v/>
       </c>
       <c r="L79" s="6">
-        <f>L67-L77</f>
+        <f>L70+L71+L72+L73+L74+L75+L76+L77+L78</f>
         <v/>
       </c>
       <c r="M79" s="6">
-        <f>M67-M77</f>
+        <f>M70+M71+M72+M73+M74+M75+M76+M77+M78</f>
         <v/>
       </c>
       <c r="N79" s="6">
@@ -6196,109 +6325,168 @@
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B81" s="6">
+        <f>B67-B79</f>
+        <v/>
+      </c>
+      <c r="C81" s="6">
+        <f>C67-C79</f>
+        <v/>
+      </c>
+      <c r="D81" s="6">
+        <f>D67-D79</f>
+        <v/>
+      </c>
+      <c r="E81" s="6">
+        <f>E67-E79</f>
+        <v/>
+      </c>
+      <c r="F81" s="6">
+        <f>F67-F79</f>
+        <v/>
+      </c>
+      <c r="G81" s="6">
+        <f>G67-G79</f>
+        <v/>
+      </c>
+      <c r="H81" s="6">
+        <f>H67-H79</f>
+        <v/>
+      </c>
+      <c r="I81" s="6">
+        <f>I67-I79</f>
+        <v/>
+      </c>
+      <c r="J81" s="6">
+        <f>J67-J79</f>
+        <v/>
+      </c>
+      <c r="K81" s="6">
+        <f>K67-K79</f>
+        <v/>
+      </c>
+      <c r="L81" s="6">
+        <f>L67-L79</f>
+        <v/>
+      </c>
+      <c r="M81" s="6">
+        <f>M67-M79</f>
+        <v/>
+      </c>
+      <c r="N81" s="6">
+        <f>SUM(B81:M81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Кэш (старт €18,000)</t>
         </is>
       </c>
-      <c r="B80">
-        <f>18000+B79</f>
-        <v/>
-      </c>
-      <c r="C80">
-        <f>B80+C79</f>
-        <v/>
-      </c>
-      <c r="D80">
-        <f>C80+D79</f>
-        <v/>
-      </c>
-      <c r="E80">
-        <f>D80+E79</f>
-        <v/>
-      </c>
-      <c r="F80">
-        <f>E80+F79</f>
-        <v/>
-      </c>
-      <c r="G80">
-        <f>F80+G79</f>
-        <v/>
-      </c>
-      <c r="H80">
-        <f>G80+H79</f>
-        <v/>
-      </c>
-      <c r="I80">
-        <f>H80+I79</f>
-        <v/>
-      </c>
-      <c r="J80">
-        <f>I80+J79</f>
-        <v/>
-      </c>
-      <c r="K80">
-        <f>J80+K79</f>
-        <v/>
-      </c>
-      <c r="L80">
-        <f>K80+L79</f>
-        <v/>
-      </c>
-      <c r="M80">
-        <f>L80+M79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B82">
+        <f>18000+B81</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>B82+C81</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>C82+D81</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>D82+E81</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>E82+F81</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>F82+G81</f>
+        <v/>
+      </c>
+      <c r="H82">
+        <f>G82+H81</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>H82+I81</f>
+        <v/>
+      </c>
+      <c r="J82">
+        <f>I82+J81</f>
+        <v/>
+      </c>
+      <c r="K82">
+        <f>J82+K81</f>
+        <v/>
+      </c>
+      <c r="L82">
+        <f>K82+L81</f>
+        <v/>
+      </c>
+      <c r="M82">
+        <f>L82+M81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>ЮНИТ-ЭКОНОМИКА (год)</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>CAC на квалифицированного лида, €</t>
-        </is>
-      </c>
-      <c r="B83">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B84">
-        <f>ROUND(N6/N59,0)</f>
-        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Выручка на агентскую сделку, €</t>
+          <t>CAC на квалифицированного лида, €</t>
         </is>
       </c>
       <c r="B85">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <f>ROUND(N6/N56,0)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B86">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B87">
+        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B86">
-        <f>ROUND(B85/B84,1)</f>
+      <c r="B88">
+        <f>ROUND(B87/B86,1)</f>
         <v/>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 35%] Только узкие запросы («Wohnung Berlin ohne Schufa», «apartment berlin english») и ретаргетинг. Кран, а не основа.</t>
+          <t>[квалификация 35%] Узкие запросы и ретаргетинг. Кран, а не основа.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 22%] FB «Berlin Housing», r/berlin, Telegram, Toytown. Дёшево и горячо, но часто нет немецких документов о доходе — квалификация ~22%. Для них шаг «доведение документов»: Bürgschaft, письмо работодателя, Schufa через нас.</t>
+          <t>[квалификация 22%] FB, r/berlin, Telegram. Дёшево, но часто без немецких доходных справок.</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 100%] HR берлинских стартапов, международные офисы TU/HU/FU, буткемпы. Приходят с датой въезда и подтверждённым работодателем доходом — уже квалифицированы.</t>
+          <t>[квалификация 100%] HR стартапов, вузы. Приходят с датой въезда и доходом — уже квалифицированы.</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 40%] Программные страницы район × комнаты × бюджет (DE + EN) на данных парсинга IS24/Immowelt — это как человек нас находит через поиск, а не то, что он снимет. Внутри у него доступ и к каталогу, и к эксклюзивам агентств — сам каталог для сделок слабый (остатки, не разобранные в CRM), но именно поэтому большинство таких лидов закрывается через эксклюзив, а не через объявление, которое их привело.</t>
+          <t>[квалификация 40%] Гео-страницы на данных парсинга — способ найти нас, а не ограничение на сделку: внутри доступны и каталог, и эксклюзивы.</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 50%] Каждый заселённый знает пятерых ищущих. Бесплатный месяц мониторинга за приведённого, кто подписал.</t>
+          <t>[квалификация 50%] Заселённый клиент приводит следующего — месяц мониторинга в подарок.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 50%] Эксклюзивы из CRM в топе выдачи + агентства шлют свои waiting-list'ы на страницу объекта у нас. Интент на конкретную квартиру.</t>
+          <t>[квалификация 50%] Эксклюзивы в топе выдачи + агентства шлют свой waiting-list к нам.</t>
         </is>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Model" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Apr-Aug (USD)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE — Берлин" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PESSIMISTIC — Берлин" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE - Берлин" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PESSIMISTIC - Берлин" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>book.immo — Business Model v2</t>
+          <t>book.immo - Business Model v2</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Берлин — стартовый рынок, затем другие города Германии</t>
+          <t>Берлин - стартовый рынок, затем другие города Германии</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CRM агентства выгружает на IS24 то, что не ушло по своей базе. Хорошие объекты на витрину не доходят. book.immo получает их из CRM до публикации — бесплатно для агентства, за сплит комиссии при сделке.</t>
+          <t>CRM агентства выгружает на IS24 то, что не ушло по своей базе. Хорошие объекты на витрину не доходят. book.immo получает их из CRM до публикации - бесплатно для агентства, за сплит комиссии при сделке.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Парсинг — для полноты каталога и SEO-трафика, не для сделок: там остатки.</t>
+          <t>Парсинг - для полноты каталога и SEO-трафика, не для сделок: там остатки.</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 100%] HR стартапов, вузы. Приходят с датой въезда и доходом — уже квалифицированы.</t>
+          <t>[квалификация 100%] HR стартапов, вузы. Приходят с датой въезда и доходом - уже квалифицированы.</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 40%] Гео-страницы на данных парсинга — способ найти нас, а не ограничение на сделку: внутри доступны и каталог, и эксклюзивы.</t>
+          <t>[квалификация 40%] Гео-страницы на данных парсинга - способ найти нас, а не ограничение на сделку: внутри доступны и каталог, и эксклюзивы.</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>[квалификация 50%] Заселённый клиент приводит следующего — месяц мониторинга в подарок.</t>
+          <t>[квалификация 50%] Заселённый клиент приводит следующего - месяц мониторинга в подарок.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Бесплатный ИИ-пакет документов: доход, состав семьи, дата въезда вводятся, чтобы его получить — квалификация на входе</t>
+          <t>Бесплатный ИИ-пакет документов: доход, состав семьи, дата въезда вводятся, чтобы его получить - квалификация на входе</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Schufa-готовность, доход ≥ 3× Kaltmiete. Экспатам без немецких справок — Bürgschaft/гарант, письмо работодателя, Schufa через нас</t>
+          <t>Schufa-готовность, доход ≥ 3× Kaltmiete. Экспатам без немецких справок - Bürgschaft/гарант, письмо работодателя, Schufa через нас</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Монитор + полный пакет → подача сразу после публикации. На эксклюзивы агентств — приоритетно, на каталог IS24 — как страховка</t>
+          <t>Монитор + полный пакет → подача сразу после публикации. На эксклюзивы агентств - приоритетно, на каталог IS24 - как страховка</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Только квалифицированные и только под конкретный эксклюзив — агентство не тратит время на шум</t>
+          <t>Только квалифицированные и только под конкретный эксклюзив - агентство не тратит время на шум</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Подписание через агентство (сплит комиссии). Закрытия на остатках IS24 — редкие, только B2C fee</t>
+          <t>Подписание через агентство (сплит комиссии). Закрытия на остатках IS24 - редкие, только B2C fee</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Нельзя брать с арендатора комиссию за посредничество. B2C fee — плата за софт (автозаявки, мониторинг, документы). Нужен письменный legal opinion до запуска.</t>
+          <t>Нельзя брать с арендатора комиссию за посредничество. B2C fee - плата за софт (автозаявки, мониторинг, документы). Нужен письменный legal opinion до запуска.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Комиссию платит собственник маклеру. Сплит book.immo — из B2B-агентского договора. Легально.</t>
+          <t>Комиссию платит собственник маклеру. Сплит book.immo - из B2B-агентского договора. Легально.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>book.immo — Pre-Launch Budget (Apr–Aug 2026, USD)</t>
+          <t>book.immo - Pre-Launch Budget (Apr–Aug 2026, USD)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Собственный бэкенд: PostgreSQL + API (auth, избранное, заявки) — без vendor lock-in</t>
+          <t>• Собственный бэкенд: PostgreSQL + API (auth, избранное, заявки) - без vendor lock-in</t>
         </is>
       </c>
     </row>
@@ -1171,14 +1171,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>book.immo — BASE, Берлин, запуск Sep 2026 (EUR)</t>
+          <t>book.immo - BASE, Берлин, запуск Sep 2026 (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — входные драйверы (можно менять). Остальное считается формулами.</t>
+          <t>Жёлтые ячейки - входные драйверы (можно менять). Остальное считается формулами.</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ДРАЙВЕРЫ — каналы (входные)</t>
+          <t>ДРАЙВЕРЫ - каналы (входные)</t>
         </is>
       </c>
     </row>
@@ -3847,14 +3847,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>book.immo — PESSIMISTIC, Берлин, запуск Sep 2026 (EUR)</t>
+          <t>book.immo - PESSIMISTIC, Берлин, запуск Sep 2026 (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — входные драйверы (можно менять). Остальное считается формулами.</t>
+          <t>Жёлтые ячейки - входные драйверы (можно менять). Остальное считается формулами.</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ДРАЙВЕРЫ — каналы (входные)</t>
+          <t>ДРАЙВЕРЫ - каналы (входные)</t>
         </is>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1484,7 +1484,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Активные агентства (накопл.)</t>
+          <t>Агентства: холодный BD (накопл.)</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -1554,513 +1554,455 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Тёплый вход: доля self-deals -&gt; партнёр-агентство</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>КВАЛИФИКАЦИЯ по каналу (доля регистраций, прошедших скрининг)</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Paid search (long-tail + EN)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Экспат-комьюнити</t>
+          <t xml:space="preserve">  Paid search (long-tail + EN)</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Relocation-партнёрства (B2B2C)</t>
+          <t xml:space="preserve">  Экспат-комьюнити</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
+          <t xml:space="preserve">  Relocation-партнёрства (B2B2C)</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Реферальная петля</t>
+          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Агентства как канал</t>
+          <t xml:space="preserve">  Реферальная петля</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Агентства как канал</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>КОНВЕРСИЯ в сделку</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Квалифицированный → сделка через агентство</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Квалифицированный → сделка на каталоге IS24</t>
+          <t>Квалифицированный → сделка через агентство</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Квалифицированный → сделка на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Потолок сделок на агентство / мес</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D31" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E31" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H31" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I31" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="J31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M31" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>UNIT ECONOMICS</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Сплит аренда, €/сделка</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>605</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Сплит продажа, €/сделка</t>
+          <t>Сплит аренда, €/сделка</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>2400</v>
+        <v>605</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Доля аренды</t>
+          <t>Сплит продажа, €/сделка</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>0.85</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2C fee, €</t>
+          <t>Доля аренды</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>149</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Доля агентских сделок, платящих B2C fee</t>
+          <t>B2C fee, €</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>0.5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Продажник: % от выручки агентских сделок</t>
+          <t>Доля агентских сделок, платящих B2C fee</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zolak: средний чек мебели, €</t>
+          <t>Продажник: % от выручки агентских сделок</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>3000</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zolak: наша доля от мебели</t>
+          <t>Zolak: средний чек мебели, €</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>0.015</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Zolak: наша доля от мебели</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I42" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="J41" s="8" t="n">
+      <c r="J42" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="K41" s="8" t="n">
+      <c r="K42" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L42" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M42" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="N41">
-        <f>SUM(B41:M41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="N42">
+        <f>SUM(B42:M42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B44">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I44">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J44">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K44">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L44">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M44">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N44">
-        <f>SUM(B44:M44)</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Регистрации: комьюнити</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>B9</f>
-        <v/>
+          <t>Тёплые агентства (накопл., от прошлых self-deals)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>C9</f>
+        <f>B45+ROUND(B61*$B$18,0)</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D9</f>
+        <f>C45+ROUND(C61*$B$18,0)</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E9</f>
+        <f>D45+ROUND(D61*$B$18,0)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F9</f>
+        <f>E45+ROUND(E61*$B$18,0)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G9</f>
+        <f>F45+ROUND(F61*$B$18,0)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H9</f>
+        <f>G45+ROUND(G61*$B$18,0)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I9</f>
+        <f>H45+ROUND(H61*$B$18,0)</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J9</f>
+        <f>I45+ROUND(I61*$B$18,0)</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K9</f>
+        <f>J45+ROUND(J61*$B$18,0)</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L9</f>
+        <f>K45+ROUND(K61*$B$18,0)</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N45">
-        <f>SUM(B45:M45)</f>
+        <f>L45+ROUND(L61*$B$18,0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Эффективные агентства (холодные + тёплые)</t>
         </is>
       </c>
       <c r="B46">
-        <f>B12*$B$13</f>
+        <f>B14+B45</f>
         <v/>
       </c>
       <c r="C46">
-        <f>C12*$B$13</f>
+        <f>C14+C45</f>
         <v/>
       </c>
       <c r="D46">
-        <f>D12*$B$13</f>
+        <f>D14+D45</f>
         <v/>
       </c>
       <c r="E46">
-        <f>E12*$B$13</f>
+        <f>E14+E45</f>
         <v/>
       </c>
       <c r="F46">
-        <f>F12*$B$13</f>
+        <f>F14+F45</f>
         <v/>
       </c>
       <c r="G46">
-        <f>G12*$B$13</f>
+        <f>G14+G45</f>
         <v/>
       </c>
       <c r="H46">
-        <f>H12*$B$13</f>
+        <f>H14+H45</f>
         <v/>
       </c>
       <c r="I46">
-        <f>I12*$B$13</f>
+        <f>I14+I45</f>
         <v/>
       </c>
       <c r="J46">
-        <f>J12*$B$13</f>
+        <f>J14+J45</f>
         <v/>
       </c>
       <c r="K46">
-        <f>K12*$B$13</f>
+        <f>K14+K45</f>
         <v/>
       </c>
       <c r="L46">
-        <f>L12*$B$13</f>
+        <f>L14+L45</f>
         <v/>
       </c>
       <c r="M46">
-        <f>M12*$B$13</f>
-        <v/>
-      </c>
-      <c r="N46">
-        <f>SUM(B46:M46)</f>
+        <f>M14+M45</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B47">
-        <f>B14*$B$15*$B$16</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C47">
-        <f>C14*$B$15*$B$16</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D47">
-        <f>D14*$B$15*$B$16</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E47">
-        <f>E14*$B$15*$B$16</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F47">
-        <f>F14*$B$15*$B$16</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G47">
-        <f>G14*$B$15*$B$16</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H47">
-        <f>H14*$B$15*$B$16</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I47">
-        <f>I14*$B$15*$B$16</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J47">
-        <f>J14*$B$15*$B$16</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K47">
-        <f>K14*$B$15*$B$16</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L47">
-        <f>L14*$B$15*$B$16</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M47">
-        <f>M14*$B$15*$B$16</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N47">
@@ -2071,55 +2013,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B48">
-        <f>B10*$B$11</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C10*$B$11</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D10*$B$11</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E10*$B$11</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F10*$B$11</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G10*$B$11</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H10*$B$11</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I10*$B$11</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J10*$B$11</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K10*$B$11</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L10*$B$11</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M10*$B$11</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N48">
@@ -2128,60 +2070,60 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Итого регистраций</t>
-        </is>
-      </c>
-      <c r="B49" s="6">
-        <f>B44+B45+B46+B47+B48</f>
-        <v/>
-      </c>
-      <c r="C49" s="6">
-        <f>C44+C45+C46+C47+C48</f>
-        <v/>
-      </c>
-      <c r="D49" s="6">
-        <f>D44+D45+D46+D47+D48</f>
-        <v/>
-      </c>
-      <c r="E49" s="6">
-        <f>E44+E45+E46+E47+E48</f>
-        <v/>
-      </c>
-      <c r="F49" s="6">
-        <f>F44+F45+F46+F47+F48</f>
-        <v/>
-      </c>
-      <c r="G49" s="6">
-        <f>G44+G45+G46+G47+G48</f>
-        <v/>
-      </c>
-      <c r="H49" s="6">
-        <f>H44+H45+H46+H47+H48</f>
-        <v/>
-      </c>
-      <c r="I49" s="6">
-        <f>I44+I45+I46+I47+I48</f>
-        <v/>
-      </c>
-      <c r="J49" s="6">
-        <f>J44+J45+J46+J47+J48</f>
-        <v/>
-      </c>
-      <c r="K49" s="6">
-        <f>K44+K45+K46+K47+K48</f>
-        <v/>
-      </c>
-      <c r="L49" s="6">
-        <f>L44+L45+L46+L47+L48</f>
-        <v/>
-      </c>
-      <c r="M49" s="6">
-        <f>M44+M45+M46+M47+M48</f>
-        <v/>
-      </c>
-      <c r="N49" s="6">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Регистрации: SEO</t>
+        </is>
+      </c>
+      <c r="B49">
+        <f>B12*$B$13</f>
+        <v/>
+      </c>
+      <c r="C49">
+        <f>C12*$B$13</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>D12*$B$13</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>E12*$B$13</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>F12*$B$13</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>G12*$B$13</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>H12*$B$13</f>
+        <v/>
+      </c>
+      <c r="I49">
+        <f>I12*$B$13</f>
+        <v/>
+      </c>
+      <c r="J49">
+        <f>J12*$B$13</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>K12*$B$13</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>L12*$B$13</f>
+        <v/>
+      </c>
+      <c r="M49">
+        <f>M12*$B$13</f>
+        <v/>
+      </c>
+      <c r="N49">
         <f>SUM(B49:M49)</f>
         <v/>
       </c>
@@ -2189,55 +2131,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: paid</t>
+          <t>Регистрации: агентства</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$20</f>
+        <f>B46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$20</f>
+        <f>C46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$20</f>
+        <f>D46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$20</f>
+        <f>E46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$20</f>
+        <f>F46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$20</f>
+        <f>G46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$20</f>
+        <f>H46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$20</f>
+        <f>I46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$20</f>
+        <f>J46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$20</f>
+        <f>K46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$20</f>
+        <f>L46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$20</f>
+        <f>M46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="N50">
@@ -2248,55 +2190,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: комьюнити</t>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$21</f>
+        <f>B10*$B$11</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$21</f>
+        <f>C10*$B$11</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$21</f>
+        <f>D10*$B$11</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$21</f>
+        <f>E10*$B$11</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$21</f>
+        <f>F10*$B$11</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$21</f>
+        <f>G10*$B$11</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$21</f>
+        <f>H10*$B$11</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$21</f>
+        <f>I10*$B$11</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$21</f>
+        <f>J10*$B$11</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$21</f>
+        <f>K10*$B$11</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$21</f>
+        <f>L10*$B$11</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$21</f>
+        <f>M10*$B$11</f>
         <v/>
       </c>
       <c r="N51">
@@ -2305,60 +2247,60 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Квалифицировано: SEO</t>
-        </is>
-      </c>
-      <c r="B52">
-        <f>B46*$B$23</f>
-        <v/>
-      </c>
-      <c r="C52">
-        <f>C46*$B$23</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>D46*$B$23</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>E46*$B$23</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>F46*$B$23</f>
-        <v/>
-      </c>
-      <c r="G52">
-        <f>G46*$B$23</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>H46*$B$23</f>
-        <v/>
-      </c>
-      <c r="I52">
-        <f>I46*$B$23</f>
-        <v/>
-      </c>
-      <c r="J52">
-        <f>J46*$B$23</f>
-        <v/>
-      </c>
-      <c r="K52">
-        <f>K46*$B$23</f>
-        <v/>
-      </c>
-      <c r="L52">
-        <f>L46*$B$23</f>
-        <v/>
-      </c>
-      <c r="M52">
-        <f>M46*$B$23</f>
-        <v/>
-      </c>
-      <c r="N52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Итого регистраций</t>
+        </is>
+      </c>
+      <c r="B52" s="6">
+        <f>B47+B48+B49+B50+B51</f>
+        <v/>
+      </c>
+      <c r="C52" s="6">
+        <f>C47+C48+C49+C50+C51</f>
+        <v/>
+      </c>
+      <c r="D52" s="6">
+        <f>D47+D48+D49+D50+D51</f>
+        <v/>
+      </c>
+      <c r="E52" s="6">
+        <f>E47+E48+E49+E50+E51</f>
+        <v/>
+      </c>
+      <c r="F52" s="6">
+        <f>F47+F48+F49+F50+F51</f>
+        <v/>
+      </c>
+      <c r="G52" s="6">
+        <f>G47+G48+G49+G50+G51</f>
+        <v/>
+      </c>
+      <c r="H52" s="6">
+        <f>H47+H48+H49+H50+H51</f>
+        <v/>
+      </c>
+      <c r="I52" s="6">
+        <f>I47+I48+I49+I50+I51</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>J47+J48+J49+J50+J51</f>
+        <v/>
+      </c>
+      <c r="K52" s="6">
+        <f>K47+K48+K49+K50+K51</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f>L47+L48+L49+L50+L51</f>
+        <v/>
+      </c>
+      <c r="M52" s="6">
+        <f>M47+M48+M49+M50+M51</f>
+        <v/>
+      </c>
+      <c r="N52" s="6">
         <f>SUM(B52:M52)</f>
         <v/>
       </c>
@@ -2366,55 +2308,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B53">
-        <f>B47*$B$25</f>
+        <f>B47*$B$21</f>
         <v/>
       </c>
       <c r="C53">
-        <f>C47*$B$25</f>
+        <f>C47*$B$21</f>
         <v/>
       </c>
       <c r="D53">
-        <f>D47*$B$25</f>
+        <f>D47*$B$21</f>
         <v/>
       </c>
       <c r="E53">
-        <f>E47*$B$25</f>
+        <f>E47*$B$21</f>
         <v/>
       </c>
       <c r="F53">
-        <f>F47*$B$25</f>
+        <f>F47*$B$21</f>
         <v/>
       </c>
       <c r="G53">
-        <f>G47*$B$25</f>
+        <f>G47*$B$21</f>
         <v/>
       </c>
       <c r="H53">
-        <f>H47*$B$25</f>
+        <f>H47*$B$21</f>
         <v/>
       </c>
       <c r="I53">
-        <f>I47*$B$25</f>
+        <f>I47*$B$21</f>
         <v/>
       </c>
       <c r="J53">
-        <f>J47*$B$25</f>
+        <f>J47*$B$21</f>
         <v/>
       </c>
       <c r="K53">
-        <f>K47*$B$25</f>
+        <f>K47*$B$21</f>
         <v/>
       </c>
       <c r="L53">
-        <f>L47*$B$25</f>
+        <f>L47*$B$21</f>
         <v/>
       </c>
       <c r="M53">
-        <f>M47*$B$25</f>
+        <f>M47*$B$21</f>
         <v/>
       </c>
       <c r="N53">
@@ -2425,7 +2367,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B54">
@@ -2484,54 +2426,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
+          <t>Квалифицировано: SEO</t>
+        </is>
+      </c>
+      <c r="B55">
+        <f>B49*$B$24</f>
+        <v/>
       </c>
       <c r="C55">
-        <f>B59*$B$17*$B$24</f>
+        <f>C49*$B$24</f>
         <v/>
       </c>
       <c r="D55">
-        <f>C59*$B$17*$B$24</f>
+        <f>D49*$B$24</f>
         <v/>
       </c>
       <c r="E55">
-        <f>D59*$B$17*$B$24</f>
+        <f>E49*$B$24</f>
         <v/>
       </c>
       <c r="F55">
-        <f>E59*$B$17*$B$24</f>
+        <f>F49*$B$24</f>
         <v/>
       </c>
       <c r="G55">
-        <f>F59*$B$17*$B$24</f>
+        <f>G49*$B$24</f>
         <v/>
       </c>
       <c r="H55">
-        <f>G59*$B$17*$B$24</f>
+        <f>H49*$B$24</f>
         <v/>
       </c>
       <c r="I55">
-        <f>H59*$B$17*$B$24</f>
+        <f>I49*$B$24</f>
         <v/>
       </c>
       <c r="J55">
-        <f>I59*$B$17*$B$24</f>
+        <f>J49*$B$24</f>
         <v/>
       </c>
       <c r="K55">
-        <f>J59*$B$17*$B$24</f>
+        <f>K49*$B$24</f>
         <v/>
       </c>
       <c r="L55">
-        <f>K59*$B$17*$B$24</f>
+        <f>L49*$B$24</f>
         <v/>
       </c>
       <c r="M55">
-        <f>L59*$B$17*$B$24</f>
+        <f>M49*$B$24</f>
         <v/>
       </c>
       <c r="N55">
@@ -2540,60 +2483,60 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Итого квалифицированных</t>
-        </is>
-      </c>
-      <c r="B56" s="6">
-        <f>B50+B51+B52+B53+B54+B55</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>C50+C51+C52+C53+C54+C55</f>
-        <v/>
-      </c>
-      <c r="D56" s="6">
-        <f>D50+D51+D52+D53+D54+D55</f>
-        <v/>
-      </c>
-      <c r="E56" s="6">
-        <f>E50+E51+E52+E53+E54+E55</f>
-        <v/>
-      </c>
-      <c r="F56" s="6">
-        <f>F50+F51+F52+F53+F54+F55</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G50+G51+G52+G53+G54+G55</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H50+H51+H52+H53+H54+H55</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I50+I51+I52+I53+I54+I55</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J50+J51+J52+J53+J54+J55</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K50+K51+K52+K53+K54+K55</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L50+L51+L52+L53+L54+L55</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M50+M51+M52+M53+M54+M55</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Квалифицировано: агентства</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>B50*$B$26</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>C50*$B$26</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>D50*$B$26</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>E50*$B$26</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>F50*$B$26</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>G50*$B$26</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>H50*$B$26</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>I50*$B$26</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>J50*$B$26</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>K50*$B$26</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>L50*$B$26</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>M50*$B$26</f>
+        <v/>
+      </c>
+      <c r="N56">
         <f>SUM(B56:M56)</f>
         <v/>
       </c>
@@ -2601,55 +2544,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Сделки через агентства</t>
+          <t>Квалифицировано: партнёры</t>
         </is>
       </c>
       <c r="B57">
-        <f>ROUND(MIN(B56*$B$28,B14*B30),0)</f>
+        <f>B51*$B$23</f>
         <v/>
       </c>
       <c r="C57">
-        <f>ROUND(MIN(C56*$B$28,C14*C30),0)</f>
+        <f>C51*$B$23</f>
         <v/>
       </c>
       <c r="D57">
-        <f>ROUND(MIN(D56*$B$28,D14*D30),0)</f>
+        <f>D51*$B$23</f>
         <v/>
       </c>
       <c r="E57">
-        <f>ROUND(MIN(E56*$B$28,E14*E30),0)</f>
+        <f>E51*$B$23</f>
         <v/>
       </c>
       <c r="F57">
-        <f>ROUND(MIN(F56*$B$28,F14*F30),0)</f>
+        <f>F51*$B$23</f>
         <v/>
       </c>
       <c r="G57">
-        <f>ROUND(MIN(G56*$B$28,G14*G30),0)</f>
+        <f>G51*$B$23</f>
         <v/>
       </c>
       <c r="H57">
-        <f>ROUND(MIN(H56*$B$28,H14*H30),0)</f>
+        <f>H51*$B$23</f>
         <v/>
       </c>
       <c r="I57">
-        <f>ROUND(MIN(I56*$B$28,I14*I30),0)</f>
+        <f>I51*$B$23</f>
         <v/>
       </c>
       <c r="J57">
-        <f>ROUND(MIN(J56*$B$28,J14*J30),0)</f>
+        <f>J51*$B$23</f>
         <v/>
       </c>
       <c r="K57">
-        <f>ROUND(MIN(K56*$B$28,K14*K30),0)</f>
+        <f>K51*$B$23</f>
         <v/>
       </c>
       <c r="L57">
-        <f>ROUND(MIN(L56*$B$28,L14*L30),0)</f>
+        <f>L51*$B$23</f>
         <v/>
       </c>
       <c r="M57">
-        <f>ROUND(MIN(M56*$B$28,M14*M30),0)</f>
+        <f>M51*$B$23</f>
         <v/>
       </c>
       <c r="N57">
@@ -2660,55 +2603,54 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Сделки на каталоге IS24</t>
-        </is>
-      </c>
-      <c r="B58">
-        <f>ROUND(B56*$B$29,0)</f>
-        <v/>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
       </c>
       <c r="C58">
-        <f>ROUND(C56*$B$29,0)</f>
+        <f>B62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="D58">
-        <f>ROUND(D56*$B$29,0)</f>
+        <f>C62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="E58">
-        <f>ROUND(E56*$B$29,0)</f>
+        <f>D62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="F58">
-        <f>ROUND(F56*$B$29,0)</f>
+        <f>E62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="G58">
-        <f>ROUND(G56*$B$29,0)</f>
+        <f>F62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="H58">
-        <f>ROUND(H56*$B$29,0)</f>
+        <f>G62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="I58">
-        <f>ROUND(I56*$B$29,0)</f>
+        <f>H62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="J58">
-        <f>ROUND(J56*$B$29,0)</f>
+        <f>I62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="K58">
-        <f>ROUND(K56*$B$29,0)</f>
+        <f>J62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="L58">
-        <f>ROUND(L56*$B$29,0)</f>
+        <f>K62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="M58">
-        <f>ROUND(M56*$B$29,0)</f>
+        <f>L62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="N58">
@@ -2719,55 +2661,55 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Сделок всего</t>
+          <t>Итого квалифицированных</t>
         </is>
       </c>
       <c r="B59" s="6">
-        <f>B57+B58</f>
+        <f>B53+B54+B55+B56+B57+B58</f>
         <v/>
       </c>
       <c r="C59" s="6">
-        <f>C57+C58</f>
+        <f>C53+C54+C55+C56+C57+C58</f>
         <v/>
       </c>
       <c r="D59" s="6">
-        <f>D57+D58</f>
+        <f>D53+D54+D55+D56+D57+D58</f>
         <v/>
       </c>
       <c r="E59" s="6">
-        <f>E57+E58</f>
+        <f>E53+E54+E55+E56+E57+E58</f>
         <v/>
       </c>
       <c r="F59" s="6">
-        <f>F57+F58</f>
+        <f>F53+F54+F55+F56+F57+F58</f>
         <v/>
       </c>
       <c r="G59" s="6">
-        <f>G57+G58</f>
+        <f>G53+G54+G55+G56+G57+G58</f>
         <v/>
       </c>
       <c r="H59" s="6">
-        <f>H57+H58</f>
+        <f>H53+H54+H55+H56+H57+H58</f>
         <v/>
       </c>
       <c r="I59" s="6">
-        <f>I57+I58</f>
+        <f>I53+I54+I55+I56+I57+I58</f>
         <v/>
       </c>
       <c r="J59" s="6">
-        <f>J57+J58</f>
+        <f>J53+J54+J55+J56+J57+J58</f>
         <v/>
       </c>
       <c r="K59" s="6">
-        <f>K57+K58</f>
+        <f>K53+K54+K55+K56+K57+K58</f>
         <v/>
       </c>
       <c r="L59" s="6">
-        <f>L57+L58</f>
+        <f>L53+L54+L55+L56+L57+L58</f>
         <v/>
       </c>
       <c r="M59" s="6">
-        <f>M57+M58</f>
+        <f>M53+M54+M55+M56+M57+M58</f>
         <v/>
       </c>
       <c r="N59" s="6">
@@ -2778,55 +2720,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Сделок с B2C fee</t>
+          <t>Сделки через агентства</t>
         </is>
       </c>
       <c r="B60">
-        <f>B58+ROUND(B57*$B$37,0)</f>
+        <f>ROUND(MIN(B59*$B$29,B46*B31),0)</f>
         <v/>
       </c>
       <c r="C60">
-        <f>C58+ROUND(C57*$B$37,0)</f>
+        <f>ROUND(MIN(C59*$B$29,C46*C31),0)</f>
         <v/>
       </c>
       <c r="D60">
-        <f>D58+ROUND(D57*$B$37,0)</f>
+        <f>ROUND(MIN(D59*$B$29,D46*D31),0)</f>
         <v/>
       </c>
       <c r="E60">
-        <f>E58+ROUND(E57*$B$37,0)</f>
+        <f>ROUND(MIN(E59*$B$29,E46*E31),0)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>F58+ROUND(F57*$B$37,0)</f>
+        <f>ROUND(MIN(F59*$B$29,F46*F31),0)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>G58+ROUND(G57*$B$37,0)</f>
+        <f>ROUND(MIN(G59*$B$29,G46*G31),0)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>H58+ROUND(H57*$B$37,0)</f>
+        <f>ROUND(MIN(H59*$B$29,H46*H31),0)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>I58+ROUND(I57*$B$37,0)</f>
+        <f>ROUND(MIN(I59*$B$29,I46*I31),0)</f>
         <v/>
       </c>
       <c r="J60">
-        <f>J58+ROUND(J57*$B$37,0)</f>
+        <f>ROUND(MIN(J59*$B$29,J46*J31),0)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>K58+ROUND(K57*$B$37,0)</f>
+        <f>ROUND(MIN(K59*$B$29,K46*K31),0)</f>
         <v/>
       </c>
       <c r="L60">
-        <f>L58+ROUND(L57*$B$37,0)</f>
+        <f>ROUND(MIN(L59*$B$29,L46*L31),0)</f>
         <v/>
       </c>
       <c r="M60">
-        <f>M58+ROUND(M57*$B$37,0)</f>
+        <f>ROUND(MIN(M59*$B$29,M46*M31),0)</f>
         <v/>
       </c>
       <c r="N60">
@@ -2834,65 +2776,176 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Сделки на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B61">
+        <f>ROUND(B59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>ROUND(C59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>ROUND(D59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>ROUND(E59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>ROUND(F59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>ROUND(G59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>ROUND(H59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>ROUND(I59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>ROUND(J59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>ROUND(K59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>ROUND(L59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>ROUND(M59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>SUM(B61:M61)</f>
+        <v/>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>ВЫРУЧКА</t>
-        </is>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Сделок всего</t>
+        </is>
+      </c>
+      <c r="B62" s="6">
+        <f>B60+B61</f>
+        <v/>
+      </c>
+      <c r="C62" s="6">
+        <f>C60+C61</f>
+        <v/>
+      </c>
+      <c r="D62" s="6">
+        <f>D60+D61</f>
+        <v/>
+      </c>
+      <c r="E62" s="6">
+        <f>E60+E61</f>
+        <v/>
+      </c>
+      <c r="F62" s="6">
+        <f>F60+F61</f>
+        <v/>
+      </c>
+      <c r="G62" s="6">
+        <f>G60+G61</f>
+        <v/>
+      </c>
+      <c r="H62" s="6">
+        <f>H60+H61</f>
+        <v/>
+      </c>
+      <c r="I62" s="6">
+        <f>I60+I61</f>
+        <v/>
+      </c>
+      <c r="J62" s="6">
+        <f>J60+J61</f>
+        <v/>
+      </c>
+      <c r="K62" s="6">
+        <f>K60+K61</f>
+        <v/>
+      </c>
+      <c r="L62" s="6">
+        <f>L60+L61</f>
+        <v/>
+      </c>
+      <c r="M62" s="6">
+        <f>M60+M61</f>
+        <v/>
+      </c>
+      <c r="N62" s="6">
+        <f>SUM(B62:M62)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
+          <t>Сделок с B2C fee</t>
         </is>
       </c>
       <c r="B63">
-        <f>ROUND(B57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>B61+ROUND(B60*$B$38,0)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>ROUND(C57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>C61+ROUND(C60*$B$38,0)</f>
         <v/>
       </c>
       <c r="D63">
-        <f>ROUND(D57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>D61+ROUND(D60*$B$38,0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>ROUND(E57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>E61+ROUND(E60*$B$38,0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>ROUND(F57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>F61+ROUND(F60*$B$38,0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>ROUND(G57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>G61+ROUND(G60*$B$38,0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>ROUND(H57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>H61+ROUND(H60*$B$38,0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>ROUND(I57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>I61+ROUND(I60*$B$38,0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>ROUND(J57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>J61+ROUND(J60*$B$38,0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>ROUND(K57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>K61+ROUND(K60*$B$38,0)</f>
         <v/>
       </c>
       <c r="L63">
-        <f>ROUND(L57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>L61+ROUND(L60*$B$38,0)</f>
         <v/>
       </c>
       <c r="M63">
-        <f>ROUND(M57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>M61+ROUND(M60*$B$38,0)</f>
         <v/>
       </c>
       <c r="N63">
@@ -2900,176 +2953,65 @@
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>R3: B2C fee</t>
-        </is>
-      </c>
-      <c r="B64">
-        <f>B60*$B$36</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>C60*$B$36</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>D60*$B$36</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>E60*$B$36</f>
-        <v/>
-      </c>
-      <c r="F64">
-        <f>F60*$B$36</f>
-        <v/>
-      </c>
-      <c r="G64">
-        <f>G60*$B$36</f>
-        <v/>
-      </c>
-      <c r="H64">
-        <f>H60*$B$36</f>
-        <v/>
-      </c>
-      <c r="I64">
-        <f>I60*$B$36</f>
-        <v/>
-      </c>
-      <c r="J64">
-        <f>J60*$B$36</f>
-        <v/>
-      </c>
-      <c r="K64">
-        <f>K60*$B$36</f>
-        <v/>
-      </c>
-      <c r="L64">
-        <f>L60*$B$36</f>
-        <v/>
-      </c>
-      <c r="M64">
-        <f>M60*$B$36</f>
-        <v/>
-      </c>
-      <c r="N64">
-        <f>SUM(B64:M64)</f>
-        <v/>
-      </c>
-    </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>R4: upsell</t>
-        </is>
-      </c>
-      <c r="B65">
-        <f>B41</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>C41</f>
-        <v/>
-      </c>
-      <c r="D65">
-        <f>D41</f>
-        <v/>
-      </c>
-      <c r="E65">
-        <f>E41</f>
-        <v/>
-      </c>
-      <c r="F65">
-        <f>F41</f>
-        <v/>
-      </c>
-      <c r="G65">
-        <f>G41</f>
-        <v/>
-      </c>
-      <c r="H65">
-        <f>H41</f>
-        <v/>
-      </c>
-      <c r="I65">
-        <f>I41</f>
-        <v/>
-      </c>
-      <c r="J65">
-        <f>J41</f>
-        <v/>
-      </c>
-      <c r="K65">
-        <f>K41</f>
-        <v/>
-      </c>
-      <c r="L65">
-        <f>L41</f>
-        <v/>
-      </c>
-      <c r="M65">
-        <f>M41</f>
-        <v/>
-      </c>
-      <c r="N65">
-        <f>SUM(B65:M65)</f>
-        <v/>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>ВЫРУЧКА</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R5: реферал на мебель (Zolak)</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B66">
-        <f>ROUND(B59*$B$39*$B$40,0)</f>
+        <f>ROUND(B60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>ROUND(C59*$B$39*$B$40,0)</f>
+        <f>ROUND(C60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="D66">
-        <f>ROUND(D59*$B$39*$B$40,0)</f>
+        <f>ROUND(D60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="E66">
-        <f>ROUND(E59*$B$39*$B$40,0)</f>
+        <f>ROUND(E60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>ROUND(F59*$B$39*$B$40,0)</f>
+        <f>ROUND(F60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="G66">
-        <f>ROUND(G59*$B$39*$B$40,0)</f>
+        <f>ROUND(G60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="H66">
-        <f>ROUND(H59*$B$39*$B$40,0)</f>
+        <f>ROUND(H60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="I66">
-        <f>ROUND(I59*$B$39*$B$40,0)</f>
+        <f>ROUND(I60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="J66">
-        <f>ROUND(J59*$B$39*$B$40,0)</f>
+        <f>ROUND(J60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="K66">
-        <f>ROUND(K59*$B$39*$B$40,0)</f>
+        <f>ROUND(K60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="L66">
-        <f>ROUND(L59*$B$39*$B$40,0)</f>
+        <f>ROUND(L60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="M66">
-        <f>ROUND(M59*$B$39*$B$40,0)</f>
+        <f>ROUND(M60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="N66">
@@ -3078,265 +3020,301 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R3: B2C fee</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>B63*$B$37</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>C63*$B$37</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>D63*$B$37</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>E63*$B$37</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>F63*$B$37</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>G63*$B$37</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>H63*$B$37</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>I63*$B$37</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>J63*$B$37</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>K63*$B$37</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>L63*$B$37</f>
+        <v/>
+      </c>
+      <c r="M67">
+        <f>M63*$B$37</f>
+        <v/>
+      </c>
+      <c r="N67">
+        <f>SUM(B67:M67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B68">
+        <f>B42</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>D42</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>F42</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>G42</f>
+        <v/>
+      </c>
+      <c r="H68">
+        <f>H42</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>I42</f>
+        <v/>
+      </c>
+      <c r="J68">
+        <f>J42</f>
+        <v/>
+      </c>
+      <c r="K68">
+        <f>K42</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>L42</f>
+        <v/>
+      </c>
+      <c r="M68">
+        <f>M42</f>
+        <v/>
+      </c>
+      <c r="N68">
+        <f>SUM(B68:M68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R5: реферал на мебель (Zolak)</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>ROUND(B62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>ROUND(C62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>ROUND(D62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>ROUND(E62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>ROUND(F62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>ROUND(G62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="H69">
+        <f>ROUND(H62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>ROUND(I62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="J69">
+        <f>ROUND(J62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="K69">
+        <f>ROUND(K62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>ROUND(L62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="M69">
+        <f>ROUND(M62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="N69">
+        <f>SUM(B69:M69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B67" s="6">
-        <f>B63+B64+B65+B66</f>
-        <v/>
-      </c>
-      <c r="C67" s="6">
-        <f>C63+C64+C65+C66</f>
-        <v/>
-      </c>
-      <c r="D67" s="6">
-        <f>D63+D64+D65+D66</f>
-        <v/>
-      </c>
-      <c r="E67" s="6">
-        <f>E63+E64+E65+E66</f>
-        <v/>
-      </c>
-      <c r="F67" s="6">
-        <f>F63+F64+F65+F66</f>
-        <v/>
-      </c>
-      <c r="G67" s="6">
-        <f>G63+G64+G65+G66</f>
-        <v/>
-      </c>
-      <c r="H67" s="6">
-        <f>H63+H64+H65+H66</f>
-        <v/>
-      </c>
-      <c r="I67" s="6">
-        <f>I63+I64+I65+I66</f>
-        <v/>
-      </c>
-      <c r="J67" s="6">
-        <f>J63+J64+J65+J66</f>
-        <v/>
-      </c>
-      <c r="K67" s="6">
-        <f>K63+K64+K65+K66</f>
-        <v/>
-      </c>
-      <c r="L67" s="6">
-        <f>L63+L64+L65+L66</f>
-        <v/>
-      </c>
-      <c r="M67" s="6">
-        <f>M63+M64+M65+M66</f>
-        <v/>
-      </c>
-      <c r="N67" s="6">
-        <f>SUM(B67:M67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B70" s="6">
+        <f>B66+B67+B68+B69</f>
+        <v/>
+      </c>
+      <c r="C70" s="6">
+        <f>C66+C67+C68+C69</f>
+        <v/>
+      </c>
+      <c r="D70" s="6">
+        <f>D66+D67+D68+D69</f>
+        <v/>
+      </c>
+      <c r="E70" s="6">
+        <f>E66+E67+E68+E69</f>
+        <v/>
+      </c>
+      <c r="F70" s="6">
+        <f>F66+F67+F68+F69</f>
+        <v/>
+      </c>
+      <c r="G70" s="6">
+        <f>G66+G67+G68+G69</f>
+        <v/>
+      </c>
+      <c r="H70" s="6">
+        <f>H66+H67+H68+H69</f>
+        <v/>
+      </c>
+      <c r="I70" s="6">
+        <f>I66+I67+I68+I69</f>
+        <v/>
+      </c>
+      <c r="J70" s="6">
+        <f>J66+J67+J68+J69</f>
+        <v/>
+      </c>
+      <c r="K70" s="6">
+        <f>K66+K67+K68+K69</f>
+        <v/>
+      </c>
+      <c r="L70" s="6">
+        <f>L66+L67+L68+L69</f>
+        <v/>
+      </c>
+      <c r="M70" s="6">
+        <f>M66+M67+M68+M69</f>
+        <v/>
+      </c>
+      <c r="N70" s="6">
+        <f>SUM(B70:M70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B70">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C70">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D70">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E70">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F70">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G70">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H70">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I70">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J70">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K70">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L70">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M70">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N70">
-        <f>SUM(B70:M70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="N71">
-        <f>SUM(B71:M71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>1291</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>1382</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>1473</v>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>1564</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>1655</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>1745</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>1836</v>
-      </c>
-      <c r="J72" s="8" t="n">
-        <v>1927</v>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L72" s="8" t="n">
-        <v>2109</v>
-      </c>
-      <c r="M72" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="N72">
-        <f>SUM(B72:M72)</f>
-        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend-контрактор (доработки, фичи)</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="K73" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="L73" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="M73" s="8" t="n">
-        <v>2700</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M73">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -3346,44 +3324,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="C74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="N74">
         <f>SUM(B74:M74)</f>
@@ -3393,44 +3371,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Support/ops (B2C + агентства)</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>600</v>
+        <v>1291</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>600</v>
+        <v>1382</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>700</v>
+        <v>1473</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>700</v>
+        <v>1564</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>700</v>
+        <v>1655</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>800</v>
+        <v>1745</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>800</v>
+        <v>1836</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>800</v>
+        <v>1927</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>900</v>
+        <v>2018</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>900</v>
+        <v>2109</v>
       </c>
       <c r="M75" s="8" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="N75">
         <f>SUM(B75:M75)</f>
@@ -3440,44 +3418,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Backend-контрактор (доработки, фичи)</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="C76" s="8" t="n">
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>850</v>
+        <v>2100</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>1050</v>
+        <v>2400</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>1150</v>
+        <v>2700</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>1200</v>
+        <v>2700</v>
       </c>
       <c r="M76" s="8" t="n">
-        <v>1250</v>
+        <v>2700</v>
       </c>
       <c r="N76">
         <f>SUM(B76:M76)</f>
@@ -3487,44 +3465,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N77">
         <f>SUM(B77:M77)</f>
@@ -3534,56 +3512,44 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B78">
-        <f>ROUND(B63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C78">
-        <f>ROUND(C63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D78">
-        <f>ROUND(D63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E78">
-        <f>ROUND(E63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F78">
-        <f>ROUND(F63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G78">
-        <f>ROUND(G63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H78">
-        <f>ROUND(H63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I78">
-        <f>ROUND(I63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J78">
-        <f>ROUND(J63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K78">
-        <f>ROUND(K63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L78">
-        <f>ROUND(L63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M78">
-        <f>ROUND(M63*$B$38,0)</f>
-        <v/>
+          <t>Support/ops (B2C + агентства)</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="L78" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>900</v>
       </c>
       <c r="N78">
         <f>SUM(B78:M78)</f>
@@ -3591,226 +3557,379 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K79" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N79">
+        <f>SUM(B79:M79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N80">
+        <f>SUM(B80:M80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>ROUND(B66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>ROUND(C66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>ROUND(D66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>ROUND(E66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>ROUND(F66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>ROUND(G66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="H81">
+        <f>ROUND(H66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>ROUND(I66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="J81">
+        <f>ROUND(J66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="K81">
+        <f>ROUND(K66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="L81">
+        <f>ROUND(L66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="M81">
+        <f>ROUND(M66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="N81">
+        <f>SUM(B81:M81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>TOTAL COSTS</t>
         </is>
       </c>
-      <c r="B79" s="6">
-        <f>B70+B71+B72+B73+B74+B75+B76+B77+B78</f>
-        <v/>
-      </c>
-      <c r="C79" s="6">
-        <f>C70+C71+C72+C73+C74+C75+C76+C77+C78</f>
-        <v/>
-      </c>
-      <c r="D79" s="6">
-        <f>D70+D71+D72+D73+D74+D75+D76+D77+D78</f>
-        <v/>
-      </c>
-      <c r="E79" s="6">
-        <f>E70+E71+E72+E73+E74+E75+E76+E77+E78</f>
-        <v/>
-      </c>
-      <c r="F79" s="6">
-        <f>F70+F71+F72+F73+F74+F75+F76+F77+F78</f>
-        <v/>
-      </c>
-      <c r="G79" s="6">
-        <f>G70+G71+G72+G73+G74+G75+G76+G77+G78</f>
-        <v/>
-      </c>
-      <c r="H79" s="6">
-        <f>H70+H71+H72+H73+H74+H75+H76+H77+H78</f>
-        <v/>
-      </c>
-      <c r="I79" s="6">
-        <f>I70+I71+I72+I73+I74+I75+I76+I77+I78</f>
-        <v/>
-      </c>
-      <c r="J79" s="6">
-        <f>J70+J71+J72+J73+J74+J75+J76+J77+J78</f>
-        <v/>
-      </c>
-      <c r="K79" s="6">
-        <f>K70+K71+K72+K73+K74+K75+K76+K77+K78</f>
-        <v/>
-      </c>
-      <c r="L79" s="6">
-        <f>L70+L71+L72+L73+L74+L75+L76+L77+L78</f>
-        <v/>
-      </c>
-      <c r="M79" s="6">
-        <f>M70+M71+M72+M73+M74+M75+M76+M77+M78</f>
-        <v/>
-      </c>
-      <c r="N79" s="6">
-        <f>SUM(B79:M79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="B82" s="6">
+        <f>B73+B74+B75+B76+B77+B78+B79+B80+B81</f>
+        <v/>
+      </c>
+      <c r="C82" s="6">
+        <f>C73+C74+C75+C76+C77+C78+C79+C80+C81</f>
+        <v/>
+      </c>
+      <c r="D82" s="6">
+        <f>D73+D74+D75+D76+D77+D78+D79+D80+D81</f>
+        <v/>
+      </c>
+      <c r="E82" s="6">
+        <f>E73+E74+E75+E76+E77+E78+E79+E80+E81</f>
+        <v/>
+      </c>
+      <c r="F82" s="6">
+        <f>F73+F74+F75+F76+F77+F78+F79+F80+F81</f>
+        <v/>
+      </c>
+      <c r="G82" s="6">
+        <f>G73+G74+G75+G76+G77+G78+G79+G80+G81</f>
+        <v/>
+      </c>
+      <c r="H82" s="6">
+        <f>H73+H74+H75+H76+H77+H78+H79+H80+H81</f>
+        <v/>
+      </c>
+      <c r="I82" s="6">
+        <f>I73+I74+I75+I76+I77+I78+I79+I80+I81</f>
+        <v/>
+      </c>
+      <c r="J82" s="6">
+        <f>J73+J74+J75+J76+J77+J78+J79+J80+J81</f>
+        <v/>
+      </c>
+      <c r="K82" s="6">
+        <f>K73+K74+K75+K76+K77+K78+K79+K80+K81</f>
+        <v/>
+      </c>
+      <c r="L82" s="6">
+        <f>L73+L74+L75+L76+L77+L78+L79+L80+L81</f>
+        <v/>
+      </c>
+      <c r="M82" s="6">
+        <f>M73+M74+M75+M76+M77+M78+M79+M80+M81</f>
+        <v/>
+      </c>
+      <c r="N82" s="6">
+        <f>SUM(B82:M82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B81" s="6">
-        <f>B67-B79</f>
-        <v/>
-      </c>
-      <c r="C81" s="6">
-        <f>C67-C79</f>
-        <v/>
-      </c>
-      <c r="D81" s="6">
-        <f>D67-D79</f>
-        <v/>
-      </c>
-      <c r="E81" s="6">
-        <f>E67-E79</f>
-        <v/>
-      </c>
-      <c r="F81" s="6">
-        <f>F67-F79</f>
-        <v/>
-      </c>
-      <c r="G81" s="6">
-        <f>G67-G79</f>
-        <v/>
-      </c>
-      <c r="H81" s="6">
-        <f>H67-H79</f>
-        <v/>
-      </c>
-      <c r="I81" s="6">
-        <f>I67-I79</f>
-        <v/>
-      </c>
-      <c r="J81" s="6">
-        <f>J67-J79</f>
-        <v/>
-      </c>
-      <c r="K81" s="6">
-        <f>K67-K79</f>
-        <v/>
-      </c>
-      <c r="L81" s="6">
-        <f>L67-L79</f>
-        <v/>
-      </c>
-      <c r="M81" s="6">
-        <f>M67-M79</f>
-        <v/>
-      </c>
-      <c r="N81" s="6">
-        <f>SUM(B81:M81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Кэш (старт €18,000)</t>
-        </is>
-      </c>
-      <c r="B82">
-        <f>18000+B81</f>
-        <v/>
-      </c>
-      <c r="C82">
-        <f>B82+C81</f>
-        <v/>
-      </c>
-      <c r="D82">
-        <f>C82+D81</f>
-        <v/>
-      </c>
-      <c r="E82">
-        <f>D82+E81</f>
-        <v/>
-      </c>
-      <c r="F82">
-        <f>E82+F81</f>
-        <v/>
-      </c>
-      <c r="G82">
-        <f>F82+G81</f>
-        <v/>
-      </c>
-      <c r="H82">
-        <f>G82+H81</f>
-        <v/>
-      </c>
-      <c r="I82">
-        <f>H82+I81</f>
-        <v/>
-      </c>
-      <c r="J82">
-        <f>I82+J81</f>
-        <v/>
-      </c>
-      <c r="K82">
-        <f>J82+K81</f>
-        <v/>
-      </c>
-      <c r="L82">
-        <f>K82+L81</f>
-        <v/>
-      </c>
-      <c r="M82">
-        <f>L82+M81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
-        </is>
+      <c r="B84" s="6">
+        <f>B70-B82</f>
+        <v/>
+      </c>
+      <c r="C84" s="6">
+        <f>C70-C82</f>
+        <v/>
+      </c>
+      <c r="D84" s="6">
+        <f>D70-D82</f>
+        <v/>
+      </c>
+      <c r="E84" s="6">
+        <f>E70-E82</f>
+        <v/>
+      </c>
+      <c r="F84" s="6">
+        <f>F70-F82</f>
+        <v/>
+      </c>
+      <c r="G84" s="6">
+        <f>G70-G82</f>
+        <v/>
+      </c>
+      <c r="H84" s="6">
+        <f>H70-H82</f>
+        <v/>
+      </c>
+      <c r="I84" s="6">
+        <f>I70-I82</f>
+        <v/>
+      </c>
+      <c r="J84" s="6">
+        <f>J70-J82</f>
+        <v/>
+      </c>
+      <c r="K84" s="6">
+        <f>K70-K82</f>
+        <v/>
+      </c>
+      <c r="L84" s="6">
+        <f>L70-L82</f>
+        <v/>
+      </c>
+      <c r="M84" s="6">
+        <f>M70-M82</f>
+        <v/>
+      </c>
+      <c r="N84" s="6">
+        <f>SUM(B84:M84)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAC на квалифицированного лида, €</t>
+          <t>Кэш (старт €18,000)</t>
         </is>
       </c>
       <c r="B85">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B86">
-        <f>ROUND(N6/N59,0)</f>
+        <f>18000+B84</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>B85+C84</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>C85+D84</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>D85+E84</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>E85+F84</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>F85+G84</f>
+        <v/>
+      </c>
+      <c r="H85">
+        <f>G85+H84</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>H85+I84</f>
+        <v/>
+      </c>
+      <c r="J85">
+        <f>I85+J84</f>
+        <v/>
+      </c>
+      <c r="K85">
+        <f>J85+K84</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>K85+L84</f>
+        <v/>
+      </c>
+      <c r="M85">
+        <f>L85+M84</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Выручка на агентскую сделку, €</t>
-        </is>
-      </c>
-      <c r="B87">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
-        <v/>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>CAC на квалифицированного лида, €</t>
+        </is>
+      </c>
+      <c r="B88">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B89">
+        <f>ROUND(N6/N62,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B90">
+        <f>ROUND($B$36*$B$34+(1-$B$36)*$B$35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B88">
-        <f>ROUND(B87/B86,1)</f>
+      <c r="B91">
+        <f>ROUND(B90/B89,1)</f>
         <v/>
       </c>
     </row>
@@ -3825,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4160,7 +4279,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Активные агентства (накопл.)</t>
+          <t>Агентства: холодный BD (накопл.)</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -4230,513 +4349,455 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Тёплый вход: доля self-deals -&gt; партнёр-агентство</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>КВАЛИФИКАЦИЯ по каналу (доля регистраций, прошедших скрининг)</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Paid search (long-tail + EN)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Экспат-комьюнити</t>
+          <t xml:space="preserve">  Paid search (long-tail + EN)</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Relocation-партнёрства (B2B2C)</t>
+          <t xml:space="preserve">  Экспат-комьюнити</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
+          <t xml:space="preserve">  Relocation-партнёрства (B2B2C)</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Реферальная петля</t>
+          <t xml:space="preserve">  SEO: гео-страницы на базе каталога</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Агентства как канал</t>
+          <t xml:space="preserve">  Реферальная петля</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Агентства как канал</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>КОНВЕРСИЯ в сделку</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Квалифицированный → сделка через агентство</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Квалифицированный → сделка на каталоге IS24</t>
+          <t>Квалифицированный → сделка через агентство</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>0.025</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Квалифицированный → сделка на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Потолок сделок на агентство / мес</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B31" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C31" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G31" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H31" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I31" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="J31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M31" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>UNIT ECONOMICS</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Сплит аренда, €/сделка</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>605</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Сплит продажа, €/сделка</t>
+          <t>Сплит аренда, €/сделка</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>2400</v>
+        <v>605</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Доля аренды</t>
+          <t>Сплит продажа, €/сделка</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>0.85</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2C fee, €</t>
+          <t>Доля аренды</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>149</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Доля агентских сделок, платящих B2C fee</t>
+          <t>B2C fee, €</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>0.5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Продажник: % от выручки агентских сделок</t>
+          <t>Доля агентских сделок, платящих B2C fee</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zolak: средний чек мебели, €</t>
+          <t>Продажник: % от выручки агентских сделок</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>3000</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zolak: наша доля от мебели</t>
+          <t>Zolak: средний чек мебели, €</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>0.015</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Zolak: наша доля от мебели</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Upsell агентствам, €/мес</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="8" t="n">
+      <c r="J42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="8" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N41">
-        <f>SUM(B41:M41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="N42">
+        <f>SUM(B42:M42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>ВОРОНКА</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Регистрации: paid</t>
-        </is>
-      </c>
-      <c r="B44">
-        <f>B6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>C6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>D6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>E6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>F6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>G6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>H6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="I44">
-        <f>I6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="J44">
-        <f>J6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="K44">
-        <f>K6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="L44">
-        <f>L6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="M44">
-        <f>M6/$B$7*$B$8</f>
-        <v/>
-      </c>
-      <c r="N44">
-        <f>SUM(B44:M44)</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Регистрации: комьюнити</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>B9</f>
-        <v/>
+          <t>Тёплые агентства (накопл., от прошлых self-deals)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>C9</f>
+        <f>B45+ROUND(B61*$B$18,0)</f>
         <v/>
       </c>
       <c r="D45">
-        <f>D9</f>
+        <f>C45+ROUND(C61*$B$18,0)</f>
         <v/>
       </c>
       <c r="E45">
-        <f>E9</f>
+        <f>D45+ROUND(D61*$B$18,0)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>F9</f>
+        <f>E45+ROUND(E61*$B$18,0)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>G9</f>
+        <f>F45+ROUND(F61*$B$18,0)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>H9</f>
+        <f>G45+ROUND(G61*$B$18,0)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>I9</f>
+        <f>H45+ROUND(H61*$B$18,0)</f>
         <v/>
       </c>
       <c r="J45">
-        <f>J9</f>
+        <f>I45+ROUND(I61*$B$18,0)</f>
         <v/>
       </c>
       <c r="K45">
-        <f>K9</f>
+        <f>J45+ROUND(J61*$B$18,0)</f>
         <v/>
       </c>
       <c r="L45">
-        <f>L9</f>
+        <f>K45+ROUND(K61*$B$18,0)</f>
         <v/>
       </c>
       <c r="M45">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N45">
-        <f>SUM(B45:M45)</f>
+        <f>L45+ROUND(L61*$B$18,0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Регистрации: SEO</t>
+          <t>Эффективные агентства (холодные + тёплые)</t>
         </is>
       </c>
       <c r="B46">
-        <f>B12*$B$13</f>
+        <f>B14+B45</f>
         <v/>
       </c>
       <c r="C46">
-        <f>C12*$B$13</f>
+        <f>C14+C45</f>
         <v/>
       </c>
       <c r="D46">
-        <f>D12*$B$13</f>
+        <f>D14+D45</f>
         <v/>
       </c>
       <c r="E46">
-        <f>E12*$B$13</f>
+        <f>E14+E45</f>
         <v/>
       </c>
       <c r="F46">
-        <f>F12*$B$13</f>
+        <f>F14+F45</f>
         <v/>
       </c>
       <c r="G46">
-        <f>G12*$B$13</f>
+        <f>G14+G45</f>
         <v/>
       </c>
       <c r="H46">
-        <f>H12*$B$13</f>
+        <f>H14+H45</f>
         <v/>
       </c>
       <c r="I46">
-        <f>I12*$B$13</f>
+        <f>I14+I45</f>
         <v/>
       </c>
       <c r="J46">
-        <f>J12*$B$13</f>
+        <f>J14+J45</f>
         <v/>
       </c>
       <c r="K46">
-        <f>K12*$B$13</f>
+        <f>K14+K45</f>
         <v/>
       </c>
       <c r="L46">
-        <f>L12*$B$13</f>
+        <f>L14+L45</f>
         <v/>
       </c>
       <c r="M46">
-        <f>M12*$B$13</f>
-        <v/>
-      </c>
-      <c r="N46">
-        <f>SUM(B46:M46)</f>
+        <f>M14+M45</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Регистрации: агентства</t>
+          <t>Регистрации: paid</t>
         </is>
       </c>
       <c r="B47">
-        <f>B14*$B$15*$B$16</f>
+        <f>B6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="C47">
-        <f>C14*$B$15*$B$16</f>
+        <f>C6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="D47">
-        <f>D14*$B$15*$B$16</f>
+        <f>D6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="E47">
-        <f>E14*$B$15*$B$16</f>
+        <f>E6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="F47">
-        <f>F14*$B$15*$B$16</f>
+        <f>F6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="G47">
-        <f>G14*$B$15*$B$16</f>
+        <f>G6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="H47">
-        <f>H14*$B$15*$B$16</f>
+        <f>H6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="I47">
-        <f>I14*$B$15*$B$16</f>
+        <f>I6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="J47">
-        <f>J14*$B$15*$B$16</f>
+        <f>J6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="K47">
-        <f>K14*$B$15*$B$16</f>
+        <f>K6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="L47">
-        <f>L14*$B$15*$B$16</f>
+        <f>L6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="M47">
-        <f>M14*$B$15*$B$16</f>
+        <f>M6/$B$7*$B$8</f>
         <v/>
       </c>
       <c r="N47">
@@ -4747,55 +4808,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Лиды: партнёры (уже квалифицированы)</t>
+          <t>Регистрации: комьюнити</t>
         </is>
       </c>
       <c r="B48">
-        <f>B10*$B$11</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="C48">
-        <f>C10*$B$11</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D48">
-        <f>D10*$B$11</f>
+        <f>D9</f>
         <v/>
       </c>
       <c r="E48">
-        <f>E10*$B$11</f>
+        <f>E9</f>
         <v/>
       </c>
       <c r="F48">
-        <f>F10*$B$11</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="G48">
-        <f>G10*$B$11</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="H48">
-        <f>H10*$B$11</f>
+        <f>H9</f>
         <v/>
       </c>
       <c r="I48">
-        <f>I10*$B$11</f>
+        <f>I9</f>
         <v/>
       </c>
       <c r="J48">
-        <f>J10*$B$11</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K48">
-        <f>K10*$B$11</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L48">
-        <f>L10*$B$11</f>
+        <f>L9</f>
         <v/>
       </c>
       <c r="M48">
-        <f>M10*$B$11</f>
+        <f>M9</f>
         <v/>
       </c>
       <c r="N48">
@@ -4804,60 +4865,60 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Итого регистраций</t>
-        </is>
-      </c>
-      <c r="B49" s="6">
-        <f>B44+B45+B46+B47+B48</f>
-        <v/>
-      </c>
-      <c r="C49" s="6">
-        <f>C44+C45+C46+C47+C48</f>
-        <v/>
-      </c>
-      <c r="D49" s="6">
-        <f>D44+D45+D46+D47+D48</f>
-        <v/>
-      </c>
-      <c r="E49" s="6">
-        <f>E44+E45+E46+E47+E48</f>
-        <v/>
-      </c>
-      <c r="F49" s="6">
-        <f>F44+F45+F46+F47+F48</f>
-        <v/>
-      </c>
-      <c r="G49" s="6">
-        <f>G44+G45+G46+G47+G48</f>
-        <v/>
-      </c>
-      <c r="H49" s="6">
-        <f>H44+H45+H46+H47+H48</f>
-        <v/>
-      </c>
-      <c r="I49" s="6">
-        <f>I44+I45+I46+I47+I48</f>
-        <v/>
-      </c>
-      <c r="J49" s="6">
-        <f>J44+J45+J46+J47+J48</f>
-        <v/>
-      </c>
-      <c r="K49" s="6">
-        <f>K44+K45+K46+K47+K48</f>
-        <v/>
-      </c>
-      <c r="L49" s="6">
-        <f>L44+L45+L46+L47+L48</f>
-        <v/>
-      </c>
-      <c r="M49" s="6">
-        <f>M44+M45+M46+M47+M48</f>
-        <v/>
-      </c>
-      <c r="N49" s="6">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Регистрации: SEO</t>
+        </is>
+      </c>
+      <c r="B49">
+        <f>B12*$B$13</f>
+        <v/>
+      </c>
+      <c r="C49">
+        <f>C12*$B$13</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>D12*$B$13</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>E12*$B$13</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>F12*$B$13</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>G12*$B$13</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>H12*$B$13</f>
+        <v/>
+      </c>
+      <c r="I49">
+        <f>I12*$B$13</f>
+        <v/>
+      </c>
+      <c r="J49">
+        <f>J12*$B$13</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>K12*$B$13</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>L12*$B$13</f>
+        <v/>
+      </c>
+      <c r="M49">
+        <f>M12*$B$13</f>
+        <v/>
+      </c>
+      <c r="N49">
         <f>SUM(B49:M49)</f>
         <v/>
       </c>
@@ -4865,55 +4926,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Квалифицировано: paid</t>
+          <t>Регистрации: агентства</t>
         </is>
       </c>
       <c r="B50">
-        <f>B44*$B$20</f>
+        <f>B46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="C50">
-        <f>C44*$B$20</f>
+        <f>C46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="D50">
-        <f>D44*$B$20</f>
+        <f>D46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="E50">
-        <f>E44*$B$20</f>
+        <f>E46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="F50">
-        <f>F44*$B$20</f>
+        <f>F46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="G50">
-        <f>G44*$B$20</f>
+        <f>G46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="H50">
-        <f>H44*$B$20</f>
+        <f>H46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="I50">
-        <f>I44*$B$20</f>
+        <f>I46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="J50">
-        <f>J44*$B$20</f>
+        <f>J46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="K50">
-        <f>K44*$B$20</f>
+        <f>K46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="L50">
-        <f>L44*$B$20</f>
+        <f>L46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="M50">
-        <f>M44*$B$20</f>
+        <f>M46*$B$15*$B$16</f>
         <v/>
       </c>
       <c r="N50">
@@ -4924,55 +4985,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Квалифицировано: комьюнити</t>
+          <t>Лиды: партнёры (уже квалифицированы)</t>
         </is>
       </c>
       <c r="B51">
-        <f>B45*$B$21</f>
+        <f>B10*$B$11</f>
         <v/>
       </c>
       <c r="C51">
-        <f>C45*$B$21</f>
+        <f>C10*$B$11</f>
         <v/>
       </c>
       <c r="D51">
-        <f>D45*$B$21</f>
+        <f>D10*$B$11</f>
         <v/>
       </c>
       <c r="E51">
-        <f>E45*$B$21</f>
+        <f>E10*$B$11</f>
         <v/>
       </c>
       <c r="F51">
-        <f>F45*$B$21</f>
+        <f>F10*$B$11</f>
         <v/>
       </c>
       <c r="G51">
-        <f>G45*$B$21</f>
+        <f>G10*$B$11</f>
         <v/>
       </c>
       <c r="H51">
-        <f>H45*$B$21</f>
+        <f>H10*$B$11</f>
         <v/>
       </c>
       <c r="I51">
-        <f>I45*$B$21</f>
+        <f>I10*$B$11</f>
         <v/>
       </c>
       <c r="J51">
-        <f>J45*$B$21</f>
+        <f>J10*$B$11</f>
         <v/>
       </c>
       <c r="K51">
-        <f>K45*$B$21</f>
+        <f>K10*$B$11</f>
         <v/>
       </c>
       <c r="L51">
-        <f>L45*$B$21</f>
+        <f>L10*$B$11</f>
         <v/>
       </c>
       <c r="M51">
-        <f>M45*$B$21</f>
+        <f>M10*$B$11</f>
         <v/>
       </c>
       <c r="N51">
@@ -4981,60 +5042,60 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Квалифицировано: SEO</t>
-        </is>
-      </c>
-      <c r="B52">
-        <f>B46*$B$23</f>
-        <v/>
-      </c>
-      <c r="C52">
-        <f>C46*$B$23</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>D46*$B$23</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>E46*$B$23</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>F46*$B$23</f>
-        <v/>
-      </c>
-      <c r="G52">
-        <f>G46*$B$23</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>H46*$B$23</f>
-        <v/>
-      </c>
-      <c r="I52">
-        <f>I46*$B$23</f>
-        <v/>
-      </c>
-      <c r="J52">
-        <f>J46*$B$23</f>
-        <v/>
-      </c>
-      <c r="K52">
-        <f>K46*$B$23</f>
-        <v/>
-      </c>
-      <c r="L52">
-        <f>L46*$B$23</f>
-        <v/>
-      </c>
-      <c r="M52">
-        <f>M46*$B$23</f>
-        <v/>
-      </c>
-      <c r="N52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Итого регистраций</t>
+        </is>
+      </c>
+      <c r="B52" s="6">
+        <f>B47+B48+B49+B50+B51</f>
+        <v/>
+      </c>
+      <c r="C52" s="6">
+        <f>C47+C48+C49+C50+C51</f>
+        <v/>
+      </c>
+      <c r="D52" s="6">
+        <f>D47+D48+D49+D50+D51</f>
+        <v/>
+      </c>
+      <c r="E52" s="6">
+        <f>E47+E48+E49+E50+E51</f>
+        <v/>
+      </c>
+      <c r="F52" s="6">
+        <f>F47+F48+F49+F50+F51</f>
+        <v/>
+      </c>
+      <c r="G52" s="6">
+        <f>G47+G48+G49+G50+G51</f>
+        <v/>
+      </c>
+      <c r="H52" s="6">
+        <f>H47+H48+H49+H50+H51</f>
+        <v/>
+      </c>
+      <c r="I52" s="6">
+        <f>I47+I48+I49+I50+I51</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>J47+J48+J49+J50+J51</f>
+        <v/>
+      </c>
+      <c r="K52" s="6">
+        <f>K47+K48+K49+K50+K51</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f>L47+L48+L49+L50+L51</f>
+        <v/>
+      </c>
+      <c r="M52" s="6">
+        <f>M47+M48+M49+M50+M51</f>
+        <v/>
+      </c>
+      <c r="N52" s="6">
         <f>SUM(B52:M52)</f>
         <v/>
       </c>
@@ -5042,55 +5103,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Квалифицировано: агентства</t>
+          <t>Квалифицировано: paid</t>
         </is>
       </c>
       <c r="B53">
-        <f>B47*$B$25</f>
+        <f>B47*$B$21</f>
         <v/>
       </c>
       <c r="C53">
-        <f>C47*$B$25</f>
+        <f>C47*$B$21</f>
         <v/>
       </c>
       <c r="D53">
-        <f>D47*$B$25</f>
+        <f>D47*$B$21</f>
         <v/>
       </c>
       <c r="E53">
-        <f>E47*$B$25</f>
+        <f>E47*$B$21</f>
         <v/>
       </c>
       <c r="F53">
-        <f>F47*$B$25</f>
+        <f>F47*$B$21</f>
         <v/>
       </c>
       <c r="G53">
-        <f>G47*$B$25</f>
+        <f>G47*$B$21</f>
         <v/>
       </c>
       <c r="H53">
-        <f>H47*$B$25</f>
+        <f>H47*$B$21</f>
         <v/>
       </c>
       <c r="I53">
-        <f>I47*$B$25</f>
+        <f>I47*$B$21</f>
         <v/>
       </c>
       <c r="J53">
-        <f>J47*$B$25</f>
+        <f>J47*$B$21</f>
         <v/>
       </c>
       <c r="K53">
-        <f>K47*$B$25</f>
+        <f>K47*$B$21</f>
         <v/>
       </c>
       <c r="L53">
-        <f>L47*$B$25</f>
+        <f>L47*$B$21</f>
         <v/>
       </c>
       <c r="M53">
-        <f>M47*$B$25</f>
+        <f>M47*$B$21</f>
         <v/>
       </c>
       <c r="N53">
@@ -5101,7 +5162,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Квалифицировано: партнёры</t>
+          <t>Квалифицировано: комьюнити</t>
         </is>
       </c>
       <c r="B54">
@@ -5160,54 +5221,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Квалифицировано: referral</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
+          <t>Квалифицировано: SEO</t>
+        </is>
+      </c>
+      <c r="B55">
+        <f>B49*$B$24</f>
+        <v/>
       </c>
       <c r="C55">
-        <f>B59*$B$17*$B$24</f>
+        <f>C49*$B$24</f>
         <v/>
       </c>
       <c r="D55">
-        <f>C59*$B$17*$B$24</f>
+        <f>D49*$B$24</f>
         <v/>
       </c>
       <c r="E55">
-        <f>D59*$B$17*$B$24</f>
+        <f>E49*$B$24</f>
         <v/>
       </c>
       <c r="F55">
-        <f>E59*$B$17*$B$24</f>
+        <f>F49*$B$24</f>
         <v/>
       </c>
       <c r="G55">
-        <f>F59*$B$17*$B$24</f>
+        <f>G49*$B$24</f>
         <v/>
       </c>
       <c r="H55">
-        <f>G59*$B$17*$B$24</f>
+        <f>H49*$B$24</f>
         <v/>
       </c>
       <c r="I55">
-        <f>H59*$B$17*$B$24</f>
+        <f>I49*$B$24</f>
         <v/>
       </c>
       <c r="J55">
-        <f>I59*$B$17*$B$24</f>
+        <f>J49*$B$24</f>
         <v/>
       </c>
       <c r="K55">
-        <f>J59*$B$17*$B$24</f>
+        <f>K49*$B$24</f>
         <v/>
       </c>
       <c r="L55">
-        <f>K59*$B$17*$B$24</f>
+        <f>L49*$B$24</f>
         <v/>
       </c>
       <c r="M55">
-        <f>L59*$B$17*$B$24</f>
+        <f>M49*$B$24</f>
         <v/>
       </c>
       <c r="N55">
@@ -5216,60 +5278,60 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Итого квалифицированных</t>
-        </is>
-      </c>
-      <c r="B56" s="6">
-        <f>B50+B51+B52+B53+B54+B55</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>C50+C51+C52+C53+C54+C55</f>
-        <v/>
-      </c>
-      <c r="D56" s="6">
-        <f>D50+D51+D52+D53+D54+D55</f>
-        <v/>
-      </c>
-      <c r="E56" s="6">
-        <f>E50+E51+E52+E53+E54+E55</f>
-        <v/>
-      </c>
-      <c r="F56" s="6">
-        <f>F50+F51+F52+F53+F54+F55</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G50+G51+G52+G53+G54+G55</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H50+H51+H52+H53+H54+H55</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I50+I51+I52+I53+I54+I55</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J50+J51+J52+J53+J54+J55</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K50+K51+K52+K53+K54+K55</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L50+L51+L52+L53+L54+L55</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M50+M51+M52+M53+M54+M55</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Квалифицировано: агентства</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>B50*$B$26</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>C50*$B$26</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>D50*$B$26</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>E50*$B$26</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>F50*$B$26</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>G50*$B$26</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>H50*$B$26</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>I50*$B$26</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>J50*$B$26</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>K50*$B$26</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>L50*$B$26</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>M50*$B$26</f>
+        <v/>
+      </c>
+      <c r="N56">
         <f>SUM(B56:M56)</f>
         <v/>
       </c>
@@ -5277,55 +5339,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Сделки через агентства</t>
+          <t>Квалифицировано: партнёры</t>
         </is>
       </c>
       <c r="B57">
-        <f>ROUND(MIN(B56*$B$28,B14*B30),0)</f>
+        <f>B51*$B$23</f>
         <v/>
       </c>
       <c r="C57">
-        <f>ROUND(MIN(C56*$B$28,C14*C30),0)</f>
+        <f>C51*$B$23</f>
         <v/>
       </c>
       <c r="D57">
-        <f>ROUND(MIN(D56*$B$28,D14*D30),0)</f>
+        <f>D51*$B$23</f>
         <v/>
       </c>
       <c r="E57">
-        <f>ROUND(MIN(E56*$B$28,E14*E30),0)</f>
+        <f>E51*$B$23</f>
         <v/>
       </c>
       <c r="F57">
-        <f>ROUND(MIN(F56*$B$28,F14*F30),0)</f>
+        <f>F51*$B$23</f>
         <v/>
       </c>
       <c r="G57">
-        <f>ROUND(MIN(G56*$B$28,G14*G30),0)</f>
+        <f>G51*$B$23</f>
         <v/>
       </c>
       <c r="H57">
-        <f>ROUND(MIN(H56*$B$28,H14*H30),0)</f>
+        <f>H51*$B$23</f>
         <v/>
       </c>
       <c r="I57">
-        <f>ROUND(MIN(I56*$B$28,I14*I30),0)</f>
+        <f>I51*$B$23</f>
         <v/>
       </c>
       <c r="J57">
-        <f>ROUND(MIN(J56*$B$28,J14*J30),0)</f>
+        <f>J51*$B$23</f>
         <v/>
       </c>
       <c r="K57">
-        <f>ROUND(MIN(K56*$B$28,K14*K30),0)</f>
+        <f>K51*$B$23</f>
         <v/>
       </c>
       <c r="L57">
-        <f>ROUND(MIN(L56*$B$28,L14*L30),0)</f>
+        <f>L51*$B$23</f>
         <v/>
       </c>
       <c r="M57">
-        <f>ROUND(MIN(M56*$B$28,M14*M30),0)</f>
+        <f>M51*$B$23</f>
         <v/>
       </c>
       <c r="N57">
@@ -5336,55 +5398,54 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Сделки на каталоге IS24</t>
-        </is>
-      </c>
-      <c r="B58">
-        <f>ROUND(B56*$B$29,0)</f>
-        <v/>
+          <t>Квалифицировано: referral</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
       </c>
       <c r="C58">
-        <f>ROUND(C56*$B$29,0)</f>
+        <f>B62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="D58">
-        <f>ROUND(D56*$B$29,0)</f>
+        <f>C62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="E58">
-        <f>ROUND(E56*$B$29,0)</f>
+        <f>D62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="F58">
-        <f>ROUND(F56*$B$29,0)</f>
+        <f>E62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="G58">
-        <f>ROUND(G56*$B$29,0)</f>
+        <f>F62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="H58">
-        <f>ROUND(H56*$B$29,0)</f>
+        <f>G62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="I58">
-        <f>ROUND(I56*$B$29,0)</f>
+        <f>H62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="J58">
-        <f>ROUND(J56*$B$29,0)</f>
+        <f>I62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="K58">
-        <f>ROUND(K56*$B$29,0)</f>
+        <f>J62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="L58">
-        <f>ROUND(L56*$B$29,0)</f>
+        <f>K62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="M58">
-        <f>ROUND(M56*$B$29,0)</f>
+        <f>L62*$B$17*$B$25</f>
         <v/>
       </c>
       <c r="N58">
@@ -5395,55 +5456,55 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Сделок всего</t>
+          <t>Итого квалифицированных</t>
         </is>
       </c>
       <c r="B59" s="6">
-        <f>B57+B58</f>
+        <f>B53+B54+B55+B56+B57+B58</f>
         <v/>
       </c>
       <c r="C59" s="6">
-        <f>C57+C58</f>
+        <f>C53+C54+C55+C56+C57+C58</f>
         <v/>
       </c>
       <c r="D59" s="6">
-        <f>D57+D58</f>
+        <f>D53+D54+D55+D56+D57+D58</f>
         <v/>
       </c>
       <c r="E59" s="6">
-        <f>E57+E58</f>
+        <f>E53+E54+E55+E56+E57+E58</f>
         <v/>
       </c>
       <c r="F59" s="6">
-        <f>F57+F58</f>
+        <f>F53+F54+F55+F56+F57+F58</f>
         <v/>
       </c>
       <c r="G59" s="6">
-        <f>G57+G58</f>
+        <f>G53+G54+G55+G56+G57+G58</f>
         <v/>
       </c>
       <c r="H59" s="6">
-        <f>H57+H58</f>
+        <f>H53+H54+H55+H56+H57+H58</f>
         <v/>
       </c>
       <c r="I59" s="6">
-        <f>I57+I58</f>
+        <f>I53+I54+I55+I56+I57+I58</f>
         <v/>
       </c>
       <c r="J59" s="6">
-        <f>J57+J58</f>
+        <f>J53+J54+J55+J56+J57+J58</f>
         <v/>
       </c>
       <c r="K59" s="6">
-        <f>K57+K58</f>
+        <f>K53+K54+K55+K56+K57+K58</f>
         <v/>
       </c>
       <c r="L59" s="6">
-        <f>L57+L58</f>
+        <f>L53+L54+L55+L56+L57+L58</f>
         <v/>
       </c>
       <c r="M59" s="6">
-        <f>M57+M58</f>
+        <f>M53+M54+M55+M56+M57+M58</f>
         <v/>
       </c>
       <c r="N59" s="6">
@@ -5454,55 +5515,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Сделок с B2C fee</t>
+          <t>Сделки через агентства</t>
         </is>
       </c>
       <c r="B60">
-        <f>B58+ROUND(B57*$B$37,0)</f>
+        <f>ROUND(MIN(B59*$B$29,B46*B31),0)</f>
         <v/>
       </c>
       <c r="C60">
-        <f>C58+ROUND(C57*$B$37,0)</f>
+        <f>ROUND(MIN(C59*$B$29,C46*C31),0)</f>
         <v/>
       </c>
       <c r="D60">
-        <f>D58+ROUND(D57*$B$37,0)</f>
+        <f>ROUND(MIN(D59*$B$29,D46*D31),0)</f>
         <v/>
       </c>
       <c r="E60">
-        <f>E58+ROUND(E57*$B$37,0)</f>
+        <f>ROUND(MIN(E59*$B$29,E46*E31),0)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>F58+ROUND(F57*$B$37,0)</f>
+        <f>ROUND(MIN(F59*$B$29,F46*F31),0)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>G58+ROUND(G57*$B$37,0)</f>
+        <f>ROUND(MIN(G59*$B$29,G46*G31),0)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>H58+ROUND(H57*$B$37,0)</f>
+        <f>ROUND(MIN(H59*$B$29,H46*H31),0)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>I58+ROUND(I57*$B$37,0)</f>
+        <f>ROUND(MIN(I59*$B$29,I46*I31),0)</f>
         <v/>
       </c>
       <c r="J60">
-        <f>J58+ROUND(J57*$B$37,0)</f>
+        <f>ROUND(MIN(J59*$B$29,J46*J31),0)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>K58+ROUND(K57*$B$37,0)</f>
+        <f>ROUND(MIN(K59*$B$29,K46*K31),0)</f>
         <v/>
       </c>
       <c r="L60">
-        <f>L58+ROUND(L57*$B$37,0)</f>
+        <f>ROUND(MIN(L59*$B$29,L46*L31),0)</f>
         <v/>
       </c>
       <c r="M60">
-        <f>M58+ROUND(M57*$B$37,0)</f>
+        <f>ROUND(MIN(M59*$B$29,M46*M31),0)</f>
         <v/>
       </c>
       <c r="N60">
@@ -5510,65 +5571,176 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Сделки на каталоге IS24</t>
+        </is>
+      </c>
+      <c r="B61">
+        <f>ROUND(B59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>ROUND(C59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>ROUND(D59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>ROUND(E59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>ROUND(F59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>ROUND(G59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>ROUND(H59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>ROUND(I59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>ROUND(J59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>ROUND(K59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>ROUND(L59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>ROUND(M59*$B$30,0)</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>SUM(B61:M61)</f>
+        <v/>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>ВЫРУЧКА</t>
-        </is>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Сделок всего</t>
+        </is>
+      </c>
+      <c r="B62" s="6">
+        <f>B60+B61</f>
+        <v/>
+      </c>
+      <c r="C62" s="6">
+        <f>C60+C61</f>
+        <v/>
+      </c>
+      <c r="D62" s="6">
+        <f>D60+D61</f>
+        <v/>
+      </c>
+      <c r="E62" s="6">
+        <f>E60+E61</f>
+        <v/>
+      </c>
+      <c r="F62" s="6">
+        <f>F60+F61</f>
+        <v/>
+      </c>
+      <c r="G62" s="6">
+        <f>G60+G61</f>
+        <v/>
+      </c>
+      <c r="H62" s="6">
+        <f>H60+H61</f>
+        <v/>
+      </c>
+      <c r="I62" s="6">
+        <f>I60+I61</f>
+        <v/>
+      </c>
+      <c r="J62" s="6">
+        <f>J60+J61</f>
+        <v/>
+      </c>
+      <c r="K62" s="6">
+        <f>K60+K61</f>
+        <v/>
+      </c>
+      <c r="L62" s="6">
+        <f>L60+L61</f>
+        <v/>
+      </c>
+      <c r="M62" s="6">
+        <f>M60+M61</f>
+        <v/>
+      </c>
+      <c r="N62" s="6">
+        <f>SUM(B62:M62)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
+          <t>Сделок с B2C fee</t>
         </is>
       </c>
       <c r="B63">
-        <f>ROUND(B57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>B61+ROUND(B60*$B$38,0)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>ROUND(C57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>C61+ROUND(C60*$B$38,0)</f>
         <v/>
       </c>
       <c r="D63">
-        <f>ROUND(D57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>D61+ROUND(D60*$B$38,0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>ROUND(E57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>E61+ROUND(E60*$B$38,0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>ROUND(F57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>F61+ROUND(F60*$B$38,0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>ROUND(G57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>G61+ROUND(G60*$B$38,0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>ROUND(H57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>H61+ROUND(H60*$B$38,0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>ROUND(I57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>I61+ROUND(I60*$B$38,0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>ROUND(J57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>J61+ROUND(J60*$B$38,0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>ROUND(K57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>K61+ROUND(K60*$B$38,0)</f>
         <v/>
       </c>
       <c r="L63">
-        <f>ROUND(L57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>L61+ROUND(L60*$B$38,0)</f>
         <v/>
       </c>
       <c r="M63">
-        <f>ROUND(M57*($B$35*$B$33+(1-$B$35)*$B$34),0)</f>
+        <f>M61+ROUND(M60*$B$38,0)</f>
         <v/>
       </c>
       <c r="N63">
@@ -5576,176 +5748,65 @@
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>R3: B2C fee</t>
-        </is>
-      </c>
-      <c r="B64">
-        <f>B60*$B$36</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>C60*$B$36</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>D60*$B$36</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>E60*$B$36</f>
-        <v/>
-      </c>
-      <c r="F64">
-        <f>F60*$B$36</f>
-        <v/>
-      </c>
-      <c r="G64">
-        <f>G60*$B$36</f>
-        <v/>
-      </c>
-      <c r="H64">
-        <f>H60*$B$36</f>
-        <v/>
-      </c>
-      <c r="I64">
-        <f>I60*$B$36</f>
-        <v/>
-      </c>
-      <c r="J64">
-        <f>J60*$B$36</f>
-        <v/>
-      </c>
-      <c r="K64">
-        <f>K60*$B$36</f>
-        <v/>
-      </c>
-      <c r="L64">
-        <f>L60*$B$36</f>
-        <v/>
-      </c>
-      <c r="M64">
-        <f>M60*$B$36</f>
-        <v/>
-      </c>
-      <c r="N64">
-        <f>SUM(B64:M64)</f>
-        <v/>
-      </c>
-    </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>R4: upsell</t>
-        </is>
-      </c>
-      <c r="B65">
-        <f>B41</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>C41</f>
-        <v/>
-      </c>
-      <c r="D65">
-        <f>D41</f>
-        <v/>
-      </c>
-      <c r="E65">
-        <f>E41</f>
-        <v/>
-      </c>
-      <c r="F65">
-        <f>F41</f>
-        <v/>
-      </c>
-      <c r="G65">
-        <f>G41</f>
-        <v/>
-      </c>
-      <c r="H65">
-        <f>H41</f>
-        <v/>
-      </c>
-      <c r="I65">
-        <f>I41</f>
-        <v/>
-      </c>
-      <c r="J65">
-        <f>J41</f>
-        <v/>
-      </c>
-      <c r="K65">
-        <f>K41</f>
-        <v/>
-      </c>
-      <c r="L65">
-        <f>L41</f>
-        <v/>
-      </c>
-      <c r="M65">
-        <f>M41</f>
-        <v/>
-      </c>
-      <c r="N65">
-        <f>SUM(B65:M65)</f>
-        <v/>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>ВЫРУЧКА</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R5: реферал на мебель (Zolak)</t>
+          <t>R1+R2: сплит комиссии (аренда/продажа)</t>
         </is>
       </c>
       <c r="B66">
-        <f>ROUND(B59*$B$39*$B$40,0)</f>
+        <f>ROUND(B60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>ROUND(C59*$B$39*$B$40,0)</f>
+        <f>ROUND(C60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="D66">
-        <f>ROUND(D59*$B$39*$B$40,0)</f>
+        <f>ROUND(D60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="E66">
-        <f>ROUND(E59*$B$39*$B$40,0)</f>
+        <f>ROUND(E60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>ROUND(F59*$B$39*$B$40,0)</f>
+        <f>ROUND(F60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="G66">
-        <f>ROUND(G59*$B$39*$B$40,0)</f>
+        <f>ROUND(G60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="H66">
-        <f>ROUND(H59*$B$39*$B$40,0)</f>
+        <f>ROUND(H60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="I66">
-        <f>ROUND(I59*$B$39*$B$40,0)</f>
+        <f>ROUND(I60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="J66">
-        <f>ROUND(J59*$B$39*$B$40,0)</f>
+        <f>ROUND(J60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="K66">
-        <f>ROUND(K59*$B$39*$B$40,0)</f>
+        <f>ROUND(K60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="L66">
-        <f>ROUND(L59*$B$39*$B$40,0)</f>
+        <f>ROUND(L60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="M66">
-        <f>ROUND(M59*$B$39*$B$40,0)</f>
+        <f>ROUND(M60*($B$36*$B$34+(1-$B$36)*$B$35),0)</f>
         <v/>
       </c>
       <c r="N66">
@@ -5754,265 +5815,301 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R3: B2C fee</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>B63*$B$37</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>C63*$B$37</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>D63*$B$37</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>E63*$B$37</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>F63*$B$37</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>G63*$B$37</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>H63*$B$37</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>I63*$B$37</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>J63*$B$37</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>K63*$B$37</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>L63*$B$37</f>
+        <v/>
+      </c>
+      <c r="M67">
+        <f>M63*$B$37</f>
+        <v/>
+      </c>
+      <c r="N67">
+        <f>SUM(B67:M67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R4: upsell</t>
+        </is>
+      </c>
+      <c r="B68">
+        <f>B42</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>D42</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>F42</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>G42</f>
+        <v/>
+      </c>
+      <c r="H68">
+        <f>H42</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>I42</f>
+        <v/>
+      </c>
+      <c r="J68">
+        <f>J42</f>
+        <v/>
+      </c>
+      <c r="K68">
+        <f>K42</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>L42</f>
+        <v/>
+      </c>
+      <c r="M68">
+        <f>M42</f>
+        <v/>
+      </c>
+      <c r="N68">
+        <f>SUM(B68:M68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R5: реферал на мебель (Zolak)</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>ROUND(B62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>ROUND(C62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>ROUND(D62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>ROUND(E62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>ROUND(F62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>ROUND(G62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="H69">
+        <f>ROUND(H62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>ROUND(I62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="J69">
+        <f>ROUND(J62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="K69">
+        <f>ROUND(K62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>ROUND(L62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="M69">
+        <f>ROUND(M62*$B$40*$B$41,0)</f>
+        <v/>
+      </c>
+      <c r="N69">
+        <f>SUM(B69:M69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B67" s="6">
-        <f>B63+B64+B65+B66</f>
-        <v/>
-      </c>
-      <c r="C67" s="6">
-        <f>C63+C64+C65+C66</f>
-        <v/>
-      </c>
-      <c r="D67" s="6">
-        <f>D63+D64+D65+D66</f>
-        <v/>
-      </c>
-      <c r="E67" s="6">
-        <f>E63+E64+E65+E66</f>
-        <v/>
-      </c>
-      <c r="F67" s="6">
-        <f>F63+F64+F65+F66</f>
-        <v/>
-      </c>
-      <c r="G67" s="6">
-        <f>G63+G64+G65+G66</f>
-        <v/>
-      </c>
-      <c r="H67" s="6">
-        <f>H63+H64+H65+H66</f>
-        <v/>
-      </c>
-      <c r="I67" s="6">
-        <f>I63+I64+I65+I66</f>
-        <v/>
-      </c>
-      <c r="J67" s="6">
-        <f>J63+J64+J65+J66</f>
-        <v/>
-      </c>
-      <c r="K67" s="6">
-        <f>K63+K64+K65+K66</f>
-        <v/>
-      </c>
-      <c r="L67" s="6">
-        <f>L63+L64+L65+L66</f>
-        <v/>
-      </c>
-      <c r="M67" s="6">
-        <f>M63+M64+M65+M66</f>
-        <v/>
-      </c>
-      <c r="N67" s="6">
-        <f>SUM(B67:M67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B70" s="6">
+        <f>B66+B67+B68+B69</f>
+        <v/>
+      </c>
+      <c r="C70" s="6">
+        <f>C66+C67+C68+C69</f>
+        <v/>
+      </c>
+      <c r="D70" s="6">
+        <f>D66+D67+D68+D69</f>
+        <v/>
+      </c>
+      <c r="E70" s="6">
+        <f>E66+E67+E68+E69</f>
+        <v/>
+      </c>
+      <c r="F70" s="6">
+        <f>F66+F67+F68+F69</f>
+        <v/>
+      </c>
+      <c r="G70" s="6">
+        <f>G66+G67+G68+G69</f>
+        <v/>
+      </c>
+      <c r="H70" s="6">
+        <f>H66+H67+H68+H69</f>
+        <v/>
+      </c>
+      <c r="I70" s="6">
+        <f>I66+I67+I68+I69</f>
+        <v/>
+      </c>
+      <c r="J70" s="6">
+        <f>J66+J67+J68+J69</f>
+        <v/>
+      </c>
+      <c r="K70" s="6">
+        <f>K66+K67+K68+K69</f>
+        <v/>
+      </c>
+      <c r="L70" s="6">
+        <f>L66+L67+L68+L69</f>
+        <v/>
+      </c>
+      <c r="M70" s="6">
+        <f>M66+M67+M68+M69</f>
+        <v/>
+      </c>
+      <c r="N70" s="6">
+        <f>SUM(B70:M70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>РАСХОДЫ</t>
         </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Маркетинг: paid</t>
-        </is>
-      </c>
-      <c r="B70">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C70">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D70">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E70">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F70">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G70">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="H70">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="I70">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="J70">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="K70">
-        <f>K6</f>
-        <v/>
-      </c>
-      <c r="L70">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="M70">
-        <f>M6</f>
-        <v/>
-      </c>
-      <c r="N70">
-        <f>SUM(B70:M70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Контент / SEO</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="J71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="L71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M71" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="N71">
-        <f>SUM(B71:M71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>1073</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>1218</v>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>1291</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>1364</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>1436</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>1509</v>
-      </c>
-      <c r="J72" s="8" t="n">
-        <v>1582</v>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>1655</v>
-      </c>
-      <c r="L72" s="8" t="n">
-        <v>1727</v>
-      </c>
-      <c r="M72" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N72">
-        <f>SUM(B72:M72)</f>
-        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend-контрактор (доработки, фичи)</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G73" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J73" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="K73" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="L73" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="M73" s="8" t="n">
-        <v>2700</v>
+          <t>Маркетинг: paid</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M73">
+        <f>M6</f>
+        <v/>
       </c>
       <c r="N73">
         <f>SUM(B73:M73)</f>
@@ -6022,44 +6119,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
+          <t>Контент / SEO</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="C74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="N74">
         <f>SUM(B74:M74)</f>
@@ -6069,44 +6166,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Support/ops (B2C + агентства)</t>
+          <t>Продажник (BD): базовая ЗП, DE-speaking</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>600</v>
+        <v>1073</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>600</v>
+        <v>1145</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>700</v>
+        <v>1218</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>700</v>
+        <v>1291</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>700</v>
+        <v>1364</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>800</v>
+        <v>1436</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>800</v>
+        <v>1509</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>800</v>
+        <v>1582</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>900</v>
+        <v>1655</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>900</v>
+        <v>1727</v>
       </c>
       <c r="M75" s="8" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="N75">
         <f>SUM(B75:M75)</f>
@@ -6116,44 +6213,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Инфраструктура + AI API</t>
+          <t>Backend-контрактор (доработки, фичи)</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="C76" s="8" t="n">
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>850</v>
+        <v>2100</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>1050</v>
+        <v>2400</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>1150</v>
+        <v>2700</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>1200</v>
+        <v>2700</v>
       </c>
       <c r="M76" s="8" t="n">
-        <v>1250</v>
+        <v>2700</v>
       </c>
       <c r="N76">
         <f>SUM(B76:M76)</f>
@@ -6163,44 +6260,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tools, legal, прочее</t>
+          <t>Парсер / инфра-мейнтенанс (IS24 anti-bot, Chrome pipeline)</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M77" s="8" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N77">
         <f>SUM(B77:M77)</f>
@@ -6210,56 +6307,44 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Продажник: комиссия (% от R1+R2)</t>
-        </is>
-      </c>
-      <c r="B78">
-        <f>ROUND(B63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="C78">
-        <f>ROUND(C63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="D78">
-        <f>ROUND(D63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="E78">
-        <f>ROUND(E63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="F78">
-        <f>ROUND(F63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="G78">
-        <f>ROUND(G63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="H78">
-        <f>ROUND(H63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="I78">
-        <f>ROUND(I63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="J78">
-        <f>ROUND(J63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="K78">
-        <f>ROUND(K63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="L78">
-        <f>ROUND(L63*$B$38,0)</f>
-        <v/>
-      </c>
-      <c r="M78">
-        <f>ROUND(M63*$B$38,0)</f>
-        <v/>
+          <t>Support/ops (B2C + агентства)</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="L78" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>900</v>
       </c>
       <c r="N78">
         <f>SUM(B78:M78)</f>
@@ -6267,226 +6352,379 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Инфраструктура + AI API</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>750</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>950</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K79" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N79">
+        <f>SUM(B79:M79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Tools, legal, прочее</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="K80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="M80" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N80">
+        <f>SUM(B80:M80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Продажник: комиссия (% от R1+R2)</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>ROUND(B66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>ROUND(C66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>ROUND(D66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>ROUND(E66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>ROUND(F66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>ROUND(G66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="H81">
+        <f>ROUND(H66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>ROUND(I66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="J81">
+        <f>ROUND(J66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="K81">
+        <f>ROUND(K66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="L81">
+        <f>ROUND(L66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="M81">
+        <f>ROUND(M66*$B$39,0)</f>
+        <v/>
+      </c>
+      <c r="N81">
+        <f>SUM(B81:M81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>TOTAL COSTS</t>
         </is>
       </c>
-      <c r="B79" s="6">
-        <f>B70+B71+B72+B73+B74+B75+B76+B77+B78</f>
-        <v/>
-      </c>
-      <c r="C79" s="6">
-        <f>C70+C71+C72+C73+C74+C75+C76+C77+C78</f>
-        <v/>
-      </c>
-      <c r="D79" s="6">
-        <f>D70+D71+D72+D73+D74+D75+D76+D77+D78</f>
-        <v/>
-      </c>
-      <c r="E79" s="6">
-        <f>E70+E71+E72+E73+E74+E75+E76+E77+E78</f>
-        <v/>
-      </c>
-      <c r="F79" s="6">
-        <f>F70+F71+F72+F73+F74+F75+F76+F77+F78</f>
-        <v/>
-      </c>
-      <c r="G79" s="6">
-        <f>G70+G71+G72+G73+G74+G75+G76+G77+G78</f>
-        <v/>
-      </c>
-      <c r="H79" s="6">
-        <f>H70+H71+H72+H73+H74+H75+H76+H77+H78</f>
-        <v/>
-      </c>
-      <c r="I79" s="6">
-        <f>I70+I71+I72+I73+I74+I75+I76+I77+I78</f>
-        <v/>
-      </c>
-      <c r="J79" s="6">
-        <f>J70+J71+J72+J73+J74+J75+J76+J77+J78</f>
-        <v/>
-      </c>
-      <c r="K79" s="6">
-        <f>K70+K71+K72+K73+K74+K75+K76+K77+K78</f>
-        <v/>
-      </c>
-      <c r="L79" s="6">
-        <f>L70+L71+L72+L73+L74+L75+L76+L77+L78</f>
-        <v/>
-      </c>
-      <c r="M79" s="6">
-        <f>M70+M71+M72+M73+M74+M75+M76+M77+M78</f>
-        <v/>
-      </c>
-      <c r="N79" s="6">
-        <f>SUM(B79:M79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="B82" s="6">
+        <f>B73+B74+B75+B76+B77+B78+B79+B80+B81</f>
+        <v/>
+      </c>
+      <c r="C82" s="6">
+        <f>C73+C74+C75+C76+C77+C78+C79+C80+C81</f>
+        <v/>
+      </c>
+      <c r="D82" s="6">
+        <f>D73+D74+D75+D76+D77+D78+D79+D80+D81</f>
+        <v/>
+      </c>
+      <c r="E82" s="6">
+        <f>E73+E74+E75+E76+E77+E78+E79+E80+E81</f>
+        <v/>
+      </c>
+      <c r="F82" s="6">
+        <f>F73+F74+F75+F76+F77+F78+F79+F80+F81</f>
+        <v/>
+      </c>
+      <c r="G82" s="6">
+        <f>G73+G74+G75+G76+G77+G78+G79+G80+G81</f>
+        <v/>
+      </c>
+      <c r="H82" s="6">
+        <f>H73+H74+H75+H76+H77+H78+H79+H80+H81</f>
+        <v/>
+      </c>
+      <c r="I82" s="6">
+        <f>I73+I74+I75+I76+I77+I78+I79+I80+I81</f>
+        <v/>
+      </c>
+      <c r="J82" s="6">
+        <f>J73+J74+J75+J76+J77+J78+J79+J80+J81</f>
+        <v/>
+      </c>
+      <c r="K82" s="6">
+        <f>K73+K74+K75+K76+K77+K78+K79+K80+K81</f>
+        <v/>
+      </c>
+      <c r="L82" s="6">
+        <f>L73+L74+L75+L76+L77+L78+L79+L80+L81</f>
+        <v/>
+      </c>
+      <c r="M82" s="6">
+        <f>M73+M74+M75+M76+M77+M78+M79+M80+M81</f>
+        <v/>
+      </c>
+      <c r="N82" s="6">
+        <f>SUM(B82:M82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B81" s="6">
-        <f>B67-B79</f>
-        <v/>
-      </c>
-      <c r="C81" s="6">
-        <f>C67-C79</f>
-        <v/>
-      </c>
-      <c r="D81" s="6">
-        <f>D67-D79</f>
-        <v/>
-      </c>
-      <c r="E81" s="6">
-        <f>E67-E79</f>
-        <v/>
-      </c>
-      <c r="F81" s="6">
-        <f>F67-F79</f>
-        <v/>
-      </c>
-      <c r="G81" s="6">
-        <f>G67-G79</f>
-        <v/>
-      </c>
-      <c r="H81" s="6">
-        <f>H67-H79</f>
-        <v/>
-      </c>
-      <c r="I81" s="6">
-        <f>I67-I79</f>
-        <v/>
-      </c>
-      <c r="J81" s="6">
-        <f>J67-J79</f>
-        <v/>
-      </c>
-      <c r="K81" s="6">
-        <f>K67-K79</f>
-        <v/>
-      </c>
-      <c r="L81" s="6">
-        <f>L67-L79</f>
-        <v/>
-      </c>
-      <c r="M81" s="6">
-        <f>M67-M79</f>
-        <v/>
-      </c>
-      <c r="N81" s="6">
-        <f>SUM(B81:M81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Кэш (старт €18,000)</t>
-        </is>
-      </c>
-      <c r="B82">
-        <f>18000+B81</f>
-        <v/>
-      </c>
-      <c r="C82">
-        <f>B82+C81</f>
-        <v/>
-      </c>
-      <c r="D82">
-        <f>C82+D81</f>
-        <v/>
-      </c>
-      <c r="E82">
-        <f>D82+E81</f>
-        <v/>
-      </c>
-      <c r="F82">
-        <f>E82+F81</f>
-        <v/>
-      </c>
-      <c r="G82">
-        <f>F82+G81</f>
-        <v/>
-      </c>
-      <c r="H82">
-        <f>G82+H81</f>
-        <v/>
-      </c>
-      <c r="I82">
-        <f>H82+I81</f>
-        <v/>
-      </c>
-      <c r="J82">
-        <f>I82+J81</f>
-        <v/>
-      </c>
-      <c r="K82">
-        <f>J82+K81</f>
-        <v/>
-      </c>
-      <c r="L82">
-        <f>K82+L81</f>
-        <v/>
-      </c>
-      <c r="M82">
-        <f>L82+M81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
-        </is>
+      <c r="B84" s="6">
+        <f>B70-B82</f>
+        <v/>
+      </c>
+      <c r="C84" s="6">
+        <f>C70-C82</f>
+        <v/>
+      </c>
+      <c r="D84" s="6">
+        <f>D70-D82</f>
+        <v/>
+      </c>
+      <c r="E84" s="6">
+        <f>E70-E82</f>
+        <v/>
+      </c>
+      <c r="F84" s="6">
+        <f>F70-F82</f>
+        <v/>
+      </c>
+      <c r="G84" s="6">
+        <f>G70-G82</f>
+        <v/>
+      </c>
+      <c r="H84" s="6">
+        <f>H70-H82</f>
+        <v/>
+      </c>
+      <c r="I84" s="6">
+        <f>I70-I82</f>
+        <v/>
+      </c>
+      <c r="J84" s="6">
+        <f>J70-J82</f>
+        <v/>
+      </c>
+      <c r="K84" s="6">
+        <f>K70-K82</f>
+        <v/>
+      </c>
+      <c r="L84" s="6">
+        <f>L70-L82</f>
+        <v/>
+      </c>
+      <c r="M84" s="6">
+        <f>M70-M82</f>
+        <v/>
+      </c>
+      <c r="N84" s="6">
+        <f>SUM(B84:M84)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAC на квалифицированного лида, €</t>
+          <t>Кэш (старт €18,000)</t>
         </is>
       </c>
       <c r="B85">
-        <f>ROUND(N6/N56,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CAC на сделку, €</t>
-        </is>
-      </c>
-      <c r="B86">
-        <f>ROUND(N6/N59,0)</f>
+        <f>18000+B84</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>B85+C84</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>C85+D84</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>D85+E84</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>E85+F84</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>F85+G84</f>
+        <v/>
+      </c>
+      <c r="H85">
+        <f>G85+H84</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>H85+I84</f>
+        <v/>
+      </c>
+      <c r="J85">
+        <f>I85+J84</f>
+        <v/>
+      </c>
+      <c r="K85">
+        <f>J85+K84</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>K85+L84</f>
+        <v/>
+      </c>
+      <c r="M85">
+        <f>L85+M84</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Выручка на агентскую сделку, €</t>
-        </is>
-      </c>
-      <c r="B87">
-        <f>ROUND($B$35*$B$33+(1-$B$35)*$B$34,0)</f>
-        <v/>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>ЮНИТ-ЭКОНОМИКА (год)</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>CAC на квалифицированного лида, €</t>
+        </is>
+      </c>
+      <c r="B88">
+        <f>ROUND(N6/N59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CAC на сделку, €</t>
+        </is>
+      </c>
+      <c r="B89">
+        <f>ROUND(N6/N62,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Выручка на агентскую сделку, €</t>
+        </is>
+      </c>
+      <c r="B90">
+        <f>ROUND($B$36*$B$34+(1-$B$36)*$B$35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>LTV / CAC (агентский канал)</t>
         </is>
       </c>
-      <c r="B88">
-        <f>ROUND(B87/B86,1)</f>
+      <c r="B91">
+        <f>ROUND(B90/B89,1)</f>
         <v/>
       </c>
     </row>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="001F4E79"/>
+      <color rgb="FF1F4E79"/>
     </font>
   </fonts>
   <fills count="6">
@@ -54,22 +54,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F0E8"/>
+        <fgColor rgb="FFE8F0E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDE8F0"/>
+        <fgColor rgb="FFDDE8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E8D9"/>
+        <fgColor rgb="FFD9E8D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7E0"/>
+        <fgColor rgb="FFFFF7E0"/>
       </patternFill>
     </fill>
   </fills>

--- a/public/plan/bookimmo_business_plan_v2.xlsx
+++ b/public/plan/bookimmo_business_plan_v2.xlsx
@@ -494,9 +494,10 @@
       <c r="B3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3">
-        <f>== ТЕЗИС ===</f>
-        <v/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ТЕЗИС ===</t>
+        </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
     </row>
@@ -541,9 +542,10 @@
       <c r="B8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3">
-        <f>== КАНАЛЫ ЛИДОВ ===</f>
-        <v/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>КАНАЛЫ ЛИДОВ ===</t>
+        </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
     </row>
@@ -624,9 +626,10 @@
       <c r="B16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3">
-        <f>== ВОРОНКА ===</f>
-        <v/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ВОРОНКА ===</t>
+        </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
     </row>
@@ -695,9 +698,10 @@
       <c r="B23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3">
-        <f>== LEGAL ===</f>
-        <v/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL ===</t>
+        </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
     </row>
